--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle + clawback strengthened</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="F16" s="11" t="n"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>10x CEO own + EBITDA $ + buyback EXECUTING -3.6%</t>
+          <t>EBITDA $ hurdle + 10x CEO ownership + SOP 45% dissent + verified buyback EXECUTING</t>
         </is>
       </c>
       <c r="F17" s="11" t="n"/>
@@ -804,12 +804,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>RenaissanceRe</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Deepest per-share metric stack (5+) · clean</t>
+          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -830,22 +830,22 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Lands' End</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>12-tranche ladder + 86% PSU + live TARGET 14D-9</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -856,22 +856,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ADT Inc</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Named asset-sale PSU + 5-metric stack + P/B 0.33</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>90% PSU%LTI (heaviest) + verified shrink -7.3%</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -923,7 +923,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Anti-hedge + verified buyback EXECUTING -8.7%</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -942,14 +942,14 @@
           <t>Mattel</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Double dollar hurdle (EBITDA + FCF)</t>
+          <t>Unique double dollar hurdle: EBITDA $ + FCF $ targets both coded</t>
         </is>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>FCF $ hurdle + backlog target</t>
+          <t>FCF $ hurdle + backlog $ target + 70% PSU%LTI</t>
         </is>
       </c>
       <c r="F24" s="11" t="n"/>
@@ -986,12 +986,12 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Coeur Mining</t>
+          <t>RenaissanceRe</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>CEO 10b5-1 termination score 80 (#1 in universe)</t>
+          <t>Deepest per-share metric stack (5+) -- full alignment</t>
         </is>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -1012,22 +1012,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GoPro</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy cluster</t>
+          <t>PSU vests on spin / separation event -- board paid to execute</t>
         </is>
       </c>
       <c r="F26" s="11" t="n"/>
@@ -1038,22 +1038,22 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>GoPro</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Coeur Mining</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>PSU vests on spin / separation</t>
+          <t>CEO 10b5-1 termination score 80 -- #1 in universe + FCF/share PSU stack</t>
         </is>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>EBITDA $ hurdle + 10x CEO ownership + SOP 45% dissent + verified buyback EXECUTING -3.6%</t>
+          <t>EBITDA $ hurdle + 10x CEO ownership + SOP 45% dissent + verified buyback EXECUTING</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -1298,32 +1298,32 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>RenaissanceRe</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>$12,054</t>
+          <t>$381</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>$282.74</t>
+          <t>$12.41</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>Deepest per-share metric stack in universe (≥5 per-share metrics) — full alignment</t>
+          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>Insurance NAV + per-share metric discipline</t>
+          <t>Active third-party bid sets mechanical floor</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
@@ -1350,136 +1350,136 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$381</t>
+          <t>$264</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$12.41</t>
+          <t>$5.43</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>12-tranche price ladder + 86% PSU%LTI + ROIC + live take-private 14D-9</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>Active third-party bid sets mechanical floor</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$264</t>
+          <t>$5,065</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$5.43</t>
+          <t>$6.66</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.33 — deep book discount + buyback shrinking organically</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$5,065</t>
+          <t>$818</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$6.66</t>
+          <t>$8.27</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>Discount-grocery defensive base</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING -8.7% (largest verified shrinkage)</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -1601,9 +1601,9 @@
           <t>Brand portfolio + 6-metric stack provides discipline</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>RNR</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Coeur Mining</t>
+          <t>RenaissanceRe</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>$16,581</t>
+          <t>$12,054</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$16.09</t>
+          <t>$282.74</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>CEO 10b5-1 termination score 80 — #1 in universe + FCF/share PSU stack</t>
+          <t>Deepest per-share metric stack (5+) -- full alignment</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>Precious-metals price floor + CEO walked back scheduled selling</t>
+          <t>Insurance NAV + per-share metric discipline</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -1714,104 +1714,104 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>GoPro</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$818</t>
+          <t>$137</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>$8.27</t>
+          <t>$0.79</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-71.80</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster ($7.9M = 0.97% mcap)</t>
+          <t>PSU vests on spin / separation event -- board paid to execute</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>Discount-grocery defensive base</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Brand + cash position</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>GoPro</t>
+          <t>Coeur Mining</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>$137</t>
+          <t>$16,581</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$0.79</t>
+          <t>$16.09</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>-71.80</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>PSU vests on spin / separation event — board paid to execute separation</t>
+          <t>CEO 10b5-1 termination score 80 -- #1 in universe + FCF/share PSU stack</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>Brand + cash position</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Precious-metals price floor + CEO walked back scheduled selling</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -752,12 +752,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="F16" s="11" t="n"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>EBITDA $ hurdle + 10x CEO ownership + SOP 45% dissent + verified buyback EXECUTING</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="F17" s="11" t="n"/>
@@ -804,22 +804,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Lands' End</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -830,12 +830,12 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>Aurinia Pharmaceuticals</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU + valuation + 10b5-1 + recent-incentive + special-sits firing</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -856,12 +856,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -882,22 +882,22 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -908,22 +908,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Tonix Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Mattel</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Unique double dollar hurdle: EBITDA $ + FCF $ targets both coded</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -960,22 +960,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>FCF $ hurdle + backlog $ target + 70% PSU%LTI</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F24" s="11" t="n"/>
@@ -986,22 +986,22 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>RenaissanceRe</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Deepest per-share metric stack (5+) -- full alignment</t>
+          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
         </is>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -1012,22 +1012,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>KUST</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>GoPro</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>KUST</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>PSU vests on spin / separation event -- board paid to execute</t>
+          <t>4 layers firing | cons 3.074</t>
         </is>
       </c>
       <c r="F26" s="11" t="n"/>
@@ -1038,51 +1038,267 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Coeur Mining</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
+          <t>Hyperscale Data</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Valuation + live tender + 10b5-1 + recent-incentive</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>FLGT</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Fulgent Genetics</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>PSU + valuation P/B 0.51 + special-sits + recent-incentive</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>BCO</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Brink's Company</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Material 2-5%</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>CEO 10b5-1 termination score 80 -- #1 in universe + FCF/share PSU stack</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>10b5-1 termination + special-sits + PSU</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>FISV</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>4 layers firing | cons 2.792</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>NUS</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>4 layers firing | cons 2.73</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n"/>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Cyclepapa Research · Module Series 1 · The framework produces 12 names by demanding (a) presence in top-N of ≥3 of 8 independent rankers built from independent evidence and (b) winner of at least one PSU/governance archetype across 57 buckets. Robustness checks: list unchanged after expanding yfinance coverage and after a governance-scoring bugfix that nearly tripled Tier-B coverage.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="31">
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E29:F29"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="C6:F6"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="C5:F5"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
@@ -1101,7 +1317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1194,47 +1410,47 @@
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>$98</t>
+          <t>$5,004</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>$1.84</t>
+          <t>$6.58</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -1246,47 +1462,47 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>$13,856</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>$33.93</t>
+          <t>$1.89</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>EBITDA $ hurdle + 10x CEO ownership + SOP 45% dissent + verified buyback EXECUTING</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>Quasi-monopoly RE data; recurring revenue base</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -1298,32 +1514,32 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>$381</t>
+          <t>$1,474</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>$12.41</t>
+          <t>$25.03</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -1333,64 +1549,64 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>Active third-party bid sets mechanical floor</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>Aurinia Pharmaceuticals</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$264</t>
+          <t>$2,117</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$5.43</t>
+          <t>$16.46</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU + valuation + 10b5-1 + recent-incentive + special-sits firing</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>Lupus nephritis franchise + cash position</t>
         </is>
       </c>
       <c r="J8" s="10" t="inlineStr">
@@ -1402,32 +1618,32 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$5,065</t>
+          <t>$254</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$6.66</t>
+          <t>$0.61</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1437,12 +1653,12 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>P/B 0.55 + IP library</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
@@ -1454,32 +1670,32 @@
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Grocery Outlet</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$818</t>
+          <t>$222</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$8.27</t>
+          <t>$5.27</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -1489,49 +1705,49 @@
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Discount-grocery defensive base</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tonix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>$1,434</t>
+          <t>$213</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>$24.35</t>
+          <t>$3.76</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1541,64 +1757,64 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.52 microcap</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Mattel</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>$4,257</t>
+          <t>$1,394</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>$14.65</t>
+          <t>$8.60</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target, fcf_dollar_target</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>Unique double dollar hurdle: EBITDA $ + FCF $ targets both coded</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>Brand portfolio + 6-metric stack provides discipline</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
@@ -1610,84 +1826,84 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>$124,580</t>
+          <t>$4,158</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>$540.33</t>
+          <t>$88.94</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>fcf_dollar_target, backlog_target</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>FCF $ hurdle + backlog $ target + 70% PSU%LTI</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>Defense backlog + sovereign counterparty</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>RenaissanceRe</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>$12,054</t>
+          <t>$31,085</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$282.74</t>
+          <t>$186.25</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -1697,101 +1913,101 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>Deepest per-share metric stack (5+) -- full alignment</t>
+          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>Insurance NAV + per-share metric discipline</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Healthcare data services franchise</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>KUST</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>GoPro</t>
+          <t>KUST</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$137</t>
+          <t>$1</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>$0.79</t>
+          <t>$1.70</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>-71.80</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>PSU vests on spin / separation event -- board paid to execute</t>
+          <t>4 layers firing | cons 3.074</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>Brand + cash position</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Coeur Mining</t>
+          <t>Hyperscale Data</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>$16,581</t>
+          <t>$91</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$16.09</t>
+          <t>$0.17</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -1801,22 +2017,438 @@
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>CEO 10b5-1 termination score 80 -- #1 in universe + FCF/share PSU stack</t>
+          <t>Valuation + live tender + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>Precious-metals price floor + CEO walked back scheduled selling</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
+          <t>P/B 0.50 + live self-tender</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>$124,308</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>$151.78</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="17" t="inlineStr">
+        <is>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>FLGT</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Fulgent Genetics</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>$511</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>$18.00</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>merger_acquisition_close</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>PSU + valuation P/B 0.51 + special-sits + recent-incentive</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Half book + cash position</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>BCO</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Brink's Company</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>$4,022</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>$97.67</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>15.36</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>10b5-1 termination + special-sits + PSU</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>Cash-handling services franchise</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>Material 2-5%</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>FISV</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>$25,522</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>$47.86</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
+        <is>
+          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+        </is>
+      </c>
+      <c r="I20" s="19" t="inlineStr">
+        <is>
+          <t>FCF/share PSU metric anchor</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>$77</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>$5.91</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
+          <t>4 layers firing | cons 2.792</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>NUS</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>$244</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>$5.02</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>asset_sale_named</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+        </is>
+      </c>
+      <c r="I22" s="19" t="inlineStr">
+        <is>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>ZTS</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>$32,997</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>$78.71</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>10.04</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+        </is>
+      </c>
+      <c r="I23" s="17" t="inlineStr">
+        <is>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>$2,929</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>$55.74</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
+        <is>
+          <t>4 layers firing | cons 2.73</t>
+        </is>
+      </c>
+      <c r="I24" s="19" t="inlineStr">
+        <is>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Catalyst (cond_cat) = forward-conditional vesting category coded in the PSU plan text. Sizing band reflects the convergence strength (number of independent screens) combined with red-flag count from the plan-evolution score. Source CSVs: consensus_ranking.csv, grand_unified_ranked.csv, buyback_verify.json, tender_scan.json.</t>
         </is>
@@ -1825,7 +2457,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1928,12 +2560,12 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>$98</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -1963,12 +2595,12 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>$13,856</t>
+          <t>$12,300</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -1998,12 +2630,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>$124,580</t>
+          <t>$117,806</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -2033,12 +2665,12 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>$13,143</t>
+          <t>$12,970</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -2068,12 +2700,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>$102,405</t>
+          <t>$107,716</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -2103,12 +2735,12 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>$124,580</t>
+          <t>$117,806</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -2138,12 +2770,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>$2,435</t>
+          <t>$2,388</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -2178,7 +2810,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>-71.80</t>
+          <t>-71.81</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -2208,12 +2840,12 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>$1,855</t>
+          <t>$2,065</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -2243,12 +2875,12 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>$264</t>
+          <t>$244</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -2278,12 +2910,12 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>$84,086</t>
+          <t>$83,814</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2313,12 +2945,12 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>$79,364</t>
+          <t>$75,711</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -2348,12 +2980,12 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>$1,620</t>
+          <t>$1,595</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2418,12 +3050,12 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>$381</t>
+          <t>$382</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2453,12 +3085,12 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>$5,065</t>
+          <t>$5,004</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -2488,12 +3120,12 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>$381</t>
+          <t>$382</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2523,12 +3155,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>$12,054</t>
+          <t>$12,755</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -2558,12 +3190,12 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>$46,722</t>
+          <t>$40,924</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2593,12 +3225,12 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>$381</t>
+          <t>$382</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -2628,12 +3260,12 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>$1,434</t>
+          <t>$1,474</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -2663,12 +3295,12 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>$13,856</t>
+          <t>$12,300</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -2698,12 +3330,12 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>$1,434</t>
+          <t>$1,474</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -2733,12 +3365,12 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>$98</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -2768,12 +3400,12 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>$211</t>
+          <t>$204</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -2803,12 +3435,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>$1,437</t>
+          <t>$1,689</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -2838,12 +3470,12 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>$13,856</t>
+          <t>$12,300</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -2873,12 +3505,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>$13,856</t>
+          <t>$12,300</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -2908,12 +3540,12 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>$13,383</t>
+          <t>$14,011</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -2943,12 +3575,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>$1,093</t>
+          <t>$981</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -2978,12 +3610,12 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>$1,486</t>
+          <t>$1,394</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -3013,12 +3645,12 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>$98</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -3048,12 +3680,12 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>$1,434</t>
+          <t>$1,474</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -3083,12 +3715,12 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>$28,412</t>
+          <t>$25,522</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -3153,12 +3785,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>$818</t>
+          <t>$916</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -3188,12 +3820,12 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>$381</t>
+          <t>$382</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
@@ -3223,12 +3855,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>$13,856</t>
+          <t>$12,300</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -3258,12 +3890,12 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>$98</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
@@ -3293,12 +3925,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>$4,257</t>
+          <t>$4,080</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -3328,12 +3960,12 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>$4,257</t>
+          <t>$4,080</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr">
@@ -3363,12 +3995,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>$38</t>
+          <t>$39</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -3398,12 +4030,12 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>$13,354</t>
+          <t>$13,048</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
@@ -3433,12 +4065,12 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>$36,671</t>
+          <t>$35,886</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -3468,12 +4100,12 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>$1,855</t>
+          <t>$2,065</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
@@ -3503,12 +4135,12 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>$264</t>
+          <t>$244</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -3538,12 +4170,12 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>$84,086</t>
+          <t>$83,814</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
@@ -3573,12 +4205,12 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>$5,065</t>
+          <t>$5,004</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -3608,12 +4240,12 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>$1,934</t>
+          <t>$1,918</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -3713,12 +4345,12 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>$7,262</t>
+          <t>$7,250</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -3748,12 +4380,12 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>$16,581</t>
+          <t>$18,045</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -3783,12 +4415,12 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>$6,348</t>
+          <t>$5,821</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -830,22 +830,22 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Aurinia Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive + special-sits firing</t>
+          <t>5 layers firing | cons 3.02</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -856,22 +856,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Getty Images</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Encore Capital</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
+          <t>PSU 43 + buyback + recent-incentive</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>5 layers firing | cons 2.38</t>
         </is>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -908,12 +908,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Tonix Pharmaceuticals</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -986,22 +986,22 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>IQVIA</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GTM (placeholder)</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
+          <t>PSU + valuation + recent activist 13D 4d ago + special-sits</t>
         </is>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -1012,22 +1012,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>KUST</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>KUST</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 3.074</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F26" s="11" t="n"/>
@@ -1064,22 +1064,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>KUST</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>KUST</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>4 layers firing | cons 2.95</t>
         </is>
       </c>
       <c r="F28" s="11" t="n"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Fulgent Genetics</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>PSU + valuation P/B 0.51 + special-sits + recent-incentive</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="F29" s="11" t="n"/>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Brink's Company</t>
+          <t>Thryv Holdings</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>10b5-1 termination + special-sits + PSU</t>
+          <t>Triple-$ PSU hurdle + valuation + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="F30" s="11" t="n"/>
@@ -1142,22 +1142,22 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Tonix Pharmaceuticals</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
         </is>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -1168,22 +1168,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>BCO</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>SWZ</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Brink's Company</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 2.792</t>
+          <t>10b5-1 termination + special-sits + PSU</t>
         </is>
       </c>
       <c r="F32" s="11" t="n"/>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -1220,22 +1220,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
         </is>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 2.73</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F35" s="11" t="n"/>
@@ -1566,32 +1566,32 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Aurinia Pharmaceuticals</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$2,117</t>
+          <t>$2,929</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$16.46</t>
+          <t>$55.74</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -1601,49 +1601,49 @@
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive + special-sits firing</t>
+          <t>5 layers firing | cons 3.02</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>Lupus nephritis franchise + cash position</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Getty Images</t>
+          <t>Encore Capital</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$254</t>
+          <t>$1,781</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$0.61</t>
+          <t>$83.05</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -1653,64 +1653,64 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
+          <t>PSU 43 + buyback + recent-incentive</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.55 + IP library</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Debt-collection franchise</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$222</t>
+          <t>$3,906</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$5.27</t>
+          <t>$39.40</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>5 layers firing | cons 2.38</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J10" s="10" t="inlineStr">
@@ -1722,47 +1722,47 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Tonix Pharmaceuticals</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>$213</t>
+          <t>$254</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>$3.76</t>
+          <t>$0.61</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.52 microcap</t>
+          <t>P/B 0.55 + IP library</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
@@ -1878,104 +1878,104 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>GTM (placeholder)</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>$31,085</t>
+          <t>$828</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$186.25</t>
+          <t>$2.81</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
+          <t>PSU + valuation + recent activist 13D 4d ago + special-sits</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>Healthcare data services franchise</t>
-        </is>
-      </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>P/B 0.54 + 78% drawdown</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>KUST</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>KUST</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$1</t>
+          <t>$124,308</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>$1.70</t>
+          <t>$151.78</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 3.074</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -2034,32 +2034,32 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>KUST</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KUST</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>$124,308</t>
+          <t>$1</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>$151.78</t>
+          <t>$1.70</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2069,64 +2069,64 @@
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>4 layers firing | cons 2.95</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>FLGT</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Fulgent Genetics</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>$511</t>
+          <t>$244</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>$18.00</t>
+          <t>$5.02</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>merger_acquisition_close</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>PSU + valuation P/B 0.51 + special-sits + recent-incentive</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>Half book + cash position</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -2138,47 +2138,47 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Brink's Company</t>
+          <t>Thryv Holdings</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>$4,022</t>
+          <t>$155</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>$97.67</t>
+          <t>$3.50</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ebitda_dollar_target, revenue_dollar_target, fcf_dollar_target</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>10b5-1 termination + special-sits + PSU</t>
+          <t>Triple-$ PSU hurdle + valuation + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>Cash-handling services franchise</t>
+          <t>P/B 0.74 SMB services</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -2190,32 +2190,32 @@
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Tonix Pharmaceuticals</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$25,522</t>
+          <t>$213</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>$47.86</t>
+          <t>$3.76</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -2225,153 +2225,153 @@
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>FCF/share PSU metric anchor</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>P/B 0.52 microcap</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>BCO</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>Brink's Company</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>$77</t>
+          <t>$4,022</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>$5.91</t>
+          <t>$97.67</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>15.36</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 2.792</t>
+          <t>10b5-1 termination + special-sits + PSU</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Cash-handling services franchise</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>$244</t>
+          <t>$25,522</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>$5.02</t>
+          <t>$47.86</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>FCF/share PSU metric anchor</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>$32,997</t>
+          <t>$31,085</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>$78.71</t>
+          <t>$186.25</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -2381,49 +2381,49 @@
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Healthcare data services franchise</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>$2,929</t>
+          <t>$32,997</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>$55.74</t>
+          <t>$78.71</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 2.73</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -12,8 +12,9 @@
     <sheet name="By Archetype" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Reserve Baskets" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Caution List" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Without Valuation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6298,6 +6299,1283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Top of Universe -- Without Valuation Leg</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Parallel ranking that excludes valuation entirely so names missing yfinance overlay are not penalised. Compared against the valuation-included ranking to identify structurally-strong-but-valuation-hidden names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Layers</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Consensus</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Lift vs val</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>ADT Inc.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>HFFG</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>HF Foods Group Inc.</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>3.604</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>PSU:48 F4:18 RI:59 SS:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Universal Display Corporation</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>BCO</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Brinks Company (The)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>+13</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>PSU:34 BB:5 C10:36 RI:32 SS:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>MMS</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Maximus, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>3.094</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>PSU:36 BB:5 RI:53 SS:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>3.084</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>IQV</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>IQVIA Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>3.062</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>+12</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>ECPG</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Encore Capital Group Inc</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>2.858</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>PSU:43 BB:5 C10:-12 RI:52 SS:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Dynatrace, Inc.</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>2.676</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>+26</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>PSU:22 BB:5 C10:49 RI:53 SS:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>BDC</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Belden Inc</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>2.666</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>+22</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>PSU:38 BB:5 C10:15 RI:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>AUPH</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Aurinia Pharmaceuticals Inc</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>2.564</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>+19</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>PSU:33 BB:5 C10:32 RI:37 SS:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>KMPR</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Kemper Corporation</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>2.526</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>FOUR</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Shift4 Payments, Inc.</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>2.412</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Mastercard Incorporated</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>2.402</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>+12</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Blend Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>2.398</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>NXST</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>2.258</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>+15</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>PSU:30 C10:25 RI:55 SS:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>lululemon athletica inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>2.176</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>+24</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>TKO</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>TKO Group Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>1.886</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>+27</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>WMS</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Advanced Drainage Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>1.836</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>+115</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>PSU:37 C10:8 RI:40 SS:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>CDW Corporation</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>1.426</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>+27</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>PSU:29 BB:5 F4:5 RI:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>CVGI</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Commercial Vehicle Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>1.024</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>PSU:28 BB:5 C10:7 RI:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Pool Corporation</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>2.732</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>+33</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>CoStar Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>2.656</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>+41</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>PSU:50 BB:8 RI:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Total Return Securities Fund</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>2.646</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>+35</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>TND:25 F4:6 RI:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>GETY</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Getty Images Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>2.608</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>PSU:5 TND:25 C10:74 RI:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>CMLSQ</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Cumulus Media Inc.</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>2.568</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>+36</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>C10:56 RI:51 SS:70</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>HDSN</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Hudson Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>BB:5 F4:18 RI:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>HubSpot, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>2.488</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>+52</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>TXRH</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Texas Roadhouse, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>2.448</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>+46</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>PSU:22 BB:8 C10:36 RI:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>DXC Technology Company</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>2.432</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>-22</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>PSU:40 BB:5 RI:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>'Lift vs val' shows how many positions a name climbs when valuation is excluded. A large positive lift means the name is structurally strong but is being penalised by the valuation layer -- likely either missing yfinance overlay or trading at multiples outside our discount zones (P/B&gt;1.5, P/E&gt;15, EV/EBITDA&gt;10). The 26 emergent names (consensus_emergent_noval.csv) are gap-fill priorities.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6705,7 +7983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -13,8 +13,9 @@
     <sheet name="Reserve Baskets" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Caution List" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Without Valuation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Single-Measure Best" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +79,12 @@
       <b val="1"/>
       <color rgb="00A41E22"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="00A41E22"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="7">
@@ -139,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -205,6 +212,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7576,6 +7586,2679 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Best in Class -- Single-Measure Exceptional</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Names ranking top in ONE individual signal even if the consensus misses them. The 'single-leg high-intensity' tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Highest PSU forensic core</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: depth + rigor of the PSU plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 72 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Target Corporation</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 64 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>TROX</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Tronox Holdings plc</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>63.9</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 60 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 60 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>ECPG</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Encore Capital Group Inc</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 59 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>CBL</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>CBL &amp; Associates Properties, In</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 58 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>STAA</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>STAAR Surgical Company</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 57 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Nasdaq, Inc.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">core 57 | cond_cats: </t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Autodesk, Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Highest governance score</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>gov 23 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>NXT</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Nextpower Inc.</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 4y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Agilent Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>GFF</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Griffon Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange Inc.</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>CGNX</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Cognex Corporation</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>ConocoPhillips</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>ATEC</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Alphatec Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>NBHC</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>National Bank Holdings Corporat</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Deepest P/B floor (&lt;0.5x book)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: hard balance-sheet value floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>P/B 0.04 | mcap $20M</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>CRMT</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>America's Car-Mart, Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>P/B 0.05 | mcap $19M</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>SVRN</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>OceanPal Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>P/B 0.06 | mcap $10M</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>ZSTK</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>ZeroStack Corp.</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>P/B 0.09 | mcap $52M</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>EHTH</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>eHealth, Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>P/B 0.09 | mcap $5M</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>FEED</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>ENvue Medical, Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>P/B 0.12 | mcap $5M</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>RBNE</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Robin Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>P/B 0.13 | mcap $10M</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Jet.AI Inc.</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>P/B 0.13 | mcap $69M</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>GPMT</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Granite Point Mortgage Trust In</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>Cheapest EV/EBITDA (&lt;6x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: enterprise-value to earnings power</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.5 | mcap $30M | Technology</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>KPLT</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Katapult Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.6 | mcap $72M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>PLRX</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Pliant Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.7 | mcap $7M | Technology</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>DTST</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Data Storage Corporation</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.7 | mcap $45M | Technology</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>LGL</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>LGL Group, Inc. (The)</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.9 | mcap $704M | Financial Services</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>HRTG</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Heritage Insurance Holdings, In</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 1.0 | mcap $539M | Real Estate</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>RMAX</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>RE/MAX Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 1.1 | mcap $1,899M | Financial Services</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Slide Insurance Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 1.1 | mcap $2,856M | Technology</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>VISN</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Vistance Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>Lowest trailing P/E (&lt;8x, positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: earnings yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>P/E 0.9 | mcap $426M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>CYH</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Community Health Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>P/E 1.1 | mcap $382M | Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Lands' End, Inc.</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>P/E 1.4 | mcap $250M | Real Estate</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>SITC</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>SITE Centers Corp.</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>P/E 1.4 | mcap $120M | Technology</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>SCOR</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>comScore, Inc.</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>P/E 1.5 | mcap $159M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>ORMP</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>Oramed Pharmaceuticals Inc.</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>P/E 1.6 | mcap $192M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>WW</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>WW International, Inc.</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>P/E 1.6 | mcap $940M | Energy</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Diversified Energy Company</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>P/E 1.6 | mcap $185M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>EMBC</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Embecta Corp.</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>Largest verified buyback shrinkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: actual supply curve compression</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>shares -29.9% over 174d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>ANAB</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>AnaptysBio, Inc.</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>shares -27.4% over 181d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>EIG</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Employers Holdings Inc</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>shares -27.2% over 147d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>NWL</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Newell Brands Inc.</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>shares -26.7% over 65d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>AHRT</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>AH Realty Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>shares -24.8% over 189d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>AESI</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Atlas Energy Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>shares -21.1% over 185d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>CWEN</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Clearway Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>shares -20.6% over 176d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>AAT</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>American Assets Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>20.6</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>shares -19.7% over 189d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>FOA</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Finance of America Companies In</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>Highest 10b5-1 termination signed score</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: insider walked back scheduled selling</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: Casey M. Nault (Senior Vice President) 202,257sh [+26]', 'BULLISH terminate sell: Mitchell J. Krebs (Chairman) 202,257sh [+38]', 'BULLISH terminate sell: Mitchell J. Krebs (Chairman) 250,000sh [+42]', 'BEARISH adopt sell: Mitchell J. Krebs (Chairman) 200,000sh [-23]', 'BEARISH adopt sell: Casey M. Nault (Senior Vice President) 200,000sh [-15]', 'BULLISH terminate sell: Casey M. Nault (Executive Vice President) 202,257sh [+26]']</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Coeur Mining, Inc.</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]']</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>IRON</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Disc Medicine, Inc.</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BEARISH adopt sell: Roger W. Byrd (General Counsel) 135,201sh [-15]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) 518,289sh [+38]', 'BULLISH terminate sell: Roger W. Byrd (General Counsel) 518,289sh [+30]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) 135,201sh [+34]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) [+26]']</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (Director) 37,890sh [+18]', 'BULLISH terminate sell: an insider (Director) 97,075sh [+22]', 'BULLISH terminate sell: an insider (Director) 387,158sh [+30]', 'BULLISH terminate sell: an insider (Director) 363,818sh [+30]', 'BULLISH terminate sell: an insider (Director) [+18]', 'BULLISH terminate sell: an insider (Director) [+18]']</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) 165,000sh [+26]', 'BULLISH terminate sell: an insider (director) [+18]']</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: John F. Marcolini (Senior Vice President) 11,400sh [+18]', 'BULLISH terminate sell: Thomas L. Deitrich (President and Chief Executive ) 9,540sh [+30]', 'BULLISH terminate sell: Thomas L. Deitrich (President and Chief Executive ) 6,904sh [+30]', 'BULLISH terminate sell: Donald L. Reeves (Senior Vice President) 4,170sh [+18]']</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>ITRI</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Itron, Inc.</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: William R. McDermott (Chief Executive Officer) 3,700sh [+30]', 'BULLISH terminate sell: Gina Mastantuono (President and Chief Financial ) 3,700sh [+26]', 'BULLISH terminate sell: Nick Tzitzon (Vice Chairman) 3,700sh [+30]', 'BULLISH terminate sell: Nick Tzitzon (Vice Chairman) 649sh [+30]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 1,200sh [-3]', 'weak BEARISH adopt sell (small): Kevin McBride (Chief Accounting Officer) 1,120sh [-3]', 'weak BEARISH adopt sell (small): Nick Tzitzon (Vice Chairman) 1,120sh [-3]', 'weak BEARISH adopt sell (small): Paul Fipps (President) 253sh [-3]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 830sh [-3]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 352sh [-3]']</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>ServiceNow, Inc.</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (?) [+18]', 'BULLISH terminate sell: an insider (director) 13,216sh [+18]', 'BULLISH terminate sell: an insider (?) 139,948sh [+26]', 'BULLISH terminate sell: an insider (director) 38,227sh [+18]']</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>SCHW</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Charles Schwab Corporation (The</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="25" t="inlineStr">
+        <is>
+          <t>Largest insider Form 4 dollar cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: insider conviction in dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>$105.1M cluster, 2 buyers</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>105122527.2</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>$100.5M cluster, 1 buyers (0.16% of mcap)</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>RSG</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Republic Services, Inc.</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>100528322.0</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>$75.3M cluster, 7 buyers (9.57% of mcap)</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>ODTX</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Odyssey Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>75319986.0</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>$75.0M cluster, 1 buyers (20.80% of mcap)</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>ARTV</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Artiva Biotherapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>74999992.3</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>$74.0M cluster, 1 buyers (4.16% of mcap)</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>GeneDx Holdings Corp.</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>74032163.4</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>$65.9M cluster, 2 buyers (4.19% of mcap)</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Alkami Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>65859500.0</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>$54.4M cluster, 9 buyers</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr"/>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>54366421.6</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>$45.7M cluster, 5 buyers (0.05% of mcap)</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>KKR &amp; Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>45684632.3</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="25" t="inlineStr">
+        <is>
+          <t>Live tender / 13E-3 events</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: mechanical bid as floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>EXFY</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Expensify, Inc.</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>ABX</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Abacus Global Management, Inc.</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>ABXL</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr"/>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>TARGET | live event</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>ASRT</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Assertio Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>UNKNOWN | live event</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="inlineStr">
+        <is>
+          <t>AUPH</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Aurinia Pharmaceuticals Inc</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>UNKNOWN | live event</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>BCIC</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>BCP Investment Corporation</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="inlineStr">
+        <is>
+          <t>BCX</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>BlackRock Resources  of Benefic</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>BGY</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Blackrock Enhanced Internationa</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>UNKNOWN | live event</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>BHC</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr"/>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>BIDDER | live event</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Biogen Inc.</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Each section ranks names by a SINGLE measure regardless of whether other layers fire. These are 'exceptional by one 'criterion' -- examples: ODTX archetype (insider cluster only), GETY (live self-tender only), CDE (CEO 10b5-1 termination only). Such names rarely appear in the consensus convergent list because they don't fire multiple layers, but they can be the right pick for a single-mandate position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A65:F65"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7862,7 +10545,7 @@
           <t>346</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
@@ -7983,7 +10666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8039,7 +10722,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set.</t>
         </is>
@@ -8054,7 +10737,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>Seven scoring layers ingested per ticker: PSU forensics, governance, valuation, buyback verification, tender mechanics, 10b5-1 directional, Form 4 P-buys (plus Form 144 for bearish).</t>
         </is>
@@ -8069,7 +10752,7 @@
           <t>Per-layer scoring</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Each layer produces (points, has_data, reason). points are capped to prevent any single layer dominating; has_data is True when ANY field in the layer is populated (key bugfix: governance is True for all 4,410 DEF 14As scanned, not only those with PSU programs).</t>
         </is>
@@ -8084,7 +10767,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>norm_score = raw_score × sqrt(7 / n_layers_present) for names with ≥3 layers. Names with 4 strong of 7 layers are not penalised vs names with 7 mediocre layers.</t>
         </is>
@@ -8099,7 +10782,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Top 10 in each of 18 catalyst patterns (forward $ hurdle, M&amp;A close, spin trigger, FDA milestone, etc.) — surfaces single-mandate leaders.</t>
         </is>
@@ -8114,7 +10797,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe. Produces PSU_ARCHETYPES.md (38) + ASYMMETRIC_BY_ARCHETYPE.md (19).</t>
         </is>
@@ -8129,7 +10812,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Each of 8 independent rankers + 2 archetype-winner markdowns contributes presence. n_screens = how many rankers surface the ticker. n_archetypes = how many buckets it wins. consensus_score = sum of rank-decay contributions.</t>
         </is>
@@ -8144,7 +10827,7 @@
           <t>Convergence test</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Name is convergent IFF n_screens ≥ 3 AND n_archetypes ≥ 1. Probability of 6-screen convergence by chance ≈ 2.4×10⁻¹⁰.</t>
         </is>
@@ -8159,7 +10842,7 @@
           <t>Robustness checks</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Check 1: re-run after expanding yfinance from 1,885 to 2,132 (no change in convergent list). Check 2: governance bugfix expanded Tier-B coverage 2.8x (still no change). Convergent twelve is structurally informative, not data-dependent.</t>
         </is>
@@ -8174,7 +10857,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>Eight red-flag classes scored from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -8189,7 +10872,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean convergent + ≥4 screens. Material (2-5%): 1-flag convergent or 4+ archetypes. Participation (0.5-2%): single-archetype or multi-flag. Basket (&lt;1% each): sub-archetype groups.</t>
         </is>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -13,9 +13,10 @@
     <sheet name="Reserve Baskets" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Caution List" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Without Valuation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Single-Measure Best" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Methodology" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Recent 30d" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Single-Measure Best" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Methodology" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1322,6 +1323,235 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>How the convergent twelve were surfaced from the 6,164-name universe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Universe construction</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Layer ingestion</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>Seven scoring layers ingested per ticker: PSU forensics, governance, valuation, buyback verification, tender mechanics, 10b5-1 directional, Form 4 P-buys (plus Form 144 for bearish).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Per-layer scoring</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Each layer produces (points, has_data, reason). points are capped to prevent any single layer dominating; has_data is True when ANY field in the layer is populated (key bugfix: governance is True for all 4,410 DEF 14As scanned, not only those with PSU programs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Coverage-normalised composite</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t>norm_score = raw_score × sqrt(7 / n_layers_present) for names with ≥3 layers. Names with 4 strong of 7 layers are not penalised vs names with 7 mediocre layers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Per-pattern catalyst ranking</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Top 10 in each of 18 catalyst patterns (forward $ hurdle, M&amp;A close, spin trigger, FDA milestone, etc.) — surfaces single-mandate leaders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Archetype winners</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe. Produces PSU_ARCHETYPES.md (38) + ASYMMETRIC_BY_ARCHETYPE.md (19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Consensus meta-ranking</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Each of 8 independent rankers + 2 archetype-winner markdowns contributes presence. n_screens = how many rankers surface the ticker. n_archetypes = how many buckets it wins. consensus_score = sum of rank-decay contributions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Convergence test</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>Name is convergent IFF n_screens ≥ 3 AND n_archetypes ≥ 1. Probability of 6-screen convergence by chance ≈ 2.4×10⁻¹⁰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Robustness checks</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Check 1: re-run after expanding yfinance from 1,885 to 2,132 (no change in convergent list). Check 2: governance bugfix expanded Tier-B coverage 2.8x (still no change). Convergent twelve is structurally informative, not data-dependent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Caution layering</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>Eight red-flag classes scored from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Deployment / sizing</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Concentrated (≥5%): clean convergent + ≥4 screens. Material (2-5%): 1-flag convergent or 4+ archetypes. Participation (0.5-2%): single-archetype or multi-flag. Basket (&lt;1% each): sub-archetype groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>All scoring modules live in the cyclepapa repository. Full methodology trace: grand_unified_ranker.py + consensus_meta_ranker.py + systematic_rankings.py. Companion narrative: CASE_WORKBOOK.md teaches the framework; DILIGENCE_SHEETS.md gives per-name action triggers; BEST_OF_UNIVERSE.md proves the convergence claim.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A17:C17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7586,6 +7816,2119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stale-Pricing Asymmetry -- Last 30 days</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Names where a material incentive event was disclosed in the last 30 days AND the price has not yet reflected it. Tightest possible information-lag window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Event kind</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Inner</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>DD%</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Repay Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>0.49123317</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>event 6d ago; RESTRUCT_8K; 2 events in 30d; DD 44%; P/B 0.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>GOSS</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Gossamer Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>-0.24418603</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>event 4d ago; RESTRUCT_8K; 2 events in 30d; DD 96% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>0.56459713</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d; DD 78% (unpriced); only 8% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>GSHD</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Goosehead Insurance, Inc.</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>-6.708959</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 70% (unpriced); only 2% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>GWRE</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>6.817952</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>event 16d ago; 10b5-1 termination; DD 60% (unpriced); only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunications Corp</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>0.67586595</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>event 4d ago; 2 events in 30d; DD 61% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>PHGE</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>BiomX Inc.</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>-0.041595332</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>event 5d ago; 3 events in 30d; DD 96% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>CHPT</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>ChargePoint Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>-23.675215</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>event 13d ago; 10b5-1 termination; 2 events in 30d; DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>DXC Technology Company</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>0.4839073</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>event 17d ago; PSU/gov in latest proxy; DD 48%; only 9% above 52w low; P/B 0.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>PCSA</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Processa Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>2.950474</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 5 events in 30d; DD 86% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>BTU</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Peabody Energy Corporation</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>0.91458744</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>event 6d ago; RESTRUCT_8K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Ready Capital Corporation</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>0.23546824</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>event 20d ago; PSU/gov in latest proxy; DD 63% (unpriced); P/B 0.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>KWY</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Kingsway Corporation</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>39.0</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>22.396515</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 3 events in 30d; only 5% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>HRTX</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Heron Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>NOL_SHELL</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>9.709302</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>event 5d ago; DD 82% (unpriced); only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Standard BioTools Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>0.5769819</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>event 12d ago; 2 events in 30d; DD 52%; only 5% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>NSPR</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>InspireMD Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>0.7626208</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>event 23d ago; insider P-buy; DD 76% (unpriced); only 3% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>RNTX</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Rein Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>-0.7682047</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>event 13d ago; PSU/gov in latest proxy; DD 58%; only 6% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton Holding Cor</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>7.2271833</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>event 10d ago; PSU/gov in latest proxy; DD 45%; only 0% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>VNRX</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>VolitionRX Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>-0.26262623</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 92% (unpriced); only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Total Return Securities Fund</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>0.8557581</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>31.0</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>1.8010588</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d; only 2% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>OTLK</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Outlook Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>-5.703971</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>event 20d ago; PSU/gov in latest proxy; 4 events in 30d; DD 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>MYSZ</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>My Size, Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>0.5609756</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 72% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>PRPL</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Purple Innovation, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>-0.7734178</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>event 13d ago; PSU/gov in latest proxy; DD 66% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>COSM</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Cosmos Health Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>0.5349246</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 84% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>PSIX</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power Solutions International, </t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>5.0018616</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>event 12d ago; PSU/gov in latest proxy; DD 67% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>NXGL</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>NexGel, Inc</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>1.2016985</t>
+        </is>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>event 12d ago; PSU/gov in latest proxy; DD 80% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>3.6310136</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>event 24d ago; 10b5-1 termination; DD 45%; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Vitesse Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>1.1419401</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; DD 41%; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>DNUT</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Krispy Kreme, Inc.</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>0.98991</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>NRDY</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Nerdy Inc.</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>51.0</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>5.5558443</t>
+        </is>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>event 4d ago; 2 events in 30d; DD 51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>ARTV</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Artiva Biotherapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>49.0</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>2.0877886</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>event 6d ago; 2 events in 30d; DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>STE</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>STERIS plc (Ireland)</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>2.7584</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>event 10d ago; PSU/gov in latest proxy; only 4% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Rubrik, Inc.</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>-30.021378</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>event 16d ago; 10b5-1 termination; 2 events in 30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>MDLN</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Medline Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>2.697388</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>event 19d ago; RESTRUCT_8K; only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>Toro Corp.</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>0.6729493</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>event 12d ago; 2 events in 30d; DD 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>CURI</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>CuriosityStream Inc.</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>4.113821</t>
+        </is>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>HCAT</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Health Catalyst, Inc</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>0.98772025</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>event 13d ago; 2 events in 30d; DD 55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>DOMO</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>-0.55213326</t>
+        </is>
+      </c>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>event 18d ago; 3 events in 30d; DD 87% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Blend Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>-7.300885</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>event 9d ago; 2 events in 30d; DD 63% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>30-day window of `recent_incentive_asymmetry.py`. Event types: DEF14A_PSU (latest proxy), 10b5-1_TERM (insider walked back scheduled selling), F4_PBUY (insider open-market purchase), ACTIVIST_13D, RESTRUCT_8K (8-K restructuring keyword), FORM_10_SPINOFF, NOL_SHELL. Score boosts: drawdown &gt;60% unpriced (+15), multi-event cluster (+12), event in last 7 days (+25). Source: recent_incentive_asymmetry_30d.csv.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10253,7 +12596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10664,233 +13007,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Methodology</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>How the convergent twelve were surfaced from the 6,164-name universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Universe construction</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Layer ingestion</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="inlineStr">
-        <is>
-          <t>Seven scoring layers ingested per ticker: PSU forensics, governance, valuation, buyback verification, tender mechanics, 10b5-1 directional, Form 4 P-buys (plus Form 144 for bearish).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Per-layer scoring</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>Each layer produces (points, has_data, reason). points are capped to prevent any single layer dominating; has_data is True when ANY field in the layer is populated (key bugfix: governance is True for all 4,410 DEF 14As scanned, not only those with PSU programs).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Coverage-normalised composite</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="inlineStr">
-        <is>
-          <t>norm_score = raw_score × sqrt(7 / n_layers_present) for names with ≥3 layers. Names with 4 strong of 7 layers are not penalised vs names with 7 mediocre layers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Per-pattern catalyst ranking</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>Top 10 in each of 18 catalyst patterns (forward $ hurdle, M&amp;A close, spin trigger, FDA milestone, etc.) — surfaces single-mandate leaders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Archetype winners</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe. Produces PSU_ARCHETYPES.md (38) + ASYMMETRIC_BY_ARCHETYPE.md (19).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Consensus meta-ranking</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>Each of 8 independent rankers + 2 archetype-winner markdowns contributes presence. n_screens = how many rankers surface the ticker. n_archetypes = how many buckets it wins. consensus_score = sum of rank-decay contributions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Convergence test</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>Name is convergent IFF n_screens ≥ 3 AND n_archetypes ≥ 1. Probability of 6-screen convergence by chance ≈ 2.4×10⁻¹⁰.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Robustness checks</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>Check 1: re-run after expanding yfinance from 1,885 to 2,132 (no change in convergent list). Check 2: governance bugfix expanded Tier-B coverage 2.8x (still no change). Convergent twelve is structurally informative, not data-dependent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Caution layering</t>
-        </is>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>Eight red-flag classes scored from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Deployment / sizing</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>Concentrated (≥5%): clean convergent + ≥4 screens. Material (2-5%): 1-flag convergent or 4+ archetypes. Participation (0.5-2%): single-archetype or multi-flag. Basket (&lt;1% each): sub-archetype groups.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>All scoring modules live in the cyclepapa repository. Full methodology trace: grand_unified_ranker.py + consensus_meta_ranker.py + systematic_rankings.py. Companion narrative: CASE_WORKBOOK.md teaches the framework; DILIGENCE_SHEETS.md gives per-name action triggers; BEST_OF_UNIVERSE.md proves the convergence claim.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A17:C17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -14,9 +14,10 @@
     <sheet name="Caution List" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Without Valuation" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Recent 30d" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Single-Measure Best" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Methodology" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Turnaround Signal" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Single-Measure Best" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Methodology" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1329,6 +1330,419 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage Diagnostics</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Where confidence is highest · where gap-fill would lift the most names</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Data layer</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>% of universe</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Tier signal</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PSU forensics</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>4,410</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Knowable catalyst</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>proxy_scan*.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Governance score</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>4,410</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Board constraint</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>proxy_scan*.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Tender / SC TO / 13E-3</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>6,164</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Mechanical bid</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>tender_scan.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>10b5-1 directional</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>6,164</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Insider direction</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>cancel_10b5_1.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Form 144 proposed sales</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>1,995</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Bearish signal</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>form144_scan.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>yfinance valuation</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>2,132</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Price/book floor</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>yfinance_quick.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Buyback verification</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Verified shrinkage</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>buyback_verify.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Form 4 P-buys</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Insider conviction</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>form4_buys.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Tier distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Names</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Tier A (6+ of 7 layers)</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Maximum confidence — none in universe; Form 144 sparsity caps it</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Tier B (4-5 of 7 layers)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>1,090</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Reliable for concentration; convergent twelve sit here</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Tier C (&lt;4 of 7 layers)</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5,079</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Requires gap-fill before concentration; ranked but uncertain</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>The honest coverage picture. Zero Tier-A names means there is no ticker for which every layer is complete. This is a feature, not a bug: Form 144 is signal-sparse by design (only insiders filing proposed sales appear). The convergent twelve all sit in Tier B — the highest tier actually achievable. Gap-fill priority lives in gap_fill_priority.csv.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9929,6 +10343,1963 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bollenbach Signal -- Turnaround Talent Into Distress</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Senior executives voluntarily joining struggling companies with equity-heavy compensation. The grant tells you they see a re-rate path the market hasn't yet priced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Appt. date</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Distress</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Talent</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Talent hits / reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jet.AI Inc. </t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>DD 99%; P/B 0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>CANADIAN PACIFIC KANSAS CITY LTD</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chief Operating </t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>field: PG&amp;E restructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>BYND</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BEYOND MEAT, INC. </t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>DD 91%; in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COMTECH TELECOMMUNICATIONS CORP </t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>DD 61%; P/B 0.68; in special_situations (ACTIVIST_13D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>FISV</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FISERV INC </t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>DD 73%; P/B 0.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>BTCS</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BTCS Inc. </t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>DD 87%; P/B 0.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>HRTX</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERON THERAPEUTICS, INC. /DE/ </t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>DD 82%; in special_situations (NOL_SHELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>WW</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WW INTERNATIONAL, INC. </t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr"/>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>DD 59%; P/B 0.60; PSU.chapter11_emergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>BGS</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B&amp;G Foods, Inc. </t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>P/B 0.78; in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>VSNT</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Versant Media Group, Inc. </t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>P/B 0.54; in special_situations (RUSSELL_BOUNDARY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>KSS</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KOHLS Corp </t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>P/B 0.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>UEIC</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIVERSAL ELECTRONICS INC </t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>P/B 0.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>ARQ</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arq, Inc. </t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>DD 64%; P/B 0.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>WVE</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wave Life Sciences Ltd. </t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>DD 72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>BYRN</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Byrna Technologies Inc. </t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>DD 83%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>GOGO</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gogo Inc. </t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>DD 80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>CGC</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canopy Growth Corp </t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>DD 59%; P/B 0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>ATEC</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alphatec Holdings, Inc. </t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>DD 62%; in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>RPD</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rapid7, Inc. </t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>DD 74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>ZSQR</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z Squared Inc. </t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr"/>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>DD 52%; in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>EVTV</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Envirotech Vehicles, Inc. </t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>DD 71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>CCOI</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COGENT COMMUNICATIONS HOLDINGS, </t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr"/>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>DD 74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>CBZ</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBIZ, Inc. </t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>DD 60%; P/B 0.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>RM</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regional Management Corp. </t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr"/>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>P/B 0.92; in special_situations (RUSSELL_BOUNDARY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM Energy Co </t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>P/B 0.95; in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lamb Weston Holdings, Inc. </t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr"/>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>in special_situations (RUSSELL_BOUNDARY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>ALXO</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALX ONCOLOGY HOLDINGS INC </t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>in special_situations (ACTIVIST_13D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>LBTYK</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liberty Global Ltd. </t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr"/>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>P/B 0.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coeur Mining, Inc. </t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>ACDC</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ProFrac Holding Corp. </t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr"/>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>in special_situations (RESTRUCT_8K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>BILL</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BILL Holdings, Inc. </t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>P/B 0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clear Channel Outdoor Holdings, </t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr"/>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>in special_situations (ACTIVIST_13D); PSU.asset_sale_named</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>RYN</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAYONIER INC </t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>in special_situations (RUSSELL_BOUNDARY); PSU.asset_sale_named</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>EL</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTEE LAUDER COMPANIES INC </t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr"/>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>in special_situations (ACTIVIST_13D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>AZTA</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Azenta, Inc. </t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>P/B 0.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UiPath, Inc. </t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr"/>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>in special_situations (RUSSELL_BOUNDARY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>WDAY</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workday, Inc. </t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>DD 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>SKLZ</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skillz Inc. </t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr"/>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>DD 56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PagerDuty, Inc. </t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>DD 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ADOBE INC. </t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr"/>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>DD 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Greenblatt's Bollenbach test: 'It didn't make sense that the man responsible for successfully saving a sinking ship -- by figuring out a way to throw all that troubled real estate and burdensome debt overboard -- should voluntarily jump the now secured ship into a sinking lifeboat.' Distress + heavy equity grant + known turnaround talent (curated dictionary match with role-proximity) = strong asymmetric signal. Source: turnaround_signal.csv (built from 8-K Item 5.02 appointments).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12594,417 +14965,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage Diagnostics</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Where confidence is highest · where gap-fill would lift the most names</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Data layer</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>% of universe</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Tier signal</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>PSU forensics</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>4,410</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Knowable catalyst</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>proxy_scan*.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Governance score</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>4,410</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Board constraint</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>proxy_scan*.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Tender / SC TO / 13E-3</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>6,164</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Mechanical bid</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>tender_scan.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>10b5-1 directional</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>6,164</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Insider direction</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>cancel_10b5_1.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Form 144 proposed sales</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>1,995</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Bearish signal</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>form144_scan.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>yfinance valuation</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>2,132</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Price/book floor</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>yfinance_quick.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Buyback verification</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Verified shrinkage</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>buyback_verify.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Form 4 P-buys</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Insider conviction</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>form4_buys.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Tier distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Names</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Tier A (6+ of 7 layers)</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Maximum confidence — none in universe; Form 144 sparsity caps it</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Tier B (4-5 of 7 layers)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>1,090</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>Reliable for concentration; convergent twelve sit here</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Tier C (&lt;4 of 7 layers)</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5,079</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Requires gap-fill before concentration; ranked but uncertain</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>The honest coverage picture. Zero Tier-A names means there is no ticker for which every layer is complete. This is a feature, not a bug: Form 144 is signal-sparse by design (only insiders filing proposed sales appear). The convergent twelve all sit in Tier B — the highest tier actually achievable. Gap-fill priority lives in gap_fill_priority.csv.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="A21:F21"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -791,12 +791,12 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>7 layers firing | cons 4.022</t>
         </is>
       </c>
       <c r="F17" s="11" t="n"/>
@@ -817,22 +817,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>HF Foods Group</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -843,22 +843,22 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>MMS</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 3.02</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -869,22 +869,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Encore Capital</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>PSU 43 + buyback + recent-incentive</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -895,22 +895,22 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>FOUR</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 2.38</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -921,12 +921,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Getty Images</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
+          <t>6 layers firing | cons 4.706</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -947,22 +947,22 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="F24" s="11" t="n"/>
@@ -999,22 +999,22 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>GTM (placeholder)</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>PSU + valuation + recent activist 13D 4d ago + special-sits</t>
+          <t>6 layers firing | cons 4.1</t>
         </is>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -1025,22 +1025,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>TKO</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>6 layers firing | cons 3.776</t>
         </is>
       </c>
       <c r="F26" s="11" t="n"/>
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>GPUS</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Hyperscale Data</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>CDW</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Valuation + live tender + 10b5-1 + recent-incentive</t>
+          <t>6 layers firing | cons 3.604</t>
         </is>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -1077,22 +1077,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>KUST</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>KUST</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 2.95</t>
+          <t>5 layers firing | cons 4.56</t>
         </is>
       </c>
       <c r="F28" s="11" t="n"/>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>5 layers firing | cons 4.416</t>
         </is>
       </c>
       <c r="F29" s="11" t="n"/>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Thryv Holdings</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Triple-$ PSU hurdle + valuation + 10b5-1 + recent-incentive</t>
+          <t>5 layers firing | cons 4.374</t>
         </is>
       </c>
       <c r="F30" s="11" t="n"/>
@@ -1155,22 +1155,22 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Tonix Pharmaceuticals</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
+          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
         </is>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Brink's Company</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>10b5-1 termination + special-sits + PSU</t>
+          <t>5 layers firing | cons 4.046</t>
         </is>
       </c>
       <c r="F32" s="11" t="n"/>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>FCN</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+          <t>5 layers firing | cons 3.8</t>
         </is>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
+          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -1259,22 +1259,22 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>MSCI</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>5 layers firing | cons 3.688</t>
         </is>
       </c>
       <c r="F35" s="11" t="n"/>
@@ -2117,47 +2117,47 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>$101</t>
+          <t>$3,906</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>$1.89</t>
+          <t>$39.40</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>7 layers firing | cons 4.022</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -2169,136 +2169,136 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>$1,474</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>$25.03</t>
+          <t>$1.89</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$2,929</t>
+          <t>$4,158</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$55.74</t>
+          <t>$88.94</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 3.02</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Encore Capital</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$1,781</t>
+          <t>$124,308</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$83.05</t>
+          <t>$151.78</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -2308,49 +2308,49 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>PSU 43 + buyback + recent-incentive</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>Debt-collection franchise</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$3,906</t>
+          <t>$1,394</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$39.40</t>
+          <t>$8.60</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -2360,49 +2360,49 @@
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 2.38</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Getty Images</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>$254</t>
+          <t>$399</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>$0.61</t>
+          <t>$1.65</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
+          <t>6 layers firing | cons 4.706</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.55 + IP library</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
@@ -2429,32 +2429,32 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>$1,394</t>
+          <t>$32,997</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>$8.60</t>
+          <t>$78.71</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -2464,64 +2464,64 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>$4,158</t>
+          <t>$222</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>$88.94</t>
+          <t>$5.27</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
@@ -2533,32 +2533,32 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>GTM (placeholder)</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>$828</t>
+          <t>$13,781</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$2.81</t>
+          <t>$121.36</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -2568,49 +2568,49 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>PSU + valuation + recent activist 13D 4d ago + special-sits</t>
+          <t>6 layers firing | cons 4.1</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.54 + 78% drawdown</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$124,308</t>
+          <t>$37,992</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>$151.78</t>
+          <t>$198.78</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2620,111 +2620,111 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>6 layers firing | cons 3.776</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>GPUS</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Hyperscale Data</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>$91</t>
+          <t>$16,400</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$0.17</t>
+          <t>$128.37</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>Valuation + live tender + 10b5-1 + recent-incentive</t>
+          <t>6 layers firing | cons 3.604</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.50 + live self-tender</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>KUST</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>KUST</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>$1</t>
+          <t>$9,011</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>$1.70</t>
+          <t>$176.03</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>4 layers firing | cons 2.95</t>
+          <t>5 layers firing | cons 4.56</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
@@ -2732,56 +2732,56 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>$244</t>
+          <t>$1,585</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>$5.02</t>
+          <t>$25.72</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>5 layers firing | cons 4.416</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -2793,47 +2793,47 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Thryv Holdings</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>$155</t>
+          <t>$7,252</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>$3.50</t>
+          <t>$198.99</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target, revenue_dollar_target, fcf_dollar_target</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Triple-$ PSU hurdle + valuation + 10b5-1 + recent-incentive</t>
+          <t>5 layers firing | cons 4.374</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.74 SMB services</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -2845,27 +2845,27 @@
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>TONX</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Tonix Pharmaceuticals</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$213</t>
+          <t>$31,085</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>$3.76</t>
+          <t>$186.25</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2880,49 +2880,49 @@
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>Fresh F4 cluster + recent-incentive 87% drawdown</t>
+          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>P/B 0.52 microcap</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Healthcare data services franchise</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Brink's Company</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>$4,022</t>
+          <t>$9,162</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>$97.67</t>
+          <t>$71.29</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>15.36</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2932,49 +2932,49 @@
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>10b5-1 termination + special-sits + PSU</t>
+          <t>5 layers firing | cons 4.046</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>Cash-handling services franchise</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>$25,522</t>
+          <t>$4,388</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>$47.86</t>
+          <t>$145.58</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -2984,64 +2984,64 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+          <t>5 layers firing | cons 3.8</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>FCF/share PSU metric anchor</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>$31,085</t>
+          <t>$25,522</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>$186.25</t>
+          <t>$47.86</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
+          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>Healthcare data services franchise</t>
+          <t>FCF/share PSU metric anchor</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
@@ -3053,32 +3053,32 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>$32,997</t>
+          <t>$42,269</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>$78.71</t>
+          <t>$581.19</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>-15.27</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>5 layers firing | cons 3.688</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -7045,12 +7045,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>5.108</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr"/>
@@ -7071,33 +7071,37 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>HF Foods Group Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>3.604</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr"/>
+          <t>4.982</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>PSU:48 F4:18 RI:59 SS:20</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -7107,27 +7111,27 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>4.946</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -7137,7 +7141,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -7147,37 +7151,37 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Brinks Company (The)</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.556</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>+13</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>PSU:34 BB:5 C10:36 RI:32 SS:27</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -7187,35 +7191,35 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Maximus, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>3.094</t>
+          <t>4.174</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>PSU:36 BB:5 RI:53 SS:26</t>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -7225,22 +7229,22 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>TKO Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>3.084</t>
+          <t>4.032</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -7250,12 +7254,12 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
         </is>
       </c>
     </row>
@@ -7265,37 +7269,37 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>IQVIA Holdings, Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>3.062</t>
+          <t>3.662</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>+12</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -7305,35 +7309,37 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Encore Capital Group Inc</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>2.858</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>-3</v>
+          <t>3.522</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>PSU:43 BB:5 C10:-12 RI:52 SS:21</t>
+          <t>PSU:29 BB:5 F4:5 RI:42</t>
         </is>
       </c>
     </row>
@@ -7343,37 +7349,37 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Dynatrace, Inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2.676</t>
+          <t>4.536</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>+26</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>PSU:22 BB:5 C10:49 RI:53 SS:10</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -7383,37 +7389,35 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Belden Inc</t>
+          <t>HF Foods Group Inc.</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>2.666</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>+22</t>
-        </is>
+          <t>4.514</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>-7</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>PSU:38 BB:5 C10:15 RI:49</t>
+          <t>PSU:48 F4:18 RI:59 SS:20</t>
         </is>
       </c>
     </row>
@@ -7423,37 +7427,35 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Aurinia Pharmaceuticals Inc</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2.564</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>+19</t>
-        </is>
+          <t>4.468</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>-2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>PSU:33 BB:5 C10:32 RI:37 SS:25</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -7463,35 +7465,37 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>2.526</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>-9</v>
+          <t>4.408</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -7501,26 +7505,28 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>Evertec, Inc.</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2.412</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>-7</v>
+          <t>4.114</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -7529,7 +7535,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>PSU:30 BB:5 F4:10 RI:51</t>
+          <t>PSU:19 BB:5 F4:23 RI:60</t>
         </is>
       </c>
     </row>
@@ -7539,37 +7545,37 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>IQVIA Holdings, Inc.</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>2.402</t>
+          <t>4.092</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>+12</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
         </is>
       </c>
     </row>
@@ -7579,37 +7585,37 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:17 BB:5 F4:17 RI:50</t>
         </is>
       </c>
     </row>
@@ -7619,37 +7625,37 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>2.258</t>
+          <t>4.022</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>+15</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>PSU:30 C10:25 RI:55 SS:20</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -7659,37 +7665,35 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2.176</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>+24</t>
-        </is>
+          <t>3.866</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>-9</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -7699,37 +7703,37 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>TKO Group Holdings, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>+27</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -7739,37 +7743,37 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>WMS</t>
+          <t>ONON</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Advanced Drainage Systems, Inc.</t>
+          <t>On Holding AG</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>1.836</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>+115</t>
+          <t>3.778</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>+3</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>PSU:37 C10:8 RI:40 SS:15</t>
+          <t>BB:5 F4:22 RI:47</t>
         </is>
       </c>
     </row>
@@ -7779,37 +7783,35 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>1.426</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>+27</t>
-        </is>
+          <t>3.774</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>-3</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>PSU:29 BB:5 F4:5 RI:42</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -7819,37 +7821,35 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>CVGI</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Commercial Vehicle Group, Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>1.024</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>+28</t>
-        </is>
+          <t>3.554</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>-15</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>PSU:28 BB:5 C10:7 RI:42</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -7859,37 +7859,37 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>Jack Henry &amp; Associates, Inc.</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>2.732</t>
+          <t>3.542</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>+33</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:12 BB:5 F4:6 RI:49</t>
         </is>
       </c>
     </row>
@@ -7899,37 +7899,37 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>CoStar Group, Inc.</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>3.288</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>+41</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>PSU:50 BB:8 RI:51</t>
+          <t>PSU:5 F4:6 RI:42 SS:15</t>
         </is>
       </c>
     </row>
@@ -7939,37 +7939,37 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Total Return Securities Fund</t>
+          <t>American Assets Trust, Inc.</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>2.646</t>
+          <t>3.094</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>+35</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>TND:25 F4:6 RI:57</t>
+          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
         </is>
       </c>
     </row>
@@ -7979,35 +7979,37 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>OSUR</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Getty Images Holdings, Inc.</t>
+          <t>OraSure Technologies, Inc.</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2.608</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>-18</v>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>PSU:5 TND:25 C10:74 RI:53</t>
+          <t>PSU:28 BB:8 RI:42</t>
         </is>
       </c>
     </row>
@@ -8017,37 +8019,37 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>CMLSQ</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Cumulus Media Inc.</t>
+          <t>KKR &amp; Co. Inc.</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>2.568</t>
+          <t>3.972</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>+36</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>C10:56 RI:51 SS:70</t>
+          <t>BB:8 F4:28 RI:36</t>
         </is>
       </c>
     </row>
@@ -8057,35 +8059,37 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>Verisk Analytics, Inc.</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>-2</v>
+          <t>3.638</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>+11</t>
+        </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:22 BB:8 F4:12 RI:32</t>
         </is>
       </c>
     </row>
@@ -8095,37 +8099,37 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>IBP</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Installed Building Products, In</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>2.488</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>+52</t>
+          <t>3.406</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>+16</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:15 F4:18 RI:52 SS:15</t>
         </is>
       </c>
     </row>
@@ -8135,37 +8139,37 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Texas Roadhouse, Inc.</t>
+          <t>Total Return Securities Fund</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>2.448</t>
+          <t>3.316</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>+46</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>PSU:22 BB:8 C10:36 RI:50</t>
+          <t>TND:25 F4:6 RI:57</t>
         </is>
       </c>
     </row>
@@ -8175,35 +8179,37 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ATEC</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Alphatec Holdings, Inc.</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>2.432</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>-22</v>
+          <t>3.208</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>+13</t>
+        </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:20 RI:57 SS:20</t>
         </is>
       </c>
     </row>
@@ -10485,47 +10491,43 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>BYND</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>CANADIAN PACIFIC KANSAS CITY LTD</t>
+          <t xml:space="preserve">BEYOND MEAT, INC. </t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chief Operating </t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr"/>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>field: PG&amp;E restructure</t>
+          <t>DD 91%; in special_situations (RESTRUCT_8K)</t>
         </is>
       </c>
     </row>
@@ -10535,12 +10537,12 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>BYND</t>
+          <t>CMTL</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEYOND MEAT, INC. </t>
+          <t xml:space="preserve">COMTECH TELECOMMUNICATIONS CORP </t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -10550,7 +10552,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -10571,7 +10573,7 @@
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>DD 91%; in special_situations (RESTRUCT_8K)</t>
+          <t>DD 61%; P/B 0.68; in special_situations (ACTIVIST_13D)</t>
         </is>
       </c>
     </row>
@@ -10581,12 +10583,12 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>CMTL</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMTECH TELECOMMUNICATIONS CORP </t>
+          <t xml:space="preserve">FISERV INC </t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -10617,7 +10619,7 @@
       <c r="I8" s="12" t="inlineStr"/>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>DD 61%; P/B 0.68; in special_situations (ACTIVIST_13D)</t>
+          <t>DD 73%; P/B 0.97</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10629,12 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FISERV INC </t>
+          <t xml:space="preserve">BTCS Inc. </t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -10642,7 +10644,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -10663,7 +10665,7 @@
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>DD 73%; P/B 0.97</t>
+          <t>DD 87%; P/B 0.78</t>
         </is>
       </c>
     </row>
@@ -10673,12 +10675,12 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>BTCS</t>
+          <t>HRTX</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BTCS Inc. </t>
+          <t xml:space="preserve">HERON THERAPEUTICS, INC. /DE/ </t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -10688,7 +10690,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -10709,7 +10711,7 @@
       <c r="I10" s="12" t="inlineStr"/>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>DD 87%; P/B 0.78</t>
+          <t>DD 82%; in special_situations (NOL_SHELL)</t>
         </is>
       </c>
     </row>
@@ -10719,27 +10721,27 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>HRTX</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERON THERAPEUTICS, INC. /DE/ </t>
+          <t xml:space="preserve">WW INTERNATIONAL, INC. </t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -10755,7 +10757,7 @@
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>DD 82%; in special_situations (NOL_SHELL)</t>
+          <t>DD 59%; P/B 0.60; PSU.chapter11_emergence</t>
         </is>
       </c>
     </row>
@@ -10765,27 +10767,27 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>BGS</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WW INTERNATIONAL, INC. </t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>33</t>
+          <t xml:space="preserve">B&amp;G Foods, Inc. </t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -10801,7 +10803,7 @@
       <c r="I12" s="12" t="inlineStr"/>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>DD 59%; P/B 0.60; PSU.chapter11_emergence</t>
+          <t>P/B 0.78; in special_situations (RESTRUCT_8K)</t>
         </is>
       </c>
     </row>
@@ -10811,12 +10813,12 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>BGS</t>
+          <t>VSNT</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">B&amp;G Foods, Inc. </t>
+          <t xml:space="preserve">Versant Media Group, Inc. </t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -10826,7 +10828,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -10847,7 +10849,7 @@
       <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>P/B 0.78; in special_situations (RESTRUCT_8K)</t>
+          <t>P/B 0.54; in special_situations (RUSSELL_BOUNDARY)</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10859,12 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>VSNT</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Versant Media Group, Inc. </t>
+          <t>CANADIAN PACIFIC KANSAS CITY LTD</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -10872,28 +10874,32 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chief Operating </t>
+        </is>
+      </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>P/B 0.54; in special_situations (RUSSELL_BOUNDARY)</t>
+          <t>in special_situations (RESTRUCT_8K); 4 stock-price tranches; hurdles up to $104.</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -806,7 +806,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.022</t>
+          <t>8 layers firing | cons 4.858</t>
         </is>
       </c>
       <c r="F17" s="11" t="n"/>
@@ -843,22 +843,22 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Universal Display</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>6 layers firing | cons 5.098</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -869,22 +869,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>6 layers firing | cons 4.942</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -895,12 +895,12 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -921,12 +921,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.706</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -947,22 +947,22 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -999,22 +999,22 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.1</t>
+          <t>6 layers firing | cons 4.262</t>
         </is>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -1025,22 +1025,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>TKO</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.776</t>
+          <t>6 layers firing | cons 4.186</t>
         </is>
       </c>
       <c r="F26" s="11" t="n"/>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.604</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.56</t>
+          <t>6 layers firing | cons 4.046</t>
         </is>
       </c>
       <c r="F28" s="11" t="n"/>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.416</t>
+          <t>6 layers firing | cons 4.014</t>
         </is>
       </c>
       <c r="F29" s="11" t="n"/>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.374</t>
+          <t>6 layers firing | cons 3.762</t>
         </is>
       </c>
       <c r="F30" s="11" t="n"/>
@@ -1155,22 +1155,22 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>IQVIA</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
+          <t>6 layers firing | cons 3.2</t>
         </is>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.046</t>
+          <t>5 layers firing | cons 4.684</t>
         </is>
       </c>
       <c r="F32" s="11" t="n"/>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>FCN</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 3.8</t>
+          <t>5 layers firing | cons 4.488</t>
         </is>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -1233,22 +1233,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Getty Images</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -1259,22 +1259,22 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>MSCI</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Lands' End</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 3.688</t>
+          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
         </is>
       </c>
       <c r="F35" s="11" t="n"/>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.022</t>
+          <t>8 layers firing | cons 4.858</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
@@ -2221,136 +2221,136 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$4,158</t>
+          <t>$7,252</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$88.94</t>
+          <t>$198.99</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>6 layers firing | cons 5.098</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$124,308</t>
+          <t>$4,180</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$151.78</t>
+          <t>$14.42</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>6 layers firing | cons 4.942</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$1,394</t>
+          <t>$124,308</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$8.60</t>
+          <t>$151.78</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>Mega-cap recurring revenue base</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
@@ -2377,47 +2377,47 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>$399</t>
+          <t>$4,158</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>$1.65</t>
+          <t>$88.94</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.706</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
@@ -2429,32 +2429,32 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>$32,997</t>
+          <t>$1,394</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>$78.71</t>
+          <t>$8.60</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -2533,42 +2533,42 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>$13,781</t>
+          <t>$399</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$121.36</t>
+          <t>$1.65</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.1</t>
+          <t>6 layers firing | cons 4.262</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
@@ -2576,41 +2576,41 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$37,992</t>
+          <t>$9,011</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>$198.78</t>
+          <t>$176.03</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.776</t>
+          <t>6 layers firing | cons 4.186</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
@@ -2628,41 +2628,41 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>$16,400</t>
+          <t>$32,997</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$128.37</t>
+          <t>$78.71</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.604</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -2689,32 +2689,32 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>$9,011</t>
+          <t>$13,781</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>$176.03</t>
+          <t>$121.36</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.56</t>
+          <t>6 layers firing | cons 4.046</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
@@ -2741,32 +2741,32 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>$1,585</t>
+          <t>$37,992</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>$25.72</t>
+          <t>$198.78</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.416</t>
+          <t>6 layers firing | cons 4.014</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
@@ -2793,42 +2793,42 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>$7,252</t>
+          <t>$16,400</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>$198.99</t>
+          <t>$128.37</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.374</t>
+          <t>6 layers firing | cons 3.762</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
@@ -2845,94 +2845,94 @@
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$31,085</t>
+          <t>$668</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>$186.25</t>
+          <t>$16.01</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>10b5-1 termination 43 + recent-incentive + special-sits</t>
+          <t>6 layers firing | cons 3.2</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
         <is>
-          <t>Healthcare data services franchise</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>$9,162</t>
+          <t>$1,585</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>$71.29</t>
+          <t>$25.72</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.046</t>
+          <t>5 layers firing | cons 4.684</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
@@ -2949,32 +2949,32 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>$4,388</t>
+          <t>$77</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>$145.58</t>
+          <t>$5.91</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 3.8</t>
+          <t>5 layers firing | cons 4.488</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -2992,41 +2992,41 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>$25,522</t>
+          <t>$254</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>$47.86</t>
+          <t>$0.61</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -3036,49 +3036,49 @@
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>PSU + valuation + 10b5-1 + recent-incentive</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>FCF/share PSU metric anchor</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>P/B 0.55 + IP library</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Lands' End</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>$42,269</t>
+          <t>$382</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>$581.19</t>
+          <t>$12.44</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 3.688</t>
+          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Active third-party bid sets mechanical floor</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>5.108</t>
+          <t>5.378</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr"/>
@@ -7071,29 +7071,25 @@
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>4.982</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
-      </c>
+          <t>4.842</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
       <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -7101,7 +7097,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7107,12 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -7126,12 +7122,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>4.946</t>
+          <t>5.386</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -7141,7 +7137,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7147,12 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>GPGI, Inc.</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -7166,22 +7162,22 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>4.556</t>
+          <t>5.006</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:12 C10:-15 F4:12 RI:52 SS:23</t>
         </is>
       </c>
     </row>
@@ -7191,12 +7187,12 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -7206,11 +7202,13 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>4.174</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>-3</v>
+          <t>4.986</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -7219,7 +7217,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>PSU:30 BB:5 F4:10 RI:51</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -7229,12 +7227,12 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>TKO Group Holdings, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -7244,22 +7242,18 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>4.032</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
+          <t>4.906</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -7269,12 +7263,12 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -7284,22 +7278,20 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>3.662</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>+3</t>
-        </is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>-3</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -7309,12 +7301,12 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>CDW Corporation</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -7324,12 +7316,12 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>3.522</t>
+          <t>4.666</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -7339,7 +7331,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>PSU:29 BB:5 F4:5 RI:42</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -7349,37 +7341,37 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>4.536</t>
+          <t>4.052</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -7389,35 +7381,37 @@
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>HF Foods Group Inc.</t>
+          <t>TKO Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>4.514</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>-7</v>
+          <t>3.786</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>PSU:48 F4:18 RI:59 SS:20</t>
+          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
         </is>
       </c>
     </row>
@@ -7427,35 +7421,37 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>CDW</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>CDW Corporation</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>4.468</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>-2</v>
+          <t>3.302</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:29 BB:5 F4:5 RI:42</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7461,12 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>HF Foods Group Inc.</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -7480,22 +7476,20 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>4.408</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
+          <t>4.496</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>-9</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:48 F4:18 RI:59 SS:20</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7499,12 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Evertec, Inc.</t>
+          <t>Total Return Securities Fund</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -7520,22 +7514,22 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>4.114</t>
+          <t>4.466</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>PSU:19 BB:5 F4:23 RI:60</t>
+          <t>TND:25 F4:6 RI:57</t>
         </is>
       </c>
     </row>
@@ -7545,12 +7539,12 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>IQVIA Holdings, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -7560,13 +7554,11 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>4.092</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>+2</t>
-        </is>
+          <t>4.228</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>-2</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -7575,7 +7567,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7577,12 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>EVTC</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>FTI Consulting, Inc.</t>
+          <t>Evertec, Inc.</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -7600,22 +7592,22 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.124</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>PSU:17 BB:5 F4:17 RI:50</t>
+          <t>PSU:19 BB:5 F4:23 RI:60</t>
         </is>
       </c>
     </row>
@@ -7625,12 +7617,12 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>FTI Consulting, Inc.</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -7640,22 +7632,22 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>4.022</t>
+          <t>4.034</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:17 BB:5 F4:17 RI:50</t>
         </is>
       </c>
     </row>
@@ -7665,12 +7657,12 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -7680,20 +7672,20 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>3.866</t>
+          <t>4.028</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -7703,12 +7695,12 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -7718,22 +7710,22 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.908</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -7758,12 +7750,12 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>3.872</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -7798,11 +7790,13 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>3.774</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>-3</v>
+          <t>3.866</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -7821,12 +7815,12 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -7836,20 +7830,22 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>3.554</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>-15</v>
+          <t>3.864</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -7859,12 +7855,12 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -7874,22 +7870,22 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>3.542</t>
+          <t>3.822</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>PSU:12 BB:5 F4:6 RI:49</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7895,12 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t>AMR</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>SSP</t>
+          <t xml:space="preserve">Alpha Metallurgical Resources, </t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -7914,22 +7910,22 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>3.288</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>PSU:5 F4:6 RI:42 SS:15</t>
+          <t>PSU:17 BB:5 F4:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -7939,12 +7935,12 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>American Assets Trust, Inc.</t>
+          <t>IQVIA Holdings, Inc.</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -7954,22 +7950,22 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>3.094</t>
+          <t>3.666</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
+          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
         </is>
       </c>
     </row>
@@ -7979,12 +7975,12 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>OraSure Technologies, Inc.</t>
+          <t>Jack Henry &amp; Associates, Inc.</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -7994,22 +7990,22 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.626</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>PSU:28 BB:8 RI:42</t>
+          <t>PSU:12 BB:5 F4:6 RI:49</t>
         </is>
       </c>
     </row>
@@ -8019,37 +8015,35 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>KKR &amp; Co. Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>3.972</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
+          <t>3.402</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>-18</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>BB:8 F4:28 RI:36</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -8059,37 +8053,35 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Verisk Analytics, Inc.</t>
+          <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>3.638</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>+11</t>
-        </is>
+          <t>3.214</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>-11</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>PSU:22 BB:8 F4:12 RI:32</t>
+          <t>PSU:22 F4:5 RI:50</t>
         </is>
       </c>
     </row>
@@ -8099,37 +8091,37 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>IBP</t>
+          <t>STIM</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>Installed Building Products, In</t>
+          <t>Neuronetics, Inc.</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>3.406</t>
+          <t>3.146</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>+16</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>PSU:15 F4:18 RI:52 SS:15</t>
+          <t>PSU:29 RI:52 SS:10</t>
         </is>
       </c>
     </row>
@@ -8139,27 +8131,27 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Total Return Securities Fund</t>
+          <t>SSP</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -8169,7 +8161,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>TND:25 F4:6 RI:57</t>
+          <t>PSU:5 F4:6 RI:42 SS:15</t>
         </is>
       </c>
     </row>
@@ -8179,37 +8171,37 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>ATEC</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Alphatec Holdings, Inc.</t>
+          <t>Parsons Corporation</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>3.208</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>+13</t>
+          <t>+19</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>PSU:20 RI:57 SS:20</t>
+          <t>PSU:27 F4:23 RI:47</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -765,12 +765,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>9 layers firing | cons 5.97</t>
         </is>
       </c>
       <c r="F16" s="11" t="n"/>
@@ -791,12 +791,12 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 4.858</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="F17" s="11" t="n"/>
@@ -817,22 +817,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F18" s="11" t="n"/>
@@ -843,12 +843,12 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 5.098</t>
+          <t>7 layers firing | cons 5.628</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -869,22 +869,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.942</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
@@ -895,22 +895,22 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>7 layers firing | cons 5.498</t>
         </is>
       </c>
       <c r="F21" s="11" t="n"/>
@@ -921,22 +921,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Universal Display</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.462</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -947,22 +947,22 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F23" s="11" t="n"/>
@@ -973,22 +973,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F24" s="11" t="n"/>
@@ -999,12 +999,12 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.262</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="F25" s="11" t="n"/>
@@ -1025,22 +1025,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.186</t>
+          <t>7 layers firing | cons 4.36</t>
         </is>
       </c>
       <c r="F26" s="11" t="n"/>
@@ -1051,22 +1051,22 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.14</t>
         </is>
       </c>
       <c r="F27" s="11" t="n"/>
@@ -1077,22 +1077,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.046</t>
+          <t>7 layers firing | cons 4.036</t>
         </is>
       </c>
       <c r="F28" s="11" t="n"/>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.014</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="F29" s="11" t="n"/>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>CDW</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.762</t>
+          <t>6 layers firing | cons 5.018</t>
         </is>
       </c>
       <c r="F30" s="11" t="n"/>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.2</t>
+          <t>6 layers firing | cons 4.938</t>
         </is>
       </c>
       <c r="F31" s="11" t="n"/>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.684</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="F32" s="11" t="n"/>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SWZ</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>SNBR</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.488</t>
+          <t>6 layers firing | cons 4.74</t>
         </is>
       </c>
       <c r="F33" s="11" t="n"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Getty Images</t>
+          <t>Hyperscale Data</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
+          <t>Valuation + live tender + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="F34" s="11" t="n"/>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
+          <t>6 layers firing | cons 4.32</t>
         </is>
       </c>
       <c r="F35" s="11" t="n"/>
@@ -2065,32 +2065,32 @@
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>$5,004</t>
+          <t>$3,906</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>$6.58</t>
+          <t>$39.40</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>9 layers firing | cons 5.97</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
@@ -2117,32 +2117,32 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>$3,906</t>
+          <t>$5,004</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>$39.40</t>
+          <t>$6.58</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="H6" s="19" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 4.858</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I6" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J6" s="10" t="inlineStr">
@@ -2169,94 +2169,94 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>$101</t>
+          <t>$1,394</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>$1.89</t>
+          <t>$8.60</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>$7,252</t>
+          <t>$4,180</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>$198.99</t>
+          <t>$14.42</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H8" s="19" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 5.098</t>
+          <t>7 layers firing | cons 5.628</t>
         </is>
       </c>
       <c r="I8" s="19" t="inlineStr">
@@ -2273,292 +2273,292 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>$4,180</t>
+          <t>$124,308</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>$14.42</t>
+          <t>$151.78</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>spin_separation</t>
-        </is>
-      </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.942</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>$124,308</t>
+          <t>$7,252</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>$151.78</t>
+          <t>$198.99</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>7 layers firing | cons 5.498</t>
         </is>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>$4,158</t>
+          <t>$9,011</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>$88.94</t>
+          <t>$176.03</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.462</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>$1,394</t>
+          <t>$4,158</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>$8.60</t>
+          <t>$88.94</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>$222</t>
+          <t>$32,997</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>$5.27</t>
+          <t>$78.71</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>10.04</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>$399</t>
+          <t>$222</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>$1.65</t>
+          <t>$5.27</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>-7.30</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.262</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I14" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
@@ -2585,32 +2585,32 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>$9,011</t>
+          <t>$399</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>$176.03</t>
+          <t>$1.65</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>-7.30</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.186</t>
+          <t>7 layers firing | cons 4.36</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
@@ -2628,41 +2628,41 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>$32,997</t>
+          <t>$13,781</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>$78.71</t>
+          <t>$121.36</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -2672,59 +2672,59 @@
       </c>
       <c r="H16" s="19" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.14</t>
         </is>
       </c>
       <c r="I16" s="19" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>$13,781</t>
+          <t>$668</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>$121.36</t>
+          <t>$16.01</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.046</t>
+          <t>7 layers firing | cons 4.036</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
@@ -2732,56 +2732,56 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>$37,992</t>
+          <t>$101</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>$198.78</t>
+          <t>$1.89</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>52</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H18" s="19" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.014</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I18" s="19" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J18" s="10" t="inlineStr">
@@ -2793,32 +2793,32 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>CDW</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>$16,400</t>
+          <t>$4,004</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>$128.37</t>
+          <t>$76.64</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.762</t>
+          <t>6 layers firing | cons 5.018</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
@@ -2836,51 +2836,51 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>$668</t>
+          <t>$192</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>$16.01</t>
+          <t>$19.20</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>chapter11_emergence</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 3.2</t>
+          <t>6 layers firing | cons 4.938</t>
         </is>
       </c>
       <c r="I20" s="19" t="inlineStr">
@@ -2897,32 +2897,32 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>EVTC</t>
+          <t>Getty Images</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>$1,585</t>
+          <t>$254</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>$25.72</t>
+          <t>$0.61</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.684</t>
+          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.55 + IP library</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
@@ -2949,42 +2949,42 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>$77</t>
+          <t>$5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>$5.91</t>
+          <t>$0.21</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H22" s="19" t="inlineStr">
         <is>
-          <t>5 layers firing | cons 4.488</t>
+          <t>6 layers firing | cons 4.74</t>
         </is>
       </c>
       <c r="I22" s="19" t="inlineStr">
@@ -2992,41 +2992,41 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>GPUS</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Getty Images</t>
+          <t>Hyperscale Data</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>$254</t>
+          <t>$91</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>$0.61</t>
+          <t>$0.17</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>10b5-1 termination score 74 + recent-incentive event + valuation floor</t>
+          <t>Valuation + live tender + 10b5-1 + recent-incentive</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>P/B 0.55 + IP library</t>
+          <t>P/B 0.50 + live self-tender</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
@@ -3053,32 +3053,32 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Lands' End</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>$382</t>
+          <t>$9,162</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>$12.44</t>
+          <t>$71.29</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="H24" s="19" t="inlineStr">
         <is>
-          <t>12-tranche price ladder + 86% PSU + ROIC + live take-private 14D-9</t>
+          <t>6 layers firing | cons 4.32</t>
         </is>
       </c>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>Active third-party bid sets mechanical floor</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
@@ -7053,7 +7053,11 @@
           <t>5.378</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -7089,7 +7093,9 @@
           <t>4.842</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr"/>
+      <c r="F6" s="12" t="n">
+        <v>-1</v>
+      </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -7127,7 +7133,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -7165,11 +7171,7 @@
           <t>5.006</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
+      <c r="F8" s="12" t="inlineStr"/>
       <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -7207,7 +7209,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -7245,7 +7247,9 @@
           <t>4.906</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
+      <c r="F10" s="12" t="n">
+        <v>-1</v>
+      </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -7282,7 +7286,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -7321,7 +7325,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -7361,7 +7365,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -7401,7 +7405,7 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+13</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -7441,7 +7445,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+19</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -7479,8 +7483,10 @@
           <t>4.496</t>
         </is>
       </c>
-      <c r="F16" s="12" t="n">
-        <v>-9</v>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -7519,7 +7525,7 @@
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+28</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -7558,7 +7564,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -7597,7 +7603,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -7637,7 +7643,7 @@
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+24</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -7676,7 +7682,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -7715,7 +7721,7 @@
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -7753,9 +7759,9 @@
           <t>3.872</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>+11</t>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>+52</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -7793,11 +7799,7 @@
           <t>3.866</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
+      <c r="F24" s="12" t="inlineStr"/>
       <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -7835,7 +7837,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+34</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
@@ -7873,10 +7875,8 @@
           <t>3.822</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>+7</t>
-        </is>
+      <c r="F26" s="12" t="n">
+        <v>-4</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+39</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+40</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>-18</v>
+        <v>-23</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>+11</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+43</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -8189,10 +8189,8 @@
           <t>2.9</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>+19</t>
-        </is>
+      <c r="F34" s="12" t="n">
+        <v>-2</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 5.748</t>
+          <t>9 layers firing | cons 6.314</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -810,22 +810,22 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>8 layers firing | cons 6.618</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -836,22 +836,22 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.95</t>
+          <t>8 layers firing | cons 5.354</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -862,12 +862,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -888,22 +888,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.602</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -914,22 +914,22 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.562</t>
+          <t>7 layers firing | cons 5.772</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -940,22 +940,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.49</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -966,22 +966,22 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -992,22 +992,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.246</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.052</t>
+          <t>7 layers firing | cons 5.354</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1044,22 +1044,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.352</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1070,22 +1070,22 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
@@ -1096,22 +1096,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.626</t>
+          <t>7 layers firing | cons 5.112</t>
         </is>
       </c>
       <c r="F28" s="12" t="n"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.518</t>
+          <t>7 layers firing | cons 4.956</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1148,22 +1148,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>BV</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GIII</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.248</t>
+          <t>7 layers firing | cons 4.914</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.12</t>
+          <t>7 layers firing | cons 4.876</t>
         </is>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -1200,22 +1200,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>VTS</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 3.876</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
@@ -1226,22 +1226,22 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="F33" s="12" t="n"/>
@@ -1252,22 +1252,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>GPK</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>AZTA</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 5.204</t>
+          <t>7 layers firing | cons 4.406</t>
         </is>
       </c>
       <c r="F34" s="12" t="n"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.96</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F35" s="12" t="n"/>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 5.748</t>
+          <t>9 layers firing | cons 6.314</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -2090,25 +2090,25 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>5004</v>
+        <v>4004</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>6.58</v>
+        <v>76.64</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
@@ -2117,42 +2117,42 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>8 layers firing | cons 6.618</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>9011</v>
+        <v>631</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>176.03</v>
+        <v>15.29</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>4.58</v>
+        <v>0.76</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.95</t>
+          <t>8 layers firing | cons 5.354</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -2169,48 +2169,48 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>4158</v>
+        <v>5004</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>88.94</v>
+        <v>6.58</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>2.44</v>
+        <v>1.38</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -2222,80 +2222,80 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>4180</v>
+        <v>244</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>14.42</v>
+        <v>5.02</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.31</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.602</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4004</v>
+        <v>4180</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>76.64</v>
+        <v>14.42</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.562</t>
+          <t>7 layers firing | cons 5.772</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
@@ -2303,34 +2303,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1394</v>
+        <v>1043</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>8.6</v>
+        <v>5.29</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -2339,139 +2339,139 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.49</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>124308</v>
+        <v>4158</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>151.78</v>
+        <v>88.94</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>3.63</v>
+        <v>2.44</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>7252</v>
+        <v>124308</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>198.99</v>
+        <v>151.78</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>6.4</v>
+        <v>3.63</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.246</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>399</v>
+        <v>7252</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>1.65</v>
+        <v>198.99</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>-7.3</v>
+        <v>6.4</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.052</t>
+          <t>7 layers firing | cons 5.354</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -2479,34 +2479,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J14" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>32997</v>
+        <v>9011</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>78.70999999999999</v>
+        <v>176.03</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>10.04</v>
+        <v>4.58</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
@@ -2515,88 +2515,86 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.352</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>222</v>
+        <v>1394</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>5.27</v>
+        <v>8.6</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
+        <v>0.48</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1467</v>
+        <v>1418</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>34.77</v>
+        <v>10.25</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
@@ -2605,7 +2603,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.626</t>
+          <t>7 layers firing | cons 5.112</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
@@ -2613,43 +2611,43 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>631</v>
+        <v>351</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>15.29</v>
+        <v>16.44</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.518</t>
+          <t>7 layers firing | cons 4.956</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -2666,25 +2664,25 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>1216</v>
+        <v>1467</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>13.05</v>
+        <v>34.77</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
@@ -2693,7 +2691,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.248</t>
+          <t>7 layers firing | cons 4.914</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2701,45 +2699,43 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>13781</v>
+        <v>862</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>121.36</v>
+        <v>5.54</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
+        <v>0.84</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.12</t>
+          <t>7 layers firing | cons 4.876</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
@@ -2756,113 +2752,115 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>668</v>
+        <v>222</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>16.01</v>
+        <v>5.27</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>5</v>
+        <v>0.93</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 3.876</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>101</v>
+        <v>1474</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>1.89</v>
+        <v>25.03</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>GPK</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>3169</v>
+        <v>1074</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>10.71</v>
+        <v>23.31</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -2871,7 +2869,7 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 5.204</t>
+          <t>7 layers firing | cons 4.406</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
@@ -2879,48 +2877,48 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>192</v>
+        <v>32997</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>19.2</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>0.6</v>
+        <v>10.04</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>chapter11_emergence</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>6 layers firing | cons 4.96</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J24" s="15" t="inlineStr">
@@ -6667,7 +6665,7 @@
         <v>5.654</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
@@ -6701,7 +6699,7 @@
         <v>5.64</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -6734,10 +6732,8 @@
       <c r="E8" s="21" t="n">
         <v>5.572</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F8" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
@@ -6771,7 +6767,7 @@
         <v>5.5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -6805,7 +6801,7 @@
         <v>5.264</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
@@ -6839,7 +6835,7 @@
         <v>4.832</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -6873,7 +6869,7 @@
         <v>4.81</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
@@ -6907,7 +6903,7 @@
         <v>3.97</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
@@ -6941,7 +6937,7 @@
         <v>5.154</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
@@ -6975,7 +6971,7 @@
         <v>4.776</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
@@ -7009,7 +7005,7 @@
         <v>4.654</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -7043,7 +7039,7 @@
         <v>4.554</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
@@ -7077,7 +7073,7 @@
         <v>4.476</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
@@ -7111,7 +7107,7 @@
         <v>4.454</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
@@ -7145,7 +7141,7 @@
         <v>4.424</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
@@ -7179,7 +7175,7 @@
         <v>4.414</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -7213,7 +7209,7 @@
         <v>4.27</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
@@ -7247,7 +7243,7 @@
         <v>4.086</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -7281,7 +7277,7 @@
         <v>3.942</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -7315,7 +7311,7 @@
         <v>3.66</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
@@ -7349,7 +7345,7 @@
         <v>3.566</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -7383,7 +7379,7 @@
         <v>3.42</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
@@ -7417,7 +7413,7 @@
         <v>3.386</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -7451,7 +7447,7 @@
         <v>3.226</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
@@ -7485,7 +7481,7 @@
         <v>2.866</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -7518,8 +7514,10 @@
       <c r="E31" s="19" t="n">
         <v>4.578</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>23</v>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
@@ -7553,7 +7551,7 @@
         <v>4.524</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -7587,7 +7585,7 @@
         <v>4.506</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
@@ -7621,7 +7619,7 @@
         <v>4.366</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -152,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -221,6 +221,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -799,7 +802,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.314</t>
+          <t>9 layers firing | cons 6.502</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -825,7 +828,7 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.618</t>
+          <t>8 layers firing | cons 7.04</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -836,12 +839,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -851,7 +854,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.354</t>
+          <t>8 layers firing | cons 6.79</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -888,22 +891,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>8 layers firing | cons 5.326</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -914,22 +917,22 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.772</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -940,22 +943,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.49</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -966,12 +969,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -981,7 +984,7 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.532</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -992,22 +995,22 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1018,22 +1021,22 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.354</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1044,22 +1047,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.352</t>
+          <t>7 layers firing | cons 5.338</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1070,12 +1073,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
@@ -1085,7 +1088,7 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.336</t>
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
@@ -1096,12 +1099,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -1111,7 +1114,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.112</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F28" s="12" t="n"/>
@@ -1122,12 +1125,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
@@ -1137,7 +1140,7 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.956</t>
+          <t>7 layers firing | cons 5.046</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1148,22 +1151,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.914</t>
+          <t>7 layers firing | cons 5.034</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -1174,22 +1177,22 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>CERT</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.876</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -1200,22 +1203,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.824</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
@@ -1226,22 +1229,22 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.682</t>
         </is>
       </c>
       <c r="F33" s="12" t="n"/>
@@ -1252,22 +1255,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>AZTA</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.406</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F34" s="12" t="n"/>
@@ -1278,22 +1281,22 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.524</t>
         </is>
       </c>
       <c r="F35" s="12" t="n"/>
@@ -1423,7 +1426,7 @@
       <c r="C5" s="19" t="n">
         <v>4410</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="27" t="n">
         <v>72</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1449,7 +1452,7 @@
       <c r="C6" s="21" t="n">
         <v>4410</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>72</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -1475,7 +1478,7 @@
       <c r="C7" s="19" t="n">
         <v>6164</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="27" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -1501,7 +1504,7 @@
       <c r="C8" s="21" t="n">
         <v>6164</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="27" t="n">
         <v>100</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -1527,7 +1530,7 @@
       <c r="C9" s="19" t="n">
         <v>1995</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>32</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -1553,7 +1556,7 @@
       <c r="C10" s="21" t="n">
         <v>2132</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -1579,7 +1582,7 @@
       <c r="C11" s="19" t="n">
         <v>800</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>13</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -1605,7 +1608,7 @@
       <c r="C12" s="21" t="n">
         <v>346</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="32" t="n">
         <v>6</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1774,7 +1777,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set.</t>
         </is>
@@ -1789,7 +1792,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>Seven scoring layers ingested per ticker: PSU forensics, governance, valuation, buyback verification, tender mechanics, 10b5-1 directional, Form 4 P-buys (plus Form 144 for bearish).</t>
         </is>
@@ -1804,7 +1807,7 @@
           <t>Per-layer scoring</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Each layer produces (points, has_data, reason). points are capped to prevent any single layer dominating; has_data is True when ANY field in the layer is populated (key bugfix: governance is True for all 4,410 DEF 14As scanned, not only those with PSU programs).</t>
         </is>
@@ -1819,7 +1822,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>norm_score = raw_score × sqrt(7 / n_layers_present) for names with ≥3 layers. Names with 4 strong of 7 layers are not penalised vs names with 7 mediocre layers.</t>
         </is>
@@ -1834,7 +1837,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>Top 10 in each of 18 catalyst patterns (forward $ hurdle, M&amp;A close, spin trigger, FDA milestone, etc.) — surfaces single-mandate leaders.</t>
         </is>
@@ -1849,7 +1852,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe. Produces PSU_ARCHETYPES.md (38) + ASYMMETRIC_BY_ARCHETYPE.md (19).</t>
         </is>
@@ -1864,7 +1867,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>Each of 8 independent rankers + 2 archetype-winner markdowns contributes presence. n_screens = how many rankers surface the ticker. n_archetypes = how many buckets it wins. consensus_score = sum of rank-decay contributions.</t>
         </is>
@@ -1879,7 +1882,7 @@
           <t>Convergence test</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Name is convergent IFF n_screens ≥ 3 AND n_archetypes ≥ 1. Probability of 6-screen convergence by chance ≈ 2.4×10⁻¹⁰.</t>
         </is>
@@ -1894,7 +1897,7 @@
           <t>Robustness checks</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>Check 1: re-run after expanding yfinance from 1,885 to 2,132 (no change in convergent list). Check 2: governance bugfix expanded Tier-B coverage 2.8x (still no change). Convergent twelve is structurally informative, not data-dependent.</t>
         </is>
@@ -1909,7 +1912,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>Eight red-flag classes scored from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -1924,7 +1927,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean convergent + ≥4 screens. Material (2-5%): 1-flag convergent or 4+ archetypes. Participation (0.5-2%): single-archetype or multi-flag. Basket (&lt;1% each): sub-archetype groups.</t>
         </is>
@@ -2073,7 +2076,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.314</t>
+          <t>9 layers firing | cons 6.502</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -2117,7 +2120,7 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.618</t>
+          <t>8 layers firing | cons 7.04</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -2134,34 +2137,36 @@
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>631</v>
+        <v>4180</v>
       </c>
       <c r="D7" s="19" t="n">
-        <v>15.29</v>
+        <v>14.42</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.354</t>
+          <t>8 layers firing | cons 6.79</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -2222,115 +2227,113 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>244</v>
+        <v>631</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>5.02</v>
+        <v>15.29</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.31</v>
+        <v>0.76</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>8 layers firing | cons 5.326</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>4180</v>
+        <v>244</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>14.42</v>
+        <v>5.02</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.31</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>40</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.772</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1043</v>
+        <v>1394</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>5.29</v>
+        <v>8.6</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -2339,56 +2342,56 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.49</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>4158</v>
+        <v>1043</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>88.94</v>
+        <v>5.29</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>2.44</v>
+        <v>0.43</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.532</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -2400,122 +2403,124 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>124308</v>
+        <v>4158</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>151.78</v>
+        <v>88.94</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>3.63</v>
+        <v>2.44</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>7252</v>
+        <v>222</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>198.99</v>
+        <v>5.27</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>22</v>
+        <v>0.93</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.354</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J14" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>9011</v>
+        <v>7252</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>176.03</v>
+        <v>198.99</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>4.58</v>
+        <v>6.4</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.352</t>
+          <t>7 layers firing | cons 5.338</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -2523,34 +2528,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>1394</v>
+        <v>9011</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>8.6</v>
+        <v>176.03</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>0.48</v>
+        <v>4.58</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -2559,12 +2564,12 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.336</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
@@ -2576,25 +2581,25 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1418</v>
+        <v>124308</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>10.25</v>
+        <v>151.78</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.57</v>
+        <v>3.63</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
@@ -2603,12 +2608,12 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.112</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Mega-cap recurring revenue base</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
@@ -2620,34 +2625,34 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>351</v>
+        <v>1467</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>16.44</v>
+        <v>34.77</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.956</t>
+          <t>7 layers firing | cons 5.046</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -2664,25 +2669,25 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>1467</v>
+        <v>399</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>34.77</v>
+        <v>1.65</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.8</v>
+        <v>-7.3</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
@@ -2691,7 +2696,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.914</t>
+          <t>7 layers firing | cons 5.034</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2699,34 +2704,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>862</v>
+        <v>1474</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>5.54</v>
+        <v>25.03</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
@@ -2735,88 +2740,88 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.876</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>222</v>
+        <v>1418</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>5.27</v>
+        <v>10.25</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+        <v>0.57</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.824</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>1474</v>
+        <v>13781</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>25.03</v>
+        <v>121.36</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>27</v>
+        <v>2.85</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
@@ -2825,42 +2830,42 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.682</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1074</v>
+        <v>32997</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>23.31</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.6899999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -2869,42 +2874,42 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.406</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>32997</v>
+        <v>862</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>78.70999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>10.04</v>
+        <v>0.84</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -2913,17 +2918,17 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.524</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6670,7 @@
         <v>5.654</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
@@ -6733,7 +6738,7 @@
         <v>5.572</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
         <v>5.5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -6801,7 +6806,7 @@
         <v>5.264</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
@@ -6835,7 +6840,7 @@
         <v>4.832</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -6869,7 +6874,7 @@
         <v>4.81</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
@@ -6903,7 +6908,7 @@
         <v>3.97</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
@@ -6971,7 +6976,7 @@
         <v>4.776</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
@@ -7005,7 +7010,7 @@
         <v>4.654</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -7039,7 +7044,7 @@
         <v>4.554</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
@@ -7073,7 +7078,7 @@
         <v>4.476</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
@@ -7141,7 +7146,7 @@
         <v>4.424</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
@@ -7175,7 +7180,7 @@
         <v>4.414</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -7209,7 +7214,7 @@
         <v>4.27</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>-6</v>
+        <v>-11</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
@@ -7243,7 +7248,7 @@
         <v>4.086</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -7277,7 +7282,7 @@
         <v>3.942</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -7345,7 +7350,7 @@
         <v>3.566</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
@@ -7379,7 +7384,7 @@
         <v>3.42</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
@@ -7413,7 +7418,7 @@
         <v>3.386</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -7447,7 +7452,7 @@
         <v>3.226</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
@@ -7481,7 +7486,7 @@
         <v>2.866</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -7514,10 +7519,8 @@
       <c r="E31" s="19" t="n">
         <v>4.578</v>
       </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F31" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
@@ -7550,8 +7553,10 @@
       <c r="E32" s="21" t="n">
         <v>4.524</v>
       </c>
-      <c r="F32" s="13" t="n">
-        <v>-2</v>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -7584,8 +7589,8 @@
       <c r="E33" s="19" t="n">
         <v>4.506</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>46</v>
+      <c r="F33" s="26" t="n">
+        <v>52</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
@@ -7619,7 +7624,7 @@
         <v>4.366</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
@@ -7759,7 +7764,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="27" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="8" t="n">
@@ -7773,7 +7778,7 @@
       <c r="G5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="28" t="n">
         <v>44</v>
       </c>
       <c r="I5" s="19" t="n">
@@ -7799,7 +7804,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="13" t="n">
@@ -7813,7 +7818,7 @@
       <c r="G6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="29" t="n">
         <v>96</v>
       </c>
       <c r="I6" s="21" t="n">
@@ -7839,7 +7844,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="27" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="8" t="n">
@@ -7853,7 +7858,7 @@
       <c r="G7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="28" t="n">
         <v>78</v>
       </c>
       <c r="I7" s="19" t="n">
@@ -7879,7 +7884,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="13" t="n">
@@ -7893,7 +7898,7 @@
       <c r="G8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="29" t="n">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="n">
@@ -7919,7 +7924,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="8" t="n">
@@ -7933,7 +7938,7 @@
       <c r="G9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="28" t="n">
         <v>60</v>
       </c>
       <c r="I9" s="19" t="n">
@@ -7959,7 +7964,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="13" t="n">
@@ -7973,7 +7978,7 @@
       <c r="G10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="29" t="n">
         <v>61</v>
       </c>
       <c r="I10" s="21" t="n">
@@ -7999,7 +8004,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -8013,7 +8018,7 @@
       <c r="G11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="28" t="n">
         <v>96</v>
       </c>
       <c r="I11" s="19" t="n">
@@ -8039,7 +8044,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="13" t="n">
@@ -8053,7 +8058,7 @@
       <c r="G12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="29" t="n">
         <v>49</v>
       </c>
       <c r="I12" s="21" t="n">
@@ -8079,7 +8084,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -8093,7 +8098,7 @@
       <c r="G13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="28" t="n">
         <v>48</v>
       </c>
       <c r="I13" s="19" t="n">
@@ -8119,7 +8124,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="13" t="n">
@@ -8133,7 +8138,7 @@
       <c r="G14" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="29" t="n">
         <v>86</v>
       </c>
       <c r="I14" s="21" t="n">
@@ -8159,7 +8164,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="30" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="8" t="n">
@@ -8173,7 +8178,7 @@
       <c r="G15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="28" t="n">
         <v>36</v>
       </c>
       <c r="I15" s="19" t="n">
@@ -8199,7 +8204,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="30" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="13" t="n">
@@ -8213,7 +8218,7 @@
       <c r="G16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="29" t="n">
         <v>63</v>
       </c>
       <c r="I16" s="21" t="n">
@@ -8239,7 +8244,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="8" t="n">
@@ -8253,7 +8258,7 @@
       <c r="G17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="28" t="n">
         <v>39</v>
       </c>
       <c r="I17" s="19" t="n">
@@ -8279,7 +8284,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="13" t="n">
@@ -8293,7 +8298,7 @@
       <c r="G18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="29" t="n">
         <v>82</v>
       </c>
       <c r="I18" s="21" t="n">
@@ -8319,7 +8324,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="8" t="n">
@@ -8333,7 +8338,7 @@
       <c r="G19" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="28" t="n">
         <v>52</v>
       </c>
       <c r="I19" s="19" t="n">
@@ -8359,7 +8364,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="13" t="n">
@@ -8373,7 +8378,7 @@
       <c r="G20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="29" t="n">
         <v>76</v>
       </c>
       <c r="I20" s="21" t="n">
@@ -8399,7 +8404,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="30" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="8" t="n">
@@ -8413,7 +8418,7 @@
       <c r="G21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="28" t="n">
         <v>58</v>
       </c>
       <c r="I21" s="19" t="n">
@@ -8439,7 +8444,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="30" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="13" t="n">
@@ -8453,7 +8458,7 @@
       <c r="G22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="29" t="n">
         <v>45</v>
       </c>
       <c r="I22" s="21" t="n">
@@ -8479,7 +8484,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="30" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="8" t="n">
@@ -8493,7 +8498,7 @@
       <c r="G23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="28" t="n">
         <v>92</v>
       </c>
       <c r="I23" s="19" t="n">
@@ -8519,7 +8524,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="30" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="13" t="n">
@@ -8533,7 +8538,7 @@
       <c r="G24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="29" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="21" t="n">
@@ -8559,7 +8564,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="30" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="8" t="n">
@@ -8573,7 +8578,7 @@
       <c r="G25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="28" t="n">
         <v>31</v>
       </c>
       <c r="I25" s="19" t="n">
@@ -8599,7 +8604,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="30" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="13" t="n">
@@ -8613,7 +8618,7 @@
       <c r="G26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="29" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="21" t="n">
@@ -8639,7 +8644,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="8" t="n">
@@ -8653,7 +8658,7 @@
       <c r="G27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="28" t="n">
         <v>72</v>
       </c>
       <c r="I27" s="19" t="n">
@@ -8679,7 +8684,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="30" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="13" t="n">
@@ -8693,7 +8698,7 @@
       <c r="G28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="29" t="n">
         <v>66</v>
       </c>
       <c r="I28" s="21" t="n">
@@ -8719,7 +8724,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="30" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="8" t="n">
@@ -8733,7 +8738,7 @@
       <c r="G29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="28" t="n">
         <v>84</v>
       </c>
       <c r="I29" s="19" t="n">
@@ -8759,7 +8764,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="30" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="13" t="n">
@@ -8773,7 +8778,7 @@
       <c r="G30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="29" t="n">
         <v>67</v>
       </c>
       <c r="I30" s="21" t="n">
@@ -8799,7 +8804,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="30" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="8" t="n">
@@ -8813,7 +8818,7 @@
       <c r="G31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="28" t="n">
         <v>80</v>
       </c>
       <c r="I31" s="19" t="n">
@@ -8839,7 +8844,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="30" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="13" t="n">
@@ -8853,7 +8858,7 @@
       <c r="G32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="28" t="n">
+      <c r="H32" s="29" t="n">
         <v>45</v>
       </c>
       <c r="I32" s="21" t="n">
@@ -8879,7 +8884,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="30" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="8" t="n">
@@ -8893,7 +8898,7 @@
       <c r="G33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="28" t="n">
         <v>41</v>
       </c>
       <c r="I33" s="19" t="n">
@@ -8919,7 +8924,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="30" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="13" t="n">
@@ -8933,7 +8938,7 @@
       <c r="G34" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H34" s="29" t="n">
         <v>37</v>
       </c>
       <c r="I34" s="21" t="n">
@@ -8959,7 +8964,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="30" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="8" t="n">
@@ -8973,7 +8978,7 @@
       <c r="G35" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="27" t="n">
+      <c r="H35" s="28" t="n">
         <v>51</v>
       </c>
       <c r="I35" s="19" t="n">
@@ -8999,7 +9004,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="30" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="13" t="n">
@@ -9013,7 +9018,7 @@
       <c r="G36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="28" t="n">
+      <c r="H36" s="29" t="n">
         <v>49</v>
       </c>
       <c r="I36" s="21" t="n">
@@ -9039,7 +9044,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="30" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="8" t="n">
@@ -9053,7 +9058,7 @@
       <c r="G37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="28" t="n">
         <v>25</v>
       </c>
       <c r="I37" s="19" t="n">
@@ -9079,7 +9084,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="30" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="13" t="n">
@@ -9093,7 +9098,7 @@
       <c r="G38" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="28" t="n">
+      <c r="H38" s="29" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="21" t="n">
@@ -9119,7 +9124,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="30" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="8" t="n">
@@ -9133,7 +9138,7 @@
       <c r="G39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="28" t="n">
         <v>29</v>
       </c>
       <c r="I39" s="19" t="n">
@@ -9159,7 +9164,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="30" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="13" t="n">
@@ -9173,7 +9178,7 @@
       <c r="G40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="28" t="n">
+      <c r="H40" s="29" t="n">
         <v>40</v>
       </c>
       <c r="I40" s="21" t="n">
@@ -9199,7 +9204,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="30" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="8" t="n">
@@ -9213,7 +9218,7 @@
       <c r="G41" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="28" t="n">
         <v>57</v>
       </c>
       <c r="I41" s="19" t="n">
@@ -9239,7 +9244,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="30" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="13" t="n">
@@ -9253,7 +9258,7 @@
       <c r="G42" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="28" t="n">
+      <c r="H42" s="29" t="n">
         <v>55</v>
       </c>
       <c r="I42" s="21" t="n">
@@ -9293,7 +9298,7 @@
       <c r="G43" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="27" t="n">
+      <c r="H43" s="28" t="n">
         <v>87</v>
       </c>
       <c r="I43" s="19" t="n">
@@ -9333,7 +9338,7 @@
       <c r="G44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="28" t="n">
+      <c r="H44" s="29" t="n">
         <v>63</v>
       </c>
       <c r="I44" s="21" t="n">
@@ -9472,7 +9477,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="30" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -9514,7 +9519,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="30" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -9556,7 +9561,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="30" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -9598,7 +9603,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -9640,7 +9645,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -9682,7 +9687,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -9724,7 +9729,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -11192,7 +11197,7 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Highest PSU forensic core</t>
         </is>
@@ -11462,7 +11467,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Highest governance score</t>
         </is>
@@ -11732,7 +11737,7 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>Deepest P/B floor (&lt;0.5x book)</t>
         </is>
@@ -12002,7 +12007,7 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>Cheapest EV/EBITDA (&lt;6x)</t>
         </is>
@@ -12272,7 +12277,7 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t>Lowest trailing P/E (&lt;8x, positive)</t>
         </is>
@@ -12542,7 +12547,7 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
+      <c r="A64" s="31" t="inlineStr">
         <is>
           <t>Largest verified buyback shrinkage</t>
         </is>
@@ -12812,7 +12817,7 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="30" t="inlineStr">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>Highest 10b5-1 termination signed score</t>
         </is>
@@ -13082,7 +13087,7 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="30" t="inlineStr">
+      <c r="A88" s="31" t="inlineStr">
         <is>
           <t>Largest insider Form 4 dollar cluster</t>
         </is>
@@ -13352,7 +13357,7 @@
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="30" t="inlineStr">
+      <c r="A100" s="31" t="inlineStr">
         <is>
           <t>Live tender / 13E-3 events</t>
         </is>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -14,10 +14,11 @@
     <sheet name="Caution List" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Without Valuation" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Recent 30d" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Turnaround Signal" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Single-Measure Best" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Methodology" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Foreign Markets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Turnaround Signal" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Single-Measure Best" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Methodology" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;–&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0);&quot;–&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +86,12 @@
       <b val="1"/>
       <color rgb="00A41E22"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00A41E22"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Georgia"/>
@@ -221,9 +228,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -236,7 +240,10 @@
     <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -802,7 +809,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.502</t>
+          <t>9 layers firing | cons 6.51</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -828,7 +835,7 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 7.04</t>
+          <t>8 layers firing | cons 7.014</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -854,7 +861,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.79</t>
+          <t>8 layers firing | cons 6.742</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -865,22 +872,22 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -891,22 +898,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ADT Inc</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.326</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -917,22 +924,22 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>8 layers firing | cons 5.352</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -943,22 +950,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -969,12 +976,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -984,7 +991,7 @@
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.532</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -995,12 +1002,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1010,7 +1017,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.424</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1021,22 +1028,22 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1047,22 +1054,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.338</t>
+          <t>7 layers firing | cons 5.134</t>
         </is>
       </c>
       <c r="F26" s="12" t="n"/>
@@ -1073,22 +1080,22 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.336</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
@@ -1099,12 +1106,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -1114,7 +1121,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>7 layers firing | cons 4.834</t>
         </is>
       </c>
       <c r="F28" s="12" t="n"/>
@@ -1140,7 +1147,7 @@
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.046</t>
+          <t>7 layers firing | cons 4.772</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1151,22 +1158,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.034</t>
+          <t>7 layers firing | cons 4.66</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -1177,12 +1184,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
@@ -1192,7 +1199,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.548</t>
         </is>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -1203,22 +1210,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.824</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
@@ -1229,22 +1236,22 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.682</t>
+          <t>7 layers firing | cons 4.484</t>
         </is>
       </c>
       <c r="F33" s="12" t="n"/>
@@ -1255,22 +1262,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.46</t>
         </is>
       </c>
       <c r="F34" s="12" t="n"/>
@@ -1281,22 +1288,22 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>CERT</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>MGPI</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.524</t>
+          <t>7 layers firing | cons 4.412</t>
         </is>
       </c>
       <c r="F35" s="12" t="n"/>
@@ -1352,6 +1359,2563 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F115"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Best in Class -- Single-Measure Exceptional</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Names ranking top in ONE individual signal even if the consensus misses them. The 'single-leg high-intensity' tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Highest PSU forensic core</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: depth + rigor of the PSU plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>core 72 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>TGT</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Target Corporation</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>72</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>core 64 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>TROX</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Tronox Holdings plc</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>core 60 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>core 60 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>ECPG</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Encore Capital Group Inc</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>core 59 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>CBL</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>CBL &amp; Associates Properties, In</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>core 58 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>STAA</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>STAAR Surgical Company</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>core 57 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Nasdaq, Inc.</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>core 57 | cond_cats:</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Autodesk, Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Highest governance score</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>gov 23 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>NXT</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Nextpower Inc.</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 4y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Agilent Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>GFF</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Griffon Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange Inc.</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>CGNX</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Cognex Corporation</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>ConocoPhillips</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>ATEC</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Alphatec Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>NBHC</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>National Bank Holdings Corporat</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>Deepest P/B floor (&lt;0.5x book)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: hard balance-sheet value floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.04 | mcap $20M</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>CRMT</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>America's Car-Mart, Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.05 | mcap $19M</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>SVRN</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>OceanPal Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.06 | mcap $10M</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>ZSTK</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>ZeroStack Corp.</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.09 | mcap $52M</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>EHTH</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>eHealth, Inc.</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.09 | mcap $5M</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>FEED</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>ENvue Medical, Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.12 | mcap $5M</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>RBNE</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Robin Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.13 | mcap $10M</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>JTAI</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Jet.AI Inc.</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.13 | mcap $69M</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>GPMT</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Granite Point Mortgage Trust In</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Cheapest EV/EBITDA (&lt;6x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: enterprise-value to earnings power</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.5 | mcap $30M | Technology</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>KPLT</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Katapult Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.6 | mcap $72M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>PLRX</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Pliant Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.7 | mcap $7M | Technology</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>DTST</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Data Storage Corporation</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.7 | mcap $45M | Technology</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>LGL</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>LGL Group, Inc. (The)</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 0.9 | mcap $704M | Financial Services</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>HRTG</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Heritage Insurance Holdings, In</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 1.0 | mcap $539M | Real Estate</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>RMAX</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>RE/MAX Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 1.1 | mcap $1,899M | Financial Services</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Slide Insurance Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>EV/EBITDA 1.1 | mcap $2,856M | Technology</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>VISN</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Vistance Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="31" t="inlineStr">
+        <is>
+          <t>Lowest trailing P/E (&lt;8x, positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: earnings yield</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>P/E 0.9 | mcap $426M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>CYH</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Community Health Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>P/E 1.1 | mcap $382M | Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>Lands' End, Inc.</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>P/E 1.4 | mcap $250M | Real Estate</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>SITC</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>SITE Centers Corp.</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>P/E 1.4 | mcap $120M | Technology</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>SCOR</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>comScore, Inc.</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>P/E 1.5 | mcap $159M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>ORMP</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Oramed Pharmaceuticals Inc.</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>P/E 1.6 | mcap $192M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>WW</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>WW International, Inc.</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>P/E 1.6 | mcap $940M | Energy</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Diversified Energy Company</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>P/E 1.6 | mcap $185M | Healthcare</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>EMBC</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>Embecta Corp.</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>Largest verified buyback shrinkage</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: actual supply curve compression</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>shares -29.9% over 174d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>ANAB</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>AnaptysBio, Inc.</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>shares -27.4% over 181d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>EIG</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Employers Holdings Inc</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>shares -27.2% over 147d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>NWL</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Newell Brands Inc.</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>shares -26.7% over 65d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>AHRT</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>AH Realty Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="E70" s="21" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>shares -24.8% over 189d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>AESI</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Atlas Energy Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>shares -21.1% over 185d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>CWEN</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Clearway Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="E72" s="21" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>shares -20.6% over 176d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>AAT</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>American Assets Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="E73" s="19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>shares -19.7% over 189d | status SHRINKING_NO_AUTH</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>FOA</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Finance of America Companies In</t>
+        </is>
+      </c>
+      <c r="E74" s="21" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Highest 10b5-1 termination signed score</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: insider walked back scheduled selling</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: Casey M. Nault (Senior Vice President) 202,257sh [+26]', 'BULLISH terminate sell: Mitchell J. Krebs (Chairman) 202,257sh [+38]', 'BULLISH terminate sell: Mitchell J. Krebs (Chairman) 250,000sh [+42]', 'BEARISH adopt sell: Mitchell J. Krebs (Chairman) 200,000sh [-23]', 'BEARISH adopt sell: Casey M. Nault (Senior Vice President) 200,000sh [-15]', 'BULLISH terminate sell: Casey M. Nault (Executive Vice President) 202,257sh [+26]']</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Coeur Mining, Inc.</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]']</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>IRON</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Disc Medicine, Inc.</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BEARISH adopt sell: Roger W. Byrd (General Counsel) 135,201sh [-15]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) 518,289sh [+38]', 'BULLISH terminate sell: Roger W. Byrd (General Counsel) 518,289sh [+30]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) 135,201sh [+34]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) [+26]']</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>KODK</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Eastman Kodak Company</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" s="15" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (Director) 37,890sh [+18]', 'BULLISH terminate sell: an insider (Director) 97,075sh [+22]', 'BULLISH terminate sell: an insider (Director) 387,158sh [+30]', 'BULLISH terminate sell: an insider (Director) 363,818sh [+30]', 'BULLISH terminate sell: an insider (Director) [+18]', 'BULLISH terminate sell: an insider (Director) [+18]']</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) 165,000sh [+26]', 'BULLISH terminate sell: an insider (director) [+18]']</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>PCTY</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Paylocity Holding Corporation</t>
+        </is>
+      </c>
+      <c r="E83" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: John F. Marcolini (Senior Vice President) 11,400sh [+18]', 'BULLISH terminate sell: Thomas L. Deitrich (President and Chief Executive ) 9,540sh [+30]', 'BULLISH terminate sell: Thomas L. Deitrich (President and Chief Executive ) 6,904sh [+30]', 'BULLISH terminate sell: Donald L. Reeves (Senior Vice President) 4,170sh [+18]']</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>ITRI</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>Itron, Inc.</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: William R. McDermott (Chief Executive Officer) 3,700sh [+30]', 'BULLISH terminate sell: Gina Mastantuono (President and Chief Financial ) 3,700sh [+26]', 'BULLISH terminate sell: Nick Tzitzon (Vice Chairman) 3,700sh [+30]', 'BULLISH terminate sell: Nick Tzitzon (Vice Chairman) 649sh [+30]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 1,200sh [-3]', 'weak BEARISH adopt sell (small): Kevin McBride (Chief Accounting Officer) 1,120sh [-3]', 'weak BEARISH adopt sell (small): Nick Tzitzon (Vice Chairman) 1,120sh [-3]', 'weak BEARISH adopt sell (small): Paul Fipps (President) 253sh [-3]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 830sh [-3]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 352sh [-3]']</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>ServiceNow, Inc.</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>signed score 80 | ['BULLISH terminate sell: an insider (?) [+18]', 'BULLISH terminate sell: an insider (director) 13,216sh [+18]', 'BULLISH terminate sell: an insider (?) 139,948sh [+26]', 'BULLISH terminate sell: an insider (director) 38,227sh [+18]']</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>SCHW</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Charles Schwab Corporation (The</t>
+        </is>
+      </c>
+      <c r="E86" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="31" t="inlineStr">
+        <is>
+          <t>Largest insider Form 4 dollar cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: insider conviction in dollars</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>$105.1M cluster, 2 buyers</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>BX</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="n">
+        <v>105122527.2</v>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>$100.5M cluster, 1 buyers (0.16% of mcap)</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>RSG</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>Republic Services, Inc.</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="n">
+        <v>100528322</v>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>$75.3M cluster, 7 buyers (9.57% of mcap)</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>ODTX</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Odyssey Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="n">
+        <v>75319986</v>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>$75.0M cluster, 1 buyers (20.80% of mcap)</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>ARTV</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>Artiva Biotherapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="E94" s="21" t="n">
+        <v>74999992.3</v>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>$74.0M cluster, 1 buyers (4.16% of mcap)</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>GeneDx Holdings Corp.</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>74032163.40000001</v>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B96" s="15" t="inlineStr">
+        <is>
+          <t>$65.9M cluster, 2 buyers (4.19% of mcap)</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>Alkami Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="E96" s="21" t="n">
+        <v>65859500</v>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>$54.4M cluster, 9 buyers</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="n">
+        <v>54366421.6</v>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>$45.7M cluster, 5 buyers (0.05% of mcap)</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>KKR &amp; Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E98" s="21" t="n">
+        <v>45684632.3</v>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="31" t="inlineStr">
+        <is>
+          <t>Live tender / 13E-3 events</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>What it measures: mechanical bid as floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>EXFY</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>Expensify, Inc.</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="15" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>ABX</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>Abacus Global Management, Inc.</t>
+        </is>
+      </c>
+      <c r="E104" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>ABXL</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B106" s="15" t="inlineStr">
+        <is>
+          <t>TARGET | live event</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>ASRT</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>Assertio Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="E106" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN | live event</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>AUPH</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Aurinia Pharmaceuticals Inc</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B108" s="15" t="inlineStr">
+        <is>
+          <t>UNKNOWN | live event</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>BCIC</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>BCP Investment Corporation</t>
+        </is>
+      </c>
+      <c r="E108" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>BCX</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>BlackRock Resources  of Benefic</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>SELF_TENDER | live event</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>BGY</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>Blackrock Enhanced Internationa</t>
+        </is>
+      </c>
+      <c r="E110" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>UNKNOWN | live event</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>BHC</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>BIDDER | live event</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>Biogen Inc.</t>
+        </is>
+      </c>
+      <c r="E112" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>Each section ranks names by a SINGLE measure regardless of whether other layers fire. These are 'exceptional by one 'criterion' -- examples: ODTX archetype (insider cluster only), GETY (live self-tender only), CDE (CEO 10b5-1 termination only). Such names rarely appear in the consensus convergent list because they don't fire multiple layers, but they can be the right pick for a single-mandate position.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A65:F65"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1426,7 +3990,7 @@
       <c r="C5" s="19" t="n">
         <v>4410</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="26" t="n">
         <v>72</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -1452,7 +4016,7 @@
       <c r="C6" s="21" t="n">
         <v>4410</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="26" t="n">
         <v>72</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -1478,7 +4042,7 @@
       <c r="C7" s="19" t="n">
         <v>6164</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="26" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -1504,7 +4068,7 @@
       <c r="C8" s="21" t="n">
         <v>6164</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="26" t="n">
         <v>100</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -1530,7 +4094,7 @@
       <c r="C9" s="19" t="n">
         <v>1995</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="29" t="n">
         <v>32</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -1556,7 +4120,7 @@
       <c r="C10" s="21" t="n">
         <v>2132</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="29" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -1582,7 +4146,7 @@
       <c r="C11" s="19" t="n">
         <v>800</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="29" t="n">
         <v>13</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -1721,7 +4285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2076,7 +4640,7 @@
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.502</t>
+          <t>9 layers firing | cons 6.51</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -2120,7 +4684,7 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 7.04</t>
+          <t>8 layers firing | cons 7.014</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -2166,7 +4730,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.79</t>
+          <t>8 layers firing | cons 6.742</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -2183,25 +4747,25 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>5004</v>
+        <v>124308</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>6.58</v>
+        <v>151.78</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>1.38</v>
+        <v>3.63</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
@@ -2210,42 +4774,42 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>631</v>
+        <v>5004</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>15.29</v>
+        <v>6.58</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.76</v>
+        <v>1.38</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -2254,144 +4818,144 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.326</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>244</v>
+        <v>631</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>5.02</v>
+        <v>15.29</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>0.31</v>
+        <v>0.76</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>8 layers firing | cons 5.352</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>1394</v>
+        <v>244</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>8.6</v>
+        <v>5.02</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1043</v>
+        <v>4158</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>5.29</v>
+        <v>88.94</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>0.43</v>
+        <v>2.44</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.532</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -2403,39 +4967,39 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>4158</v>
+        <v>1043</v>
       </c>
       <c r="D13" s="19" t="n">
-        <v>88.94</v>
+        <v>5.29</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>2.44</v>
+        <v>0.43</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.424</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -2447,80 +5011,78 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>222</v>
+        <v>1394</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>5.27</v>
+        <v>8.6</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
+        <v>0.48</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>7252</v>
+        <v>9011</v>
       </c>
       <c r="D15" s="19" t="n">
-        <v>198.99</v>
+        <v>176.03</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>6.4</v>
+        <v>4.58</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.338</t>
+          <t>7 layers firing | cons 5.134</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -2528,34 +5090,36 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>9011</v>
+        <v>222</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>176.03</v>
+        <v>5.27</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>7</v>
+        <v>0.93</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -2564,42 +5128,42 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.336</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>124308</v>
+        <v>1418</v>
       </c>
       <c r="D17" s="19" t="n">
-        <v>151.78</v>
+        <v>10.25</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>3.63</v>
+        <v>0.57</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
@@ -2608,12 +5172,12 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>7 layers firing | cons 4.834</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
@@ -2652,7 +5216,7 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.046</t>
+          <t>7 layers firing | cons 4.772</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
@@ -2669,25 +5233,25 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>399</v>
+        <v>862</v>
       </c>
       <c r="D19" s="19" t="n">
-        <v>1.65</v>
+        <v>5.54</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>-7.3</v>
+        <v>0.84</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
@@ -2696,7 +5260,7 @@
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.034</t>
+          <t>7 layers firing | cons 4.66</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
@@ -2704,48 +5268,48 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>1474</v>
+        <v>7252</v>
       </c>
       <c r="D20" s="21" t="n">
-        <v>25.03</v>
+        <v>198.99</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>0.5600000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.548</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J20" s="15" t="inlineStr">
@@ -2757,25 +5321,25 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1418</v>
+        <v>1474</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>10.25</v>
+        <v>25.03</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -2784,53 +5348,51 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.824</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>13781</v>
+        <v>399</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>121.36</v>
+        <v>1.65</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
+        <v>-7.3</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.682</t>
+          <t>7 layers firing | cons 4.484</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
@@ -2838,34 +5400,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>32997</v>
+        <v>1216</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>78.70999999999999</v>
+        <v>13.05</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>10.04</v>
+        <v>0.98</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -2874,51 +5436,51 @@
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.46</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>862</v>
+        <v>351</v>
       </c>
       <c r="D24" s="21" t="n">
-        <v>5.54</v>
+        <v>16.44</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.524</t>
+          <t>7 layers firing | cons 4.412</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
@@ -2926,9 +5488,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J24" s="15" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -6704,7 +9266,7 @@
         <v>5.64</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
@@ -6738,7 +9300,7 @@
         <v>5.572</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
@@ -6772,7 +9334,7 @@
         <v>5.5</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -6806,7 +9368,7 @@
         <v>5.264</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
@@ -6840,7 +9402,7 @@
         <v>4.832</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -6874,7 +9436,7 @@
         <v>4.81</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
@@ -6908,7 +9470,7 @@
         <v>3.97</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
@@ -6976,7 +9538,7 @@
         <v>4.776</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
@@ -7010,7 +9572,7 @@
         <v>4.654</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
@@ -7044,7 +9606,7 @@
         <v>4.554</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
@@ -7078,7 +9640,7 @@
         <v>4.476</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
@@ -7146,7 +9708,7 @@
         <v>4.424</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
@@ -7180,7 +9742,7 @@
         <v>4.414</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
@@ -7214,7 +9776,7 @@
         <v>4.27</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
@@ -7248,7 +9810,7 @@
         <v>4.086</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
@@ -7282,7 +9844,7 @@
         <v>3.942</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
@@ -7316,7 +9878,7 @@
         <v>3.66</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
@@ -7384,7 +9946,7 @@
         <v>3.42</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
@@ -7418,7 +9980,7 @@
         <v>3.386</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
@@ -7452,7 +10014,7 @@
         <v>3.226</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
@@ -7486,7 +10048,7 @@
         <v>2.866</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
@@ -7553,10 +10115,8 @@
       <c r="E32" s="21" t="n">
         <v>4.524</v>
       </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F32" s="13" t="n">
+        <v>-1</v>
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
@@ -7589,8 +10149,8 @@
       <c r="E33" s="19" t="n">
         <v>4.506</v>
       </c>
-      <c r="F33" s="26" t="n">
-        <v>52</v>
+      <c r="F33" s="8" t="n">
+        <v>48</v>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
@@ -7624,7 +10184,7 @@
         <v>4.366</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
@@ -7764,7 +10324,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="26" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="8" t="n">
@@ -7778,7 +10338,7 @@
       <c r="G5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="27" t="n">
         <v>44</v>
       </c>
       <c r="I5" s="19" t="n">
@@ -7804,7 +10364,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="26" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="13" t="n">
@@ -7818,7 +10378,7 @@
       <c r="G6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="28" t="n">
         <v>96</v>
       </c>
       <c r="I6" s="21" t="n">
@@ -7844,7 +10404,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="26" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="8" t="n">
@@ -7858,7 +10418,7 @@
       <c r="G7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="27" t="n">
         <v>78</v>
       </c>
       <c r="I7" s="19" t="n">
@@ -7884,7 +10444,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="29" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="13" t="n">
@@ -7898,7 +10458,7 @@
       <c r="G8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="28" t="n">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="n">
@@ -7924,7 +10484,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="29" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="8" t="n">
@@ -7938,7 +10498,7 @@
       <c r="G9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="27" t="n">
         <v>60</v>
       </c>
       <c r="I9" s="19" t="n">
@@ -7964,7 +10524,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="29" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="13" t="n">
@@ -7978,7 +10538,7 @@
       <c r="G10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="29" t="n">
+      <c r="H10" s="28" t="n">
         <v>61</v>
       </c>
       <c r="I10" s="21" t="n">
@@ -8004,7 +10564,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="29" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="8" t="n">
@@ -8018,7 +10578,7 @@
       <c r="G11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="27" t="n">
         <v>96</v>
       </c>
       <c r="I11" s="19" t="n">
@@ -8044,7 +10604,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="29" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="13" t="n">
@@ -8058,7 +10618,7 @@
       <c r="G12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="29" t="n">
+      <c r="H12" s="28" t="n">
         <v>49</v>
       </c>
       <c r="I12" s="21" t="n">
@@ -8084,7 +10644,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="29" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="8" t="n">
@@ -8098,7 +10658,7 @@
       <c r="G13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="27" t="n">
         <v>48</v>
       </c>
       <c r="I13" s="19" t="n">
@@ -8124,7 +10684,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="29" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="13" t="n">
@@ -8138,7 +10698,7 @@
       <c r="G14" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="29" t="n">
+      <c r="H14" s="28" t="n">
         <v>86</v>
       </c>
       <c r="I14" s="21" t="n">
@@ -8164,7 +10724,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="30" t="n">
+      <c r="D15" s="29" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="8" t="n">
@@ -8178,7 +10738,7 @@
       <c r="G15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="27" t="n">
         <v>36</v>
       </c>
       <c r="I15" s="19" t="n">
@@ -8204,7 +10764,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="29" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="13" t="n">
@@ -8218,7 +10778,7 @@
       <c r="G16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="29" t="n">
+      <c r="H16" s="28" t="n">
         <v>63</v>
       </c>
       <c r="I16" s="21" t="n">
@@ -8244,7 +10804,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="30" t="n">
+      <c r="D17" s="29" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="8" t="n">
@@ -8258,7 +10818,7 @@
       <c r="G17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="27" t="n">
         <v>39</v>
       </c>
       <c r="I17" s="19" t="n">
@@ -8284,7 +10844,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="29" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="13" t="n">
@@ -8298,7 +10858,7 @@
       <c r="G18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H18" s="28" t="n">
         <v>82</v>
       </c>
       <c r="I18" s="21" t="n">
@@ -8324,7 +10884,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="29" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="8" t="n">
@@ -8338,7 +10898,7 @@
       <c r="G19" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="27" t="n">
         <v>52</v>
       </c>
       <c r="I19" s="19" t="n">
@@ -8364,7 +10924,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="30" t="n">
+      <c r="D20" s="29" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="13" t="n">
@@ -8378,7 +10938,7 @@
       <c r="G20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="29" t="n">
+      <c r="H20" s="28" t="n">
         <v>76</v>
       </c>
       <c r="I20" s="21" t="n">
@@ -8404,7 +10964,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="D21" s="29" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="8" t="n">
@@ -8418,7 +10978,7 @@
       <c r="G21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="27" t="n">
         <v>58</v>
       </c>
       <c r="I21" s="19" t="n">
@@ -8444,7 +11004,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="D22" s="29" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="13" t="n">
@@ -8458,7 +11018,7 @@
       <c r="G22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="29" t="n">
+      <c r="H22" s="28" t="n">
         <v>45</v>
       </c>
       <c r="I22" s="21" t="n">
@@ -8484,7 +11044,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="30" t="n">
+      <c r="D23" s="29" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="8" t="n">
@@ -8498,7 +11058,7 @@
       <c r="G23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="27" t="n">
         <v>92</v>
       </c>
       <c r="I23" s="19" t="n">
@@ -8524,7 +11084,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="30" t="n">
+      <c r="D24" s="29" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="13" t="n">
@@ -8538,7 +11098,7 @@
       <c r="G24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="29" t="n">
+      <c r="H24" s="28" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="21" t="n">
@@ -8564,7 +11124,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="30" t="n">
+      <c r="D25" s="29" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="8" t="n">
@@ -8578,7 +11138,7 @@
       <c r="G25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="27" t="n">
         <v>31</v>
       </c>
       <c r="I25" s="19" t="n">
@@ -8604,7 +11164,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="30" t="n">
+      <c r="D26" s="29" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="13" t="n">
@@ -8618,7 +11178,7 @@
       <c r="G26" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="28" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="21" t="n">
@@ -8644,7 +11204,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="30" t="n">
+      <c r="D27" s="29" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="8" t="n">
@@ -8658,7 +11218,7 @@
       <c r="G27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="27" t="n">
         <v>72</v>
       </c>
       <c r="I27" s="19" t="n">
@@ -8684,7 +11244,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="30" t="n">
+      <c r="D28" s="29" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="13" t="n">
@@ -8698,7 +11258,7 @@
       <c r="G28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="29" t="n">
+      <c r="H28" s="28" t="n">
         <v>66</v>
       </c>
       <c r="I28" s="21" t="n">
@@ -8724,7 +11284,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="30" t="n">
+      <c r="D29" s="29" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="8" t="n">
@@ -8738,7 +11298,7 @@
       <c r="G29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="28" t="n">
+      <c r="H29" s="27" t="n">
         <v>84</v>
       </c>
       <c r="I29" s="19" t="n">
@@ -8764,7 +11324,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="30" t="n">
+      <c r="D30" s="29" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="13" t="n">
@@ -8778,7 +11338,7 @@
       <c r="G30" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="29" t="n">
+      <c r="H30" s="28" t="n">
         <v>67</v>
       </c>
       <c r="I30" s="21" t="n">
@@ -8804,7 +11364,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="30" t="n">
+      <c r="D31" s="29" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="8" t="n">
@@ -8818,7 +11378,7 @@
       <c r="G31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="27" t="n">
         <v>80</v>
       </c>
       <c r="I31" s="19" t="n">
@@ -8844,7 +11404,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="30" t="n">
+      <c r="D32" s="29" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="13" t="n">
@@ -8858,7 +11418,7 @@
       <c r="G32" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="29" t="n">
+      <c r="H32" s="28" t="n">
         <v>45</v>
       </c>
       <c r="I32" s="21" t="n">
@@ -8884,7 +11444,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="30" t="n">
+      <c r="D33" s="29" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="8" t="n">
@@ -8898,7 +11458,7 @@
       <c r="G33" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="28" t="n">
+      <c r="H33" s="27" t="n">
         <v>41</v>
       </c>
       <c r="I33" s="19" t="n">
@@ -8924,7 +11484,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="30" t="n">
+      <c r="D34" s="29" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="13" t="n">
@@ -8938,7 +11498,7 @@
       <c r="G34" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="29" t="n">
+      <c r="H34" s="28" t="n">
         <v>37</v>
       </c>
       <c r="I34" s="21" t="n">
@@ -8964,7 +11524,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="30" t="n">
+      <c r="D35" s="29" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="8" t="n">
@@ -8978,7 +11538,7 @@
       <c r="G35" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="27" t="n">
         <v>51</v>
       </c>
       <c r="I35" s="19" t="n">
@@ -9004,7 +11564,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="30" t="n">
+      <c r="D36" s="29" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="13" t="n">
@@ -9018,7 +11578,7 @@
       <c r="G36" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="29" t="n">
+      <c r="H36" s="28" t="n">
         <v>49</v>
       </c>
       <c r="I36" s="21" t="n">
@@ -9044,7 +11604,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="30" t="n">
+      <c r="D37" s="29" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="8" t="n">
@@ -9058,7 +11618,7 @@
       <c r="G37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="28" t="n">
+      <c r="H37" s="27" t="n">
         <v>25</v>
       </c>
       <c r="I37" s="19" t="n">
@@ -9084,7 +11644,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="30" t="n">
+      <c r="D38" s="29" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="13" t="n">
@@ -9098,7 +11658,7 @@
       <c r="G38" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="29" t="n">
+      <c r="H38" s="28" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="21" t="n">
@@ -9124,7 +11684,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="30" t="n">
+      <c r="D39" s="29" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="8" t="n">
@@ -9138,7 +11698,7 @@
       <c r="G39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="28" t="n">
+      <c r="H39" s="27" t="n">
         <v>29</v>
       </c>
       <c r="I39" s="19" t="n">
@@ -9164,7 +11724,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="30" t="n">
+      <c r="D40" s="29" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="13" t="n">
@@ -9178,7 +11738,7 @@
       <c r="G40" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="29" t="n">
+      <c r="H40" s="28" t="n">
         <v>40</v>
       </c>
       <c r="I40" s="21" t="n">
@@ -9204,7 +11764,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="30" t="n">
+      <c r="D41" s="29" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="8" t="n">
@@ -9218,7 +11778,7 @@
       <c r="G41" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="28" t="n">
+      <c r="H41" s="27" t="n">
         <v>57</v>
       </c>
       <c r="I41" s="19" t="n">
@@ -9244,7 +11804,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="30" t="n">
+      <c r="D42" s="29" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="13" t="n">
@@ -9258,7 +11818,7 @@
       <c r="G42" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="29" t="n">
+      <c r="H42" s="28" t="n">
         <v>55</v>
       </c>
       <c r="I42" s="21" t="n">
@@ -9298,7 +11858,7 @@
       <c r="G43" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="28" t="n">
+      <c r="H43" s="27" t="n">
         <v>87</v>
       </c>
       <c r="I43" s="19" t="n">
@@ -9338,7 +11898,7 @@
       <c r="G44" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="28" t="n">
         <v>63</v>
       </c>
       <c r="I44" s="21" t="n">
@@ -9368,6 +11928,2261 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foreign Markets — JP / KR / UK</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Japan TSE PBR&lt;1 reform targets, Korea Value-Up chaebol, UK FTSE 100 scheme/take-private candidates. Foreign tickers kept separate from US universe consensus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mkt</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>ROE %</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>9022.T</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>CENTRAL JAPAN RAILWAY CO</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>0.6296625</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>5.854111</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>11.4700004</v>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.63 (TSE reform target); quality+value ROE 11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>9501.T</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>TOKYO ELEC POWER CO HLDGS INC</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>0.22752257</v>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>-12.622</v>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.23 (TSE reform target); DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>VTY.L</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>VISTRY GROUP PLC ORD 50P</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0.26397306</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>6.5333333</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>4.2069998</v>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.26 (scheme candidate); P/E 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>III.L</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>3I GROUP PLC ORD 73 19/22P</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.83113635</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>4.679035</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>19.077998</v>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.83; P/E 4.7; div yield 372.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>VOD.L</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>VODAFONE GROUP PLC ORD USD0.20</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>0.5547121</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>0.10899999</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.55 (scheme candidate); div yield 378.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>SBRY.L</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>SAINSBURY (J) PLC ORD 28 4/7P</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0.688652</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>17.51089</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>6.4109996</v>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.69 (scheme candidate); div yield 439.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>TOYOTA MOTOR CORP</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.881705</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>9.148345000000001</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>10.233</v>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.88; quality+value ROE 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>7267.T</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>HONDA MOTOR CO</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>0.46575868</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>-2.8499998</v>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.47 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>7270.T</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>SUBARU CORPORATION</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0.6179315</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>19.150717</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>3.3069998</v>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.62 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>7201.T</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>NISSAN MOTOR CO</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>0.22002745</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>-9.856</v>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.22 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>1605.T</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>INPEX CORPORATION</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>0.7812199</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>9.943130500000001</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>8.282</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.78; quality+value ROE 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>5020.T</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>ENEOS HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>0.9507054</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>12.411422</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.95; quality+value ROE 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>5401.T</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>NIPPON STEEL CORPORATION</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>0.516917</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>166.7683</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.52 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>5411.T</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>JFE HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>0.37543565</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>14.648475</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>2.8110001</v>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.38 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>9101.T</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>NIPPON YUSEN KABUSHIKI KAISHA</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>0.6957521</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>10.444035</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>7.056</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.70 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>9104.T</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>MITSUI O.S.K. LINES LTD</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>0.62819624</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>8.47991</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>7.566000000000001</v>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.63 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>1925.T</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>DAIWA HOUSE INDUSTRY CO</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>0.93027914</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>7.682529</v>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>12.528</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.93; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>1928.T</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>SEKISUI HOUSE</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>0.9845158000000001</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>8.268003999999999</v>
+      </c>
+      <c r="G22" s="28" t="n">
+        <v>12.644</v>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.98; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>9201.T</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>JAPAN AIRLINES CO LTD</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>0.9385531</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>9.176824</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.94; quality+value ROE 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>9202.T</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>ANA HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>0.90998346</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>9.315649000000001</v>
+      </c>
+      <c r="G24" s="28" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>PBR 0.91; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>9503.T</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>KANSAI ELECTRIC POWER CO INC</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" s="19" t="n">
+        <v>0.74417263</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>6.766146</v>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>11.607</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.74; quality+value ROE 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>SK hynix</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="28" t="n">
+        <v>61.172</v>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>028260.KS</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>SAMSUNG C&amp;T</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>7.478999999999999</v>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>066570.KS</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>LGELECTRONICS</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>051910.KS</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>LGCHEM</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>-5.933999999999999</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>006400.KS</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>SAMSUNG SDI CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G30" s="28" t="n">
+        <v>-2.5710002</v>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>032830.KS</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>SAMSUNG LIFE</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>5.252</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>029780.KS</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>SAMSUNG CARD</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G32" s="28" t="n">
+        <v>7.2129995</v>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>017670.KS</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>SKTelecom</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>010140.KS</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>SamsungHvyInd</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>13.207</v>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>267250.KS</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>HD HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>16.758</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>IAG.L</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL CONSOLIDATED AIRL</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>3.4071958</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <v>7.927419</v>
+      </c>
+      <c r="G36" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>P/E 7.9; div yield 178.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>ABDN.L</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>0.88921183</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>11.657143</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <v>7.823</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.89; div yield 629.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>KGF.L</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>KINGFISHER PLC ORD 15 5/7P</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>0.80710936</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>20.921429</v>
+      </c>
+      <c r="G38" s="28" t="n">
+        <v>3.918999799999999</v>
+      </c>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>P/B 0.81; div yield 430.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>9107.T</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>KAWASAKI KISEN KAISHA</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>0.85800916</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>11.634099</v>
+      </c>
+      <c r="G39" s="27" t="n">
+        <v>7.754</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>SamsungElec</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G40" s="28" t="n">
+        <v>18.855</v>
+      </c>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>005380.KS</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>HyundaiMtr</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="n">
+        <v>7.539999999999999</v>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>005490.KS</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>POSCO Holdings</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>086790.KS</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>HANAFINANCIALGR</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G43" s="27" t="n">
+        <v>9.097</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>316140.KS</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>WooriFinancialGroup</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G44" s="28" t="n">
+        <v>8.518000000000001</v>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>105560.KS</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>KBFinancialGroup</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G45" s="27" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>005935.KS</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>SamsungElec(1P)</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G46" s="28" t="n">
+        <v>18.855</v>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>035720.KS</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Kakao</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G47" s="27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>012330.KS</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Mobis</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G48" s="28" t="n">
+        <v>7.2270006</v>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>treasury ~36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>015760.KS</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>KEPCO</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G49" s="27" t="n">
+        <v>18.671</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>036570.KS</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="28" t="n">
+        <v>14.094</v>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>treasury ~45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>251270.KS</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Netmarble</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G51" s="27" t="n">
+        <v>6.414000000000001</v>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>010130.KS</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>KOREA ZINC</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G52" s="28" t="n">
+        <v>10.064</v>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>treasury ~75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>024110.KS</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G53" s="27" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>009540.KS</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>HDKSOE</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G54" s="28" t="n">
+        <v>21.757999</v>
+      </c>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>treasury ~35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>047810.KS</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>KOREA AEROSPACE</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="27" t="n">
+        <v>10.922</v>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>138040.KS</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Meritz Financial</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G56" s="28" t="n">
+        <v>21.345</v>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>treasury ~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>SHEL.L</t>
+        </is>
+      </c>
+      <c r="B57" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>SHELL PLC ORD EUR0.07</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>1.2567812</v>
+      </c>
+      <c r="F57" s="19" t="n">
+        <v>12.022634</v>
+      </c>
+      <c r="G57" s="27" t="n">
+        <v>10.697</v>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>div yield 396.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>BP.L</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>BP PLC $0.25</t>
+        </is>
+      </c>
+      <c r="D58" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>1.7580478</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <v>29.628126</v>
+      </c>
+      <c r="G58" s="28" t="n">
+        <v>5.842</v>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>div yield 518.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>ULVR.L</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>UNILEVER PLC ORD 3.5P</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>7.4571557</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>20.560537</v>
+      </c>
+      <c r="G59" s="27" t="n">
+        <v>30.955</v>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>div yield 372.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>HSBA.L</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>HSBC HOLDINGS PLC ORD $0.50 (UK</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>1.8993394</v>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>15.749999</v>
+      </c>
+      <c r="G60" s="28" t="n">
+        <v>11.611</v>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>div yield 389.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>AZN.L</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>ASTRAZENECA PLC ORD SHS $0.25</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" s="19" t="n">
+        <v>6.094377</v>
+      </c>
+      <c r="F61" s="19" t="n">
+        <v>27.900793</v>
+      </c>
+      <c r="G61" s="27" t="n">
+        <v>23.482999</v>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>div yield 170.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>GSK.L</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>GSK PLC ORD 31 1/4P</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="21" t="n">
+        <v>4.443819</v>
+      </c>
+      <c r="F62" s="21" t="n">
+        <v>13.897888</v>
+      </c>
+      <c r="G62" s="28" t="n">
+        <v>40.905997</v>
+      </c>
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>div yield 349.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>BATS.L</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>BRITISH AMERICAN TOBACCO PLC OR</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="19" t="n">
+        <v>2.2128325</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>13.429799</v>
+      </c>
+      <c r="G63" s="27" t="n">
+        <v>15.824</v>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>div yield 524.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="20" t="inlineStr">
+        <is>
+          <t>BARC.L</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>BARCLAYS PLC ORD 25P</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="21" t="n">
+        <v>1.1118265</v>
+      </c>
+      <c r="F64" s="21" t="n">
+        <v>12.046511</v>
+      </c>
+      <c r="G64" s="28" t="n">
+        <v>9.552</v>
+      </c>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>div yield 170.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Japan signal: TSE explicit policy targets PBR&lt;1 companies for capital return reform; scored highest at PBR&lt;0.7. Korea: Value-Up / treasury cancellation program (chaebol families named candidates: Samsung, Hyundai, LG, SK, POSCO). UK: scheme of arrangement is the dominant take-private mechanism in London; deep-discount FTSE names are the target pool. Source: foreign_markets.json (yfinance with .T/.KS/.L suffixes; seed list ~130 tickers, expandable).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9477,7 +14292,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="29" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -9519,7 +14334,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="29" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -9561,7 +14376,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="29" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -9603,7 +14418,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="29" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -9645,7 +14460,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="29" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -9687,7 +14502,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="29" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -9729,7 +14544,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="29" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -11158,2561 +15973,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F115"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Best in Class -- Single-Measure Exceptional</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Names ranking top in ONE individual signal even if the consensus misses them. The 'single-leg high-intensity' tail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>Highest PSU forensic core</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: depth + rigor of the PSU plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>core 72 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Target Corporation</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>72</v>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>core 64 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>TROX</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Tronox Holdings plc</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>core 60 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>core 60 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>ECPG</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Encore Capital Group Inc</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>core 59 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>CBL</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>CBL &amp; Associates Properties, In</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>59</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>core 58 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>STAA</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>STAAR Surgical Company</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>58</v>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>core 57 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>NDAQ</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Nasdaq, Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>57</v>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>core 57 | cond_cats:</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>ADSK</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Autodesk, Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>57</v>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>Highest governance score</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>gov 23 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>NXT</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Nextpower Inc.</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>23</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>gov 21 | reasons: double-trigger only; 4y vesting; clawback strengthened</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>Agilent Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>GFF</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Griffon Corporation</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange Inc.</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>gov 21 | reasons: double-trigger only; 3y vesting; clawback strengthened</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>CGNX</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Cognex Corporation</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>ConocoPhillips</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>ATEC</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Alphatec Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>gov 20 | reasons: double-trigger only; post-vest holding requirement; 3y vesting</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>NBHC</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>National Bank Holdings Corporat</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>Deepest P/B floor (&lt;0.5x book)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: hard balance-sheet value floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.04 | mcap $20M</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>CRMT</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>America's Car-Mart, Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>P/B 0.05 | mcap $19M</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>SVRN</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>OceanPal Inc.</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.06 | mcap $10M</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>ZSTK</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>ZeroStack Corp.</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>P/B 0.09 | mcap $52M</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>EHTH</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>eHealth, Inc.</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.09 | mcap $5M</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>FEED</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>ENvue Medical, Inc.</t>
-        </is>
-      </c>
-      <c r="E35" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F35" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>P/B 0.12 | mcap $5M</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>RBNE</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>Robin Energy Ltd.</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.13 | mcap $10M</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>JTAI</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Jet.AI Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>P/B 0.13 | mcap $69M</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>GPMT</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>Granite Point Mortgage Trust In</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="31" t="inlineStr">
-        <is>
-          <t>Cheapest EV/EBITDA (&lt;6x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: enterprise-value to earnings power</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 0.5 | mcap $30M | Technology</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>KPLT</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Katapult Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="E43" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 0.6 | mcap $72M | Healthcare</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>PLRX</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
-        <is>
-          <t>Pliant Therapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 0.7 | mcap $7M | Technology</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>DTST</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Data Storage Corporation</t>
-        </is>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 0.7 | mcap $45M | Technology</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>LGL</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>LGL Group, Inc. (The)</t>
-        </is>
-      </c>
-      <c r="E46" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 0.9 | mcap $704M | Financial Services</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>HRTG</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>Heritage Insurance Holdings, In</t>
-        </is>
-      </c>
-      <c r="E47" s="19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 1.0 | mcap $539M | Real Estate</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>RMAX</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>RE/MAX Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="15" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 1.1 | mcap $1,899M | Financial Services</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>SLDE</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>Slide Insurance Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="E49" s="19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>EV/EBITDA 1.1 | mcap $2,856M | Technology</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>VISN</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>Vistance Networks, Inc.</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F50" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="31" t="inlineStr">
-        <is>
-          <t>Lowest trailing P/E (&lt;8x, positive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: earnings yield</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>P/E 0.9 | mcap $426M | Healthcare</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>CYH</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Community Health Systems, Inc.</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>P/E 1.1 | mcap $382M | Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="inlineStr">
-        <is>
-          <t>Lands' End, Inc.</t>
-        </is>
-      </c>
-      <c r="E56" s="21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F56" s="15" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>P/E 1.4 | mcap $250M | Real Estate</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>SITC</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>SITE Centers Corp.</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>P/E 1.4 | mcap $120M | Technology</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>SCOR</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>comScore, Inc.</t>
-        </is>
-      </c>
-      <c r="E58" s="21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>P/E 1.5 | mcap $159M | Healthcare</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>ORMP</t>
-        </is>
-      </c>
-      <c r="D59" s="10" t="inlineStr">
-        <is>
-          <t>Oramed Pharmaceuticals Inc.</t>
-        </is>
-      </c>
-      <c r="E59" s="19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F59" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>P/E 1.6 | mcap $192M | Healthcare</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>WW</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>WW International, Inc.</t>
-        </is>
-      </c>
-      <c r="E60" s="21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>P/E 1.6 | mcap $940M | Energy</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>Diversified Energy Company</t>
-        </is>
-      </c>
-      <c r="E61" s="19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F61" s="10" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>P/E 1.6 | mcap $185M | Healthcare</t>
-        </is>
-      </c>
-      <c r="C62" s="20" t="inlineStr">
-        <is>
-          <t>EMBC</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>Embecta Corp.</t>
-        </is>
-      </c>
-      <c r="E62" s="21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F62" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t>Largest verified buyback shrinkage</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: actual supply curve compression</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>shares -29.9% over 174d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>ANAB</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>AnaptysBio, Inc.</t>
-        </is>
-      </c>
-      <c r="E67" s="19" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>shares -27.4% over 181d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C68" s="20" t="inlineStr">
-        <is>
-          <t>EIG</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>Employers Holdings Inc</t>
-        </is>
-      </c>
-      <c r="E68" s="21" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="F68" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>shares -27.2% over 147d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>NWL</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Newell Brands Inc.</t>
-        </is>
-      </c>
-      <c r="E69" s="19" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>Consumer Defensive</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>shares -26.7% over 65d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="inlineStr">
-        <is>
-          <t>AHRT</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>AH Realty Trust, Inc.</t>
-        </is>
-      </c>
-      <c r="E70" s="21" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>shares -24.8% over 189d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>AESI</t>
-        </is>
-      </c>
-      <c r="D71" s="10" t="inlineStr">
-        <is>
-          <t>Atlas Energy Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="E71" s="19" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>shares -21.1% over 185d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C72" s="20" t="inlineStr">
-        <is>
-          <t>CWEN</t>
-        </is>
-      </c>
-      <c r="D72" s="15" t="inlineStr">
-        <is>
-          <t>Clearway Energy, Inc.</t>
-        </is>
-      </c>
-      <c r="E72" s="21" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>shares -20.6% over 176d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>AAT</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>American Assets Trust, Inc.</t>
-        </is>
-      </c>
-      <c r="E73" s="19" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>shares -19.7% over 189d | status SHRINKING_NO_AUTH</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="inlineStr">
-        <is>
-          <t>FOA</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>Finance of America Companies In</t>
-        </is>
-      </c>
-      <c r="E74" s="21" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F74" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Highest 10b5-1 termination signed score</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: insider walked back scheduled selling</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: Casey M. Nault (Senior Vice President) 202,257sh [+26]', 'BULLISH terminate sell: Mitchell J. Krebs (Chairman) 202,257sh [+38]', 'BULLISH terminate sell: Mitchell J. Krebs (Chairman) 250,000sh [+42]', 'BEARISH adopt sell: Mitchell J. Krebs (Chairman) 200,000sh [-23]', 'BEARISH adopt sell: Casey M. Nault (Senior Vice President) 200,000sh [-15]', 'BULLISH terminate sell: Casey M. Nault (Executive Vice President) 202,257sh [+26]']</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
-        <is>
-          <t>CDE</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Coeur Mining, Inc.</t>
-        </is>
-      </c>
-      <c r="E79" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B80" s="15" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]']</t>
-        </is>
-      </c>
-      <c r="C80" s="20" t="inlineStr">
-        <is>
-          <t>IRON</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>Disc Medicine, Inc.</t>
-        </is>
-      </c>
-      <c r="E80" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="F80" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BEARISH adopt sell: Roger W. Byrd (General Counsel) 135,201sh [-15]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) 518,289sh [+38]', 'BULLISH terminate sell: Roger W. Byrd (General Counsel) 518,289sh [+30]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) 135,201sh [+34]', 'BULLISH terminate sell: David E. Bullwinkle (Chief Financial Officer) [+26]']</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>KODK</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr">
-        <is>
-          <t>Eastman Kodak Company</t>
-        </is>
-      </c>
-      <c r="E81" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: an insider (Director) 37,890sh [+18]', 'BULLISH terminate sell: an insider (Director) 97,075sh [+22]', 'BULLISH terminate sell: an insider (Director) 387,158sh [+30]', 'BULLISH terminate sell: an insider (Director) 363,818sh [+30]', 'BULLISH terminate sell: an insider (Director) [+18]', 'BULLISH terminate sell: an insider (Director) [+18]']</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E82" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="F82" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) [+18]', 'BULLISH terminate sell: an insider (director) 165,000sh [+26]', 'BULLISH terminate sell: an insider (director) [+18]']</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="inlineStr">
-        <is>
-          <t>PCTY</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="inlineStr">
-        <is>
-          <t>Paylocity Holding Corporation</t>
-        </is>
-      </c>
-      <c r="E83" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="A84" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="15" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: John F. Marcolini (Senior Vice President) 11,400sh [+18]', 'BULLISH terminate sell: Thomas L. Deitrich (President and Chief Executive ) 9,540sh [+30]', 'BULLISH terminate sell: Thomas L. Deitrich (President and Chief Executive ) 6,904sh [+30]', 'BULLISH terminate sell: Donald L. Reeves (Senior Vice President) 4,170sh [+18]']</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="inlineStr">
-        <is>
-          <t>ITRI</t>
-        </is>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>Itron, Inc.</t>
-        </is>
-      </c>
-      <c r="E84" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="F84" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: William R. McDermott (Chief Executive Officer) 3,700sh [+30]', 'BULLISH terminate sell: Gina Mastantuono (President and Chief Financial ) 3,700sh [+26]', 'BULLISH terminate sell: Nick Tzitzon (Vice Chairman) 3,700sh [+30]', 'BULLISH terminate sell: Nick Tzitzon (Vice Chairman) 649sh [+30]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 1,200sh [-3]', 'weak BEARISH adopt sell (small): Kevin McBride (Chief Accounting Officer) 1,120sh [-3]', 'weak BEARISH adopt sell (small): Nick Tzitzon (Vice Chairman) 1,120sh [-3]', 'weak BEARISH adopt sell (small): Paul Fipps (President) 253sh [-3]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 830sh [-3]', 'weak BEARISH adopt sell (small): Gina Mastantuono (Chief Financial Officer) 352sh [-3]']</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>ServiceNow, Inc.</t>
-        </is>
-      </c>
-      <c r="E85" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B86" s="15" t="inlineStr">
-        <is>
-          <t>signed score 80 | ['BULLISH terminate sell: an insider (?) [+18]', 'BULLISH terminate sell: an insider (director) 13,216sh [+18]', 'BULLISH terminate sell: an insider (?) 139,948sh [+26]', 'BULLISH terminate sell: an insider (director) 38,227sh [+18]']</t>
-        </is>
-      </c>
-      <c r="C86" s="20" t="inlineStr">
-        <is>
-          <t>SCHW</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>Charles Schwab Corporation (The</t>
-        </is>
-      </c>
-      <c r="E86" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="F86" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="31" t="inlineStr">
-        <is>
-          <t>Largest insider Form 4 dollar cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: insider conviction in dollars</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>$105.1M cluster, 2 buyers</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>BX</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E91" s="19" t="n">
-        <v>105122527.2</v>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="A92" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t>$100.5M cluster, 1 buyers (0.16% of mcap)</t>
-        </is>
-      </c>
-      <c r="C92" s="20" t="inlineStr">
-        <is>
-          <t>RSG</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>Republic Services, Inc.</t>
-        </is>
-      </c>
-      <c r="E92" s="21" t="n">
-        <v>100528322</v>
-      </c>
-      <c r="F92" s="15" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>$75.3M cluster, 7 buyers (9.57% of mcap)</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="inlineStr">
-        <is>
-          <t>ODTX</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>Odyssey Therapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="n">
-        <v>75319986</v>
-      </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="A94" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>$75.0M cluster, 1 buyers (20.80% of mcap)</t>
-        </is>
-      </c>
-      <c r="C94" s="20" t="inlineStr">
-        <is>
-          <t>ARTV</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>Artiva Biotherapeutics, Inc.</t>
-        </is>
-      </c>
-      <c r="E94" s="21" t="n">
-        <v>74999992.3</v>
-      </c>
-      <c r="F94" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>$74.0M cluster, 1 buyers (4.16% of mcap)</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
-        <is>
-          <t>WGS</t>
-        </is>
-      </c>
-      <c r="D95" s="10" t="inlineStr">
-        <is>
-          <t>GeneDx Holdings Corp.</t>
-        </is>
-      </c>
-      <c r="E95" s="19" t="n">
-        <v>74032163.40000001</v>
-      </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="A96" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>$65.9M cluster, 2 buyers (4.19% of mcap)</t>
-        </is>
-      </c>
-      <c r="C96" s="20" t="inlineStr">
-        <is>
-          <t>ALKT</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>Alkami Technology, Inc.</t>
-        </is>
-      </c>
-      <c r="E96" s="21" t="n">
-        <v>65859500</v>
-      </c>
-      <c r="F96" s="15" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>$54.4M cluster, 9 buyers</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E97" s="19" t="n">
-        <v>54366421.6</v>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="A98" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B98" s="15" t="inlineStr">
-        <is>
-          <t>$45.7M cluster, 5 buyers (0.05% of mcap)</t>
-        </is>
-      </c>
-      <c r="C98" s="20" t="inlineStr">
-        <is>
-          <t>KKR</t>
-        </is>
-      </c>
-      <c r="D98" s="15" t="inlineStr">
-        <is>
-          <t>KKR &amp; Co. Inc.</t>
-        </is>
-      </c>
-      <c r="E98" s="21" t="n">
-        <v>45684632.3</v>
-      </c>
-      <c r="F98" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="31" t="inlineStr">
-        <is>
-          <t>Live tender / 13E-3 events</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>What it measures: mechanical bid as floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E102" s="7" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="A103" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>SELF_TENDER | live event</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>EXFY</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>Expensify, Inc.</t>
-        </is>
-      </c>
-      <c r="E103" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" s="15" t="inlineStr">
-        <is>
-          <t>SELF_TENDER | live event</t>
-        </is>
-      </c>
-      <c r="C104" s="20" t="inlineStr">
-        <is>
-          <t>ABX</t>
-        </is>
-      </c>
-      <c r="D104" s="15" t="inlineStr">
-        <is>
-          <t>Abacus Global Management, Inc.</t>
-        </is>
-      </c>
-      <c r="E104" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F104" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>SELF_TENDER | live event</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>ABXL</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E105" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t>TARGET | live event</t>
-        </is>
-      </c>
-      <c r="C106" s="20" t="inlineStr">
-        <is>
-          <t>ASRT</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>Assertio Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="E106" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B107" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN | live event</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
-        <is>
-          <t>AUPH</t>
-        </is>
-      </c>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t>Aurinia Pharmaceuticals Inc</t>
-        </is>
-      </c>
-      <c r="E107" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="10" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B108" s="15" t="inlineStr">
-        <is>
-          <t>UNKNOWN | live event</t>
-        </is>
-      </c>
-      <c r="C108" s="20" t="inlineStr">
-        <is>
-          <t>BCIC</t>
-        </is>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>BCP Investment Corporation</t>
-        </is>
-      </c>
-      <c r="E108" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>SELF_TENDER | live event</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
-        <is>
-          <t>BCX</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>BlackRock Resources  of Benefic</t>
-        </is>
-      </c>
-      <c r="E109" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B110" s="15" t="inlineStr">
-        <is>
-          <t>SELF_TENDER | live event</t>
-        </is>
-      </c>
-      <c r="C110" s="20" t="inlineStr">
-        <is>
-          <t>BGY</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>Blackrock Enhanced Internationa</t>
-        </is>
-      </c>
-      <c r="E110" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="15" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>UNKNOWN | live event</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>BHC</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E111" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B112" s="15" t="inlineStr">
-        <is>
-          <t>BIDDER | live event</t>
-        </is>
-      </c>
-      <c r="C112" s="20" t="inlineStr">
-        <is>
-          <t>BIIB</t>
-        </is>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>Biogen Inc.</t>
-        </is>
-      </c>
-      <c r="E112" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="17" t="inlineStr">
-        <is>
-          <t>Each section ranks names by a SINGLE measure regardless of whether other layers fire. These are 'exceptional by one 'criterion' -- examples: ODTX archetype (insider cluster only), GETY (live self-tender only), CDE (CEO 10b5-1 termination only). Such names rarely appear in the consensus convergent list because they don't fire multiple layers, but they can be the right pick for a single-mandate position.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A65:F65"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6394,7 +6394,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1121</v>
+        <v>1105</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 5.792</t>
+          <t>9 layers firing | cons 6.088</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.736</t>
+          <t>8 layers firing | cons 6.768</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.54</t>
+          <t>8 layers firing | cons 6.626</t>
         </is>
       </c>
     </row>
@@ -7023,22 +7023,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ADT Inc</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.698</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -7048,22 +7048,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>8 layers firing | cons 5.336</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.902</t>
+          <t>7 layers firing | cons 5.812</t>
         </is>
       </c>
     </row>
@@ -7098,12 +7098,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>7 layers firing | cons 5.706</t>
         </is>
       </c>
     </row>
@@ -7148,22 +7148,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>GIII</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.52</t>
+          <t>7 layers firing | cons 5.398</t>
         </is>
       </c>
     </row>
@@ -7173,22 +7173,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.328</t>
         </is>
       </c>
     </row>
@@ -7198,22 +7198,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.124</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7223,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.012</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -7248,12 +7248,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.862</t>
+          <t>7 layers firing | cons 4.87</t>
         </is>
       </c>
     </row>
@@ -7273,22 +7273,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.856</t>
+          <t>7 layers firing | cons 4.85</t>
         </is>
       </c>
     </row>
@@ -7298,22 +7298,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7323,22 +7323,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.67</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7348,22 +7348,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.64</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7373,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.558</t>
+          <t>7 layers firing | cons 4.452</t>
         </is>
       </c>
     </row>
@@ -7398,22 +7398,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>MGPI</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.52</t>
+          <t>7 layers firing | cons 4.45</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 5.792</t>
+          <t>9 layers firing | cons 6.088</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.736</t>
+          <t>8 layers firing | cons 6.768</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.54</t>
+          <t>8 layers firing | cons 6.626</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7742,25 +7742,25 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>631</v>
+        <v>5004</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>15.29</v>
+        <v>6.58</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.76</v>
+        <v>1.38</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -7769,42 +7769,42 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.698</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5004</v>
+        <v>631</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>6.58</v>
+        <v>15.29</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1.38</v>
+        <v>0.76</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -7813,17 +7813,17 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>8 layers firing | cons 5.336</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.902</t>
+          <t>7 layers firing | cons 5.812</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -7874,39 +7874,39 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>244</v>
+        <v>1043</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>5.02</v>
+        <v>5.29</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>7 layers firing | cons 5.706</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -7962,25 +7962,25 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1043</v>
+        <v>1467</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>5.29</v>
+        <v>34.77</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.52</t>
+          <t>7 layers firing | cons 5.398</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -7997,175 +7997,175 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4158</v>
+        <v>1418</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>88.94</v>
+        <v>10.25</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2.44</v>
+        <v>0.57</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.328</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1418</v>
+        <v>4158</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>10.25</v>
+        <v>88.94</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.57</v>
+        <v>2.44</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.124</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>351</v>
+        <v>244</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>16.44</v>
+        <v>5.02</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.6</v>
+        <v>0.31</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.012</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1467</v>
+        <v>7252</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>34.77</v>
+        <v>198.99</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.862</t>
+          <t>7 layers firing | cons 4.87</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -8182,34 +8182,34 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>7252</v>
+        <v>399</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>198.99</v>
+        <v>1.65</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>6.4</v>
+        <v>-7.3</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.856</t>
+          <t>7 layers firing | cons 4.85</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8217,80 +8217,80 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>222</v>
+        <v>1474</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>5.27</v>
+        <v>25.03</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>862</v>
+        <v>222</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>5.54</v>
+        <v>5.27</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>29</v>
+        <v>0.93</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -8299,42 +8299,44 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.67</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1474</v>
+        <v>13781</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>25.03</v>
+        <v>121.36</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>27</v>
+        <v>2.85</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -8343,53 +8345,51 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.64</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>13781</v>
+        <v>1074</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>121.36</v>
+        <v>23.31</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.558</t>
+          <t>7 layers firing | cons 4.452</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8399,41 +8399,41 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>1.65</v>
+        <v>16.44</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>-7.3</v>
+        <v>0.6</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.52</t>
+          <t>7 layers firing | cons 4.45</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -8441,9 +8441,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12150,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.62</v>
+        <v>6.776</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>1</v>
@@ -12184,7 +12184,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.02</v>
+        <v>6.266</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>2</v>
@@ -12218,7 +12218,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.914</v>
+        <v>6.112</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-2</v>
@@ -12240,22 +12240,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.81</v>
+        <v>5.828</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:10 C10:-29 F4:18 RI:53</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12274,31 +12274,31 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.4</v>
+        <v>5.702</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:10 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -12308,31 +12308,31 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.396</v>
+        <v>5.524</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12342,22 +12342,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.21</v>
+        <v>5.432</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12376,31 +12376,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.146</v>
+        <v>5.25</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>-2</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -12410,22 +12410,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5.086</v>
+        <v>4.784</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -12444,31 +12444,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.704</v>
+        <v>4.694</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12490,10 +12490,10 @@
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.698</v>
+        <v>4.494</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -12524,10 +12524,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.446</v>
+        <v>5.36</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -12558,10 +12558,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>5.138</v>
+        <v>4.964</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -12580,31 +12580,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>IQVIA Holdings, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.904</v>
+        <v>4.926</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12614,31 +12614,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.864</v>
+        <v>4.834</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -12660,10 +12660,10 @@
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.786</v>
+        <v>4.79</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -12682,31 +12682,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.76</v>
+        <v>4.724</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>17</v>
+        <v>-8</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -12716,31 +12716,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.574</v>
+        <v>4.542</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-10</v>
+        <v>21</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -12762,10 +12762,10 @@
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.48</v>
+        <v>4.482</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -12784,31 +12784,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>IQVIA Holdings, Inc.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
         </is>
       </c>
     </row>
@@ -12818,31 +12818,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.342</v>
+        <v>4.364</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-12</v>
+        <v>26</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -12852,22 +12852,22 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.324</v>
+        <v>4.336</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>15</v>
+        <v>-6</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -12886,33 +12886,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>CarMax Inc</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.244</v>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.3</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>19</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:29</t>
+          <t>PSU:30 BB:8 RI:33</t>
         </is>
       </c>
     </row>
@@ -12922,22 +12920,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, LTD.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.22</v>
+        <v>4.268</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -12946,7 +12944,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:37 BB:5 RI:34</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -12968,7 +12966,7 @@
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.176</v>
+        <v>4.254</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>-3</v>
@@ -12990,31 +12988,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.126</v>
+        <v>4.032</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -13024,31 +13022,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.106</v>
+        <v>3.996</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -13058,31 +13056,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>MGP Ingredients, Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.084</v>
+        <v>3.954</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-15</v>
+        <v>9</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:30 RI:46</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -13092,31 +13090,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Insperity, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.016</v>
+        <v>3.934</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-17</v>
+        <v>25</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:43 F4:28 RI:40</t>
         </is>
       </c>
     </row>
@@ -13126,31 +13124,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Insperity, Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3.996</v>
+        <v>3.918</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>26</v>
+        <v>-11</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:43 F4:28 RI:40</t>
+          <t>PSU:29</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -186,6 +186,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -939,7 +942,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="20" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -981,7 +984,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1023,7 +1026,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1065,7 +1068,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1107,7 +1110,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1149,7 +1152,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1191,7 +1194,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2662,14 +2665,14 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Highest PSU forensic core</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>What it measures: depth + rigor of the PSU plan</t>
         </is>
@@ -2932,14 +2935,14 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Highest governance score</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
         </is>
@@ -3202,14 +3205,14 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Deepest P/B floor (&lt;0.5x book)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>What it measures: hard balance-sheet value floor</t>
         </is>
@@ -3472,14 +3475,14 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Cheapest EV/EBITDA (&lt;6x)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>What it measures: enterprise-value to earnings power</t>
         </is>
@@ -3742,14 +3745,14 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>Lowest trailing P/E (&lt;8x, positive)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>What it measures: earnings yield</t>
         </is>
@@ -4012,14 +4015,14 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>Largest verified buyback shrinkage</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="23" t="inlineStr">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>What it measures: actual supply curve compression</t>
         </is>
@@ -4282,14 +4285,14 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>Highest 10b5-1 termination signed score</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="23" t="inlineStr">
+      <c r="A77" s="24" t="inlineStr">
         <is>
           <t>What it measures: insider walked back scheduled selling</t>
         </is>
@@ -4552,14 +4555,14 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="A88" s="23" t="inlineStr">
         <is>
           <t>Largest insider Form 4 dollar cluster</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="23" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>What it measures: insider conviction in dollars</t>
         </is>
@@ -4822,14 +4825,14 @@
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="22" t="inlineStr">
+      <c r="A100" s="23" t="inlineStr">
         <is>
           <t>Live tender / 13E-3 events</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="23" t="inlineStr">
+      <c r="A101" s="24" t="inlineStr">
         <is>
           <t>What it measures: mechanical bid as floor</t>
         </is>
@@ -5298,7 +5301,7 @@
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0.67</v>
+        <v>0.667</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -5378,7 +5381,7 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.58</v>
+        <v>0.581</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -5578,7 +5581,7 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -5658,7 +5661,7 @@
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>0.272</v>
+        <v>0.274</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -5804,12 +5807,12 @@
       <c r="B5" s="16" t="n">
         <v>4410</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>71.54445165476963</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5832,12 +5835,12 @@
       <c r="B6" s="17" t="n">
         <v>4410</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="22" t="n">
         <v>71.54445165476963</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -5860,12 +5863,12 @@
       <c r="B7" s="16" t="n">
         <v>6164</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>15d</t>
+          <t>19d</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -5888,12 +5891,12 @@
       <c r="B8" s="17" t="n">
         <v>6164</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="22" t="n">
         <v>100</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -5916,12 +5919,12 @@
       <c r="B9" s="16" t="n">
         <v>2935</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="21" t="n">
         <v>47.61518494484101</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>16d</t>
+          <t>20d</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -5944,12 +5947,12 @@
       <c r="B10" s="17" t="n">
         <v>2807</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="22" t="n">
         <v>45.53861129136924</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>7d</t>
+          <t>11d</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -5972,12 +5975,12 @@
       <c r="B11" s="16" t="n">
         <v>1221</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>19.80856586632057</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>13d</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6000,12 +6003,12 @@
       <c r="B12" s="17" t="n">
         <v>346</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="22" t="n">
         <v>5.613238157040882</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>25d</t>
+          <t>30d</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -6028,12 +6031,12 @@
       <c r="B13" s="16" t="n">
         <v>346</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>5.613238157040882</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>10d</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -6056,7 +6059,7 @@
       <c r="B14" s="17" t="n">
         <v>164</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="22" t="n">
         <v>2.660609993510707</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -6084,12 +6087,12 @@
       <c r="B15" s="16" t="n">
         <v>260</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>4.218040233614536</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -6112,12 +6115,12 @@
       <c r="B16" s="17" t="n">
         <v>1982</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="22" t="n">
         <v>32.15444516547696</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -6140,12 +6143,12 @@
       <c r="B17" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="21" t="n">
         <v>19.14341336794289</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>5d</t>
+          <t>9d</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -6168,7 +6171,7 @@
       <c r="B18" s="17" t="n">
         <v>1167</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="22" t="n">
         <v>18.93251135626216</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -6196,7 +6199,7 @@
       <c r="B19" s="16" t="n">
         <v>46</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="21" t="n">
         <v>0.7462686567164178</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -6224,7 +6227,7 @@
       <c r="B20" s="17" t="n">
         <v>209</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="22" t="n">
         <v>3.390655418559377</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6252,7 +6255,7 @@
       <c r="B21" s="16" t="n">
         <v>71</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="21" t="n">
         <v>1.151849448410123</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -6280,12 +6283,12 @@
       <c r="B22" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="22" t="n">
         <v>0.4055807916937054</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4d</t>
+          <t>8d</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -6308,7 +6311,7 @@
       <c r="B23" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="21" t="n">
         <v>1.443867618429591</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -6420,7 +6423,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6436,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6446,7 +6449,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6459,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6553,7 +6556,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set. Foreign names (JP/KR/UK) live in a separate tab and universe.</t>
         </is>
@@ -6568,7 +6571,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>30 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, and financial-sector primary.</t>
         </is>
@@ -6583,7 +6586,7 @@
           <t>Additive discipline</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Every layer ADDS to the composite; none modifies another's score. New legs append fields; existing weights never change. This is enforced and audited (verify_universe_methodology.py).</t>
         </is>
@@ -6598,7 +6601,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Sparse-coverage names are not penalised for missing layers; the norm score rescales by sqrt(n_total/n_present) so a name strong on few layers competes with a name mediocre on many.</t>
         </is>
@@ -6613,7 +6616,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Top names in each catalyst pattern (forward $ hurdle, M&amp;A close, spin trigger, FDA/PDUFA, post-Ch11, asset sale, etc.) — surfaces single-mandate leaders (see Single-Measure tab).</t>
         </is>
@@ -6628,7 +6631,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe (PSU_ARCHETYPES.md 38 + ASYMMETRIC_BY_ARCHETYPE.md 19).</t>
         </is>
@@ -6643,7 +6646,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>n_layers_firing = how many of the 30 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
         </is>
@@ -6658,7 +6661,7 @@
           <t>Layer independence</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 30 raw layers to ~21 effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
         </is>
@@ -6673,7 +6676,7 @@
           <t>Freshness weighting</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>layer_freshness.json records each layer's data age. Most layers are &lt;14 days old. An optional age-decay multiplier (opt-in) can down-weight stale layers; current build reports age without auto-decaying.</t>
         </is>
@@ -6688,7 +6691,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Eight red-flag classes from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -6703,7 +6706,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean high-layer-count names. Material (2-5%): strong but 1-2 flags. Participation (0.5-2%): single-leg or multi-flag. Basket (&lt;1% each): sub-archetype groups, Cohen-Malloy stack, R2000-boundary, NOL shells, foreign.</t>
         </is>
@@ -6718,7 +6721,7 @@
           <t>Honest limitations</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>No realized-return backtest yet (AUDIT.md S1.1) — the composite is a structurally-sound pattern-recognition system, not yet validated alpha. Cohen-Malloy needs deeper Form 4 history. Coval-Stafford proxy supplements but does not replace the N-PORT real signal. See AUDIT.md for the full ledger.</t>
         </is>
@@ -6938,7 +6941,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.088</t>
+          <t>9 layers firing | cons 6.154</t>
         </is>
       </c>
     </row>
@@ -6948,22 +6951,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.768</t>
+          <t>8 layers firing | cons 6.876</t>
         </is>
       </c>
     </row>
@@ -6973,22 +6976,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.626</t>
+          <t>8 layers firing | cons 6.574</t>
         </is>
       </c>
     </row>
@@ -6998,22 +7001,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -7023,22 +7026,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7066,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.336</t>
+          <t>8 layers firing | cons 5.704</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7091,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.812</t>
+          <t>7 layers firing | cons 5.802</t>
         </is>
       </c>
     </row>
@@ -7098,12 +7101,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7113,7 +7116,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.706</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7123,22 +7126,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.522</t>
         </is>
       </c>
     </row>
@@ -7148,22 +7151,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Nu Skin</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.398</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7191,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.328</t>
+          <t>7 layers firing | cons 5.332</t>
         </is>
       </c>
     </row>
@@ -7198,22 +7201,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.26</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7226,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7248,22 +7251,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>CERT</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.87</t>
+          <t>7 layers firing | cons 5.002</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7291,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.85</t>
+          <t>7 layers firing | cons 4.94</t>
         </is>
       </c>
     </row>
@@ -7323,22 +7326,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7348,22 +7351,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.64</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7376,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.452</t>
+          <t>7 layers firing | cons 4.658</t>
         </is>
       </c>
     </row>
@@ -7398,12 +7401,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -7413,7 +7416,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.45</t>
+          <t>7 layers firing | cons 4.656</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7594,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.088</t>
+          <t>9 layers firing | cons 6.154</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7608,36 +7611,34 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>4180</v>
+        <v>4004</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>14.42</v>
+        <v>76.64</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+        <v>1.18</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>spin_separation</t>
-        </is>
-      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.768</t>
+          <t>8 layers firing | cons 6.876</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7645,43 +7646,45 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4004</v>
+        <v>4180</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>76.64</v>
+        <v>14.42</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.626</t>
+          <t>8 layers firing | cons 6.574</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7689,34 +7692,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>124308</v>
+        <v>5004</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>151.78</v>
+        <v>6.58</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>3.63</v>
+        <v>1.38</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -7725,42 +7728,42 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5004</v>
+        <v>124308</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>6.58</v>
+        <v>151.78</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>1.38</v>
+        <v>3.63</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -7769,17 +7772,17 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>Mega-cap recurring revenue base</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7816,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.336</t>
+          <t>8 layers firing | cons 5.704</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -7857,7 +7860,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.812</t>
+          <t>7 layers firing | cons 5.802</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -7874,39 +7877,39 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1043</v>
+        <v>4158</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>5.29</v>
+        <v>88.94</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>0.43</v>
+        <v>2.44</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.706</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -7918,25 +7921,25 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1394</v>
+        <v>1043</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>8.6</v>
+        <v>5.29</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -7945,61 +7948,61 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.522</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1467</v>
+        <v>244</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>34.77</v>
+        <v>5.02</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.398</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -8033,7 +8036,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.328</t>
+          <t>7 layers firing | cons 5.332</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -8050,122 +8053,122 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4158</v>
+        <v>7252</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>88.94</v>
+        <v>198.99</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.26</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>244</v>
+        <v>1394</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>5.02</v>
+        <v>8.6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.31</v>
+        <v>0.48</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>7252</v>
+        <v>862</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>198.99</v>
+        <v>5.54</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>6.4</v>
+        <v>0.84</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.87</t>
+          <t>7 layers firing | cons 5.002</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -8173,9 +8176,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -8209,7 +8212,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.85</t>
+          <t>7 layers firing | cons 4.94</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8270,68 +8273,66 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>222</v>
+        <v>32997</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>5.27</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
+        <v>10.04</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>13781</v>
+        <v>222</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>121.36</v>
+        <v>5.27</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2.85</v>
+        <v>0.93</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -8345,42 +8346,44 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.64</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1074</v>
+        <v>13781</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>23.31</v>
+        <v>121.36</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>34</v>
+        <v>2.85</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -8389,7 +8392,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.452</t>
+          <t>7 layers firing | cons 4.658</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8399,41 +8402,41 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>351</v>
+        <v>1467</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>16.44</v>
+        <v>34.77</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.45</t>
+          <t>7 layers firing | cons 4.656</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -12150,10 +12153,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.776</v>
+        <v>6.638</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -12184,10 +12187,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.266</v>
+        <v>6.198</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -12218,7 +12221,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6.112</v>
+        <v>5.748</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-2</v>
@@ -12240,22 +12243,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.828</v>
+        <v>6.116</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12264,7 +12267,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:10 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -12274,22 +12277,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.702</v>
+        <v>5.918</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12298,7 +12301,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:10 C10:-29 F4:18 RI:53</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12308,31 +12311,31 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.524</v>
+        <v>5.578</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12342,22 +12345,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.432</v>
+        <v>5.176</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -12366,7 +12369,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -12376,31 +12379,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.25</v>
+        <v>4.88</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12410,31 +12413,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.784</v>
+        <v>4.876</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12444,31 +12447,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.694</v>
+        <v>4.348</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -12490,10 +12493,10 @@
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.494</v>
+        <v>4.234</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -12524,10 +12527,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.36</v>
+        <v>5.314</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -12558,10 +12561,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.964</v>
+        <v>5.086</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -12592,10 +12595,10 @@
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.926</v>
+        <v>4.894</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -12614,31 +12617,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.834</v>
+        <v>4.876</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>-2</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -12648,31 +12651,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.79</v>
+        <v>4.732</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -12682,31 +12685,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>IQVIA Holdings, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.724</v>
+        <v>4.726</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-8</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
         </is>
       </c>
     </row>
@@ -12716,22 +12719,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.542</v>
+        <v>4.688</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>21</v>
+        <v>-9</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -12740,7 +12743,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12762,10 +12765,10 @@
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.482</v>
+        <v>4.61</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -12784,31 +12787,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>IQVIA Holdings, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.4</v>
+        <v>4.478</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -12818,31 +12821,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>CarMax Inc</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.364</v>
+        <v>4.458</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:30 BB:8 RI:33</t>
         </is>
       </c>
     </row>
@@ -12852,31 +12855,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.336</v>
+        <v>4.448</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-6</v>
+        <v>26</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -12886,22 +12889,22 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>CarMax Inc</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
@@ -12910,7 +12913,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 BB:8 RI:33</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -12920,31 +12923,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.268</v>
+        <v>4.314</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -12954,31 +12957,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.254</v>
+        <v>4.296</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-3</v>
+        <v>-15</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -13000,7 +13003,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.032</v>
+        <v>4.224</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>-15</v>
@@ -13022,31 +13025,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>3.996</v>
+        <v>4.144</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>17</v>
+        <v>-11</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -13056,22 +13059,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>3.954</v>
+        <v>4.126</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>9</v>
+        <v>-6</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
@@ -13080,7 +13083,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:29</t>
         </is>
       </c>
     </row>
@@ -13090,31 +13093,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Insperity, Inc.</t>
+          <t>MGP Ingredients, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>3.934</v>
+        <v>4.012</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>25</v>
+        <v>-8</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:43 F4:28 RI:40</t>
+          <t>PSU:30 RI:46</t>
         </is>
       </c>
     </row>
@@ -13124,31 +13127,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>TSEOF</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Trinseo PLC</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3.918</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>-11</v>
+        <v>4.01</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>66</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:29</t>
+          <t>PSU:17 C10:-10 RI:40 SS:55</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13285,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="20" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -13296,7 +13299,7 @@
       <c r="G5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="21" t="n">
         <v>44</v>
       </c>
       <c r="I5" s="16" t="n">
@@ -13322,7 +13325,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -13336,7 +13339,7 @@
       <c r="G6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="22" t="n">
         <v>96</v>
       </c>
       <c r="I6" s="17" t="n">
@@ -13362,7 +13365,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -13376,7 +13379,7 @@
       <c r="G7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="21" t="n">
         <v>78</v>
       </c>
       <c r="I7" s="16" t="n">
@@ -13402,7 +13405,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -13416,7 +13419,7 @@
       <c r="G8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="22" t="n">
         <v>70</v>
       </c>
       <c r="I8" s="17" t="n">
@@ -13442,7 +13445,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -13456,7 +13459,7 @@
       <c r="G9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>60</v>
       </c>
       <c r="I9" s="16" t="n">
@@ -13482,7 +13485,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -13496,7 +13499,7 @@
       <c r="G10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="22" t="n">
         <v>61</v>
       </c>
       <c r="I10" s="17" t="n">
@@ -13522,7 +13525,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -13536,7 +13539,7 @@
       <c r="G11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>96</v>
       </c>
       <c r="I11" s="16" t="n">
@@ -13562,7 +13565,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -13576,7 +13579,7 @@
       <c r="G12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="22" t="n">
         <v>49</v>
       </c>
       <c r="I12" s="17" t="n">
@@ -13602,7 +13605,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="20" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -13616,7 +13619,7 @@
       <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="21" t="n">
         <v>48</v>
       </c>
       <c r="I13" s="16" t="n">
@@ -13642,7 +13645,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="20" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -13656,7 +13659,7 @@
       <c r="G14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>86</v>
       </c>
       <c r="I14" s="17" t="n">
@@ -13682,7 +13685,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="20" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -13696,7 +13699,7 @@
       <c r="G15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="21" t="n">
         <v>36</v>
       </c>
       <c r="I15" s="16" t="n">
@@ -13722,7 +13725,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="20" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -13736,7 +13739,7 @@
       <c r="G16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H16" s="22" t="n">
         <v>63</v>
       </c>
       <c r="I16" s="17" t="n">
@@ -13762,7 +13765,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="20" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -13776,7 +13779,7 @@
       <c r="G17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="21" t="n">
         <v>39</v>
       </c>
       <c r="I17" s="16" t="n">
@@ -13802,7 +13805,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="20" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -13816,7 +13819,7 @@
       <c r="G18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="H18" s="22" t="n">
         <v>82</v>
       </c>
       <c r="I18" s="17" t="n">
@@ -13842,7 +13845,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="20" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -13856,7 +13859,7 @@
       <c r="G19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="21" t="n">
         <v>52</v>
       </c>
       <c r="I19" s="16" t="n">
@@ -13882,7 +13885,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="20" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -13896,7 +13899,7 @@
       <c r="G20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="21" t="n">
+      <c r="H20" s="22" t="n">
         <v>76</v>
       </c>
       <c r="I20" s="17" t="n">
@@ -13922,7 +13925,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="20" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -13936,7 +13939,7 @@
       <c r="G21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="21" t="n">
         <v>58</v>
       </c>
       <c r="I21" s="16" t="n">
@@ -13962,7 +13965,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="20" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -13976,7 +13979,7 @@
       <c r="G22" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="21" t="n">
+      <c r="H22" s="22" t="n">
         <v>45</v>
       </c>
       <c r="I22" s="17" t="n">
@@ -14002,7 +14005,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="20" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -14016,7 +14019,7 @@
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="21" t="n">
         <v>92</v>
       </c>
       <c r="I23" s="16" t="n">
@@ -14042,7 +14045,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="20" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -14056,7 +14059,7 @@
       <c r="G24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="21" t="n">
+      <c r="H24" s="22" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="17" t="n">
@@ -14082,7 +14085,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="20" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -14096,7 +14099,7 @@
       <c r="G25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="21" t="n">
         <v>31</v>
       </c>
       <c r="I25" s="16" t="n">
@@ -14122,7 +14125,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="20" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -14136,7 +14139,7 @@
       <c r="G26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="22" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="17" t="n">
@@ -14162,7 +14165,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="20" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="5" t="n">
@@ -14176,7 +14179,7 @@
       <c r="G27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="20" t="n">
+      <c r="H27" s="21" t="n">
         <v>72</v>
       </c>
       <c r="I27" s="16" t="n">
@@ -14202,7 +14205,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="20" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -14216,7 +14219,7 @@
       <c r="G28" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="H28" s="22" t="n">
         <v>66</v>
       </c>
       <c r="I28" s="17" t="n">
@@ -14242,7 +14245,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="20" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -14256,7 +14259,7 @@
       <c r="G29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="20" t="n">
+      <c r="H29" s="21" t="n">
         <v>84</v>
       </c>
       <c r="I29" s="16" t="n">
@@ -14282,7 +14285,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="20" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="8" t="n">
@@ -14296,7 +14299,7 @@
       <c r="G30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="21" t="n">
+      <c r="H30" s="22" t="n">
         <v>67</v>
       </c>
       <c r="I30" s="17" t="n">
@@ -14322,7 +14325,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="20" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -14336,7 +14339,7 @@
       <c r="G31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="20" t="n">
+      <c r="H31" s="21" t="n">
         <v>80</v>
       </c>
       <c r="I31" s="16" t="n">
@@ -14362,7 +14365,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="20" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="8" t="n">
@@ -14376,7 +14379,7 @@
       <c r="G32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="21" t="n">
+      <c r="H32" s="22" t="n">
         <v>45</v>
       </c>
       <c r="I32" s="17" t="n">
@@ -14402,7 +14405,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="20" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="5" t="n">
@@ -14416,7 +14419,7 @@
       <c r="G33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="20" t="n">
+      <c r="H33" s="21" t="n">
         <v>41</v>
       </c>
       <c r="I33" s="16" t="n">
@@ -14442,7 +14445,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="D34" s="20" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="8" t="n">
@@ -14456,7 +14459,7 @@
       <c r="G34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="H34" s="22" t="n">
         <v>37</v>
       </c>
       <c r="I34" s="17" t="n">
@@ -14482,7 +14485,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D35" s="20" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="5" t="n">
@@ -14496,7 +14499,7 @@
       <c r="G35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="20" t="n">
+      <c r="H35" s="21" t="n">
         <v>51</v>
       </c>
       <c r="I35" s="16" t="n">
@@ -14522,7 +14525,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="20" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="8" t="n">
@@ -14536,7 +14539,7 @@
       <c r="G36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="H36" s="22" t="n">
         <v>49</v>
       </c>
       <c r="I36" s="17" t="n">
@@ -14562,7 +14565,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="19" t="n">
+      <c r="D37" s="20" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="5" t="n">
@@ -14576,7 +14579,7 @@
       <c r="G37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="20" t="n">
+      <c r="H37" s="21" t="n">
         <v>25</v>
       </c>
       <c r="I37" s="16" t="n">
@@ -14602,7 +14605,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D38" s="20" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -14616,7 +14619,7 @@
       <c r="G38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="H38" s="22" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="17" t="n">
@@ -14642,7 +14645,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="20" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="5" t="n">
@@ -14656,7 +14659,7 @@
       <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="21" t="n">
         <v>29</v>
       </c>
       <c r="I39" s="16" t="n">
@@ -14682,7 +14685,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="19" t="n">
+      <c r="D40" s="20" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -14696,7 +14699,7 @@
       <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="21" t="n">
+      <c r="H40" s="22" t="n">
         <v>40</v>
       </c>
       <c r="I40" s="17" t="n">
@@ -14722,7 +14725,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="19" t="n">
+      <c r="D41" s="20" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="5" t="n">
@@ -14736,7 +14739,7 @@
       <c r="G41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="20" t="n">
+      <c r="H41" s="21" t="n">
         <v>57</v>
       </c>
       <c r="I41" s="16" t="n">
@@ -14762,7 +14765,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="19" t="n">
+      <c r="D42" s="20" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -14776,7 +14779,7 @@
       <c r="G42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="21" t="n">
+      <c r="H42" s="22" t="n">
         <v>55</v>
       </c>
       <c r="I42" s="17" t="n">
@@ -14816,7 +14819,7 @@
       <c r="G43" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="20" t="n">
+      <c r="H43" s="21" t="n">
         <v>87</v>
       </c>
       <c r="I43" s="16" t="n">
@@ -14856,7 +14859,7 @@
       <c r="G44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="21" t="n">
+      <c r="H44" s="22" t="n">
         <v>63</v>
       </c>
       <c r="I44" s="17" t="n">
@@ -14995,7 +14998,7 @@
       <c r="F5" s="16" t="n">
         <v>5.854111</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>11.4700004</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -15031,7 +15034,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="22" t="n">
         <v>-12.622</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -15065,7 +15068,7 @@
       <c r="F7" s="16" t="n">
         <v>6.5333333</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>4.2069998</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -15099,7 +15102,7 @@
       <c r="F8" s="17" t="n">
         <v>4.679035</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="22" t="n">
         <v>19.077998</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -15135,7 +15138,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>0.10899999</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -15169,7 +15172,7 @@
       <c r="F10" s="17" t="n">
         <v>17.51089</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="22" t="n">
         <v>6.4109996</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -15203,7 +15206,7 @@
       <c r="F11" s="16" t="n">
         <v>9.148345000000001</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>10.233</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -15239,7 +15242,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="22" t="n">
         <v>-2.8499998</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -15273,7 +15276,7 @@
       <c r="F13" s="16" t="n">
         <v>19.150717</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <v>3.3069998</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -15309,7 +15312,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <v>-9.856</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -15343,7 +15346,7 @@
       <c r="F15" s="16" t="n">
         <v>9.943130500000001</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="21" t="n">
         <v>8.282</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -15377,7 +15380,7 @@
       <c r="F16" s="17" t="n">
         <v>12.411422</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>8.5</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -15411,7 +15414,7 @@
       <c r="F17" s="16" t="n">
         <v>166.7683</v>
       </c>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="21" t="n">
         <v>0.75</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -15445,7 +15448,7 @@
       <c r="F18" s="17" t="n">
         <v>14.648475</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="22" t="n">
         <v>2.8110001</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -15479,7 +15482,7 @@
       <c r="F19" s="16" t="n">
         <v>10.444035</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="21" t="n">
         <v>7.056</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -15513,7 +15516,7 @@
       <c r="F20" s="17" t="n">
         <v>8.47991</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="22" t="n">
         <v>7.566000000000001</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -15547,7 +15550,7 @@
       <c r="F21" s="16" t="n">
         <v>7.682529</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G21" s="21" t="n">
         <v>12.528</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -15581,7 +15584,7 @@
       <c r="F22" s="17" t="n">
         <v>8.268003999999999</v>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="22" t="n">
         <v>12.644</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -15615,7 +15618,7 @@
       <c r="F23" s="16" t="n">
         <v>9.176824</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="21" t="n">
         <v>12.286</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -15649,7 +15652,7 @@
       <c r="F24" s="17" t="n">
         <v>9.315649000000001</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="22" t="n">
         <v>12.94</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -15683,7 +15686,7 @@
       <c r="F25" s="16" t="n">
         <v>6.766146</v>
       </c>
-      <c r="G25" s="20" t="n">
+      <c r="G25" s="21" t="n">
         <v>11.607</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -15721,7 +15724,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="22" t="n">
         <v>61.172</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -15759,7 +15762,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="21" t="n">
         <v>7.478999999999999</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -15797,7 +15800,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="22" t="n">
         <v>4.777</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -15835,7 +15838,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G29" s="20" t="n">
+      <c r="G29" s="21" t="n">
         <v>-5.933999999999999</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -15873,7 +15876,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="G30" s="22" t="n">
         <v>-2.5710002</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -15911,7 +15914,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="21" t="n">
         <v>5.252</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -15949,7 +15952,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="22" t="n">
         <v>7.2129995</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -15987,7 +15990,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G33" s="20" t="n">
+      <c r="G33" s="21" t="n">
         <v>2.609</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -16025,7 +16028,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="G34" s="22" t="n">
         <v>13.207</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -16063,7 +16066,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G35" s="20" t="n">
+      <c r="G35" s="21" t="n">
         <v>16.758</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -16097,7 +16100,7 @@
       <c r="F36" s="17" t="n">
         <v>7.927419</v>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="G36" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -16131,7 +16134,7 @@
       <c r="F37" s="16" t="n">
         <v>11.657143</v>
       </c>
-      <c r="G37" s="20" t="n">
+      <c r="G37" s="21" t="n">
         <v>7.823</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -16165,7 +16168,7 @@
       <c r="F38" s="17" t="n">
         <v>20.921429</v>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="G38" s="22" t="n">
         <v>3.918999799999999</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -16199,7 +16202,7 @@
       <c r="F39" s="16" t="n">
         <v>11.634099</v>
       </c>
-      <c r="G39" s="20" t="n">
+      <c r="G39" s="21" t="n">
         <v>7.754</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -16237,7 +16240,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G40" s="21" t="n">
+      <c r="G40" s="22" t="n">
         <v>18.855</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -16275,7 +16278,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G41" s="20" t="n">
+      <c r="G41" s="21" t="n">
         <v>7.539999999999999</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -16313,7 +16316,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G42" s="21" t="n">
+      <c r="G42" s="22" t="n">
         <v>1.125</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -16351,7 +16354,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G43" s="20" t="n">
+      <c r="G43" s="21" t="n">
         <v>9.097</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -16389,7 +16392,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G44" s="21" t="n">
+      <c r="G44" s="22" t="n">
         <v>8.518000000000001</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -16427,7 +16430,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G45" s="20" t="n">
+      <c r="G45" s="21" t="n">
         <v>9.991</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -16465,7 +16468,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G46" s="21" t="n">
+      <c r="G46" s="22" t="n">
         <v>18.855</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -16503,7 +16506,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G47" s="20" t="n">
+      <c r="G47" s="21" t="n">
         <v>3.85</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -16541,7 +16544,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G48" s="21" t="n">
+      <c r="G48" s="22" t="n">
         <v>7.2270006</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -16579,7 +16582,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G49" s="20" t="n">
+      <c r="G49" s="21" t="n">
         <v>18.671</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -16617,7 +16620,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G50" s="21" t="n">
+      <c r="G50" s="22" t="n">
         <v>14.094</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -16655,7 +16658,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G51" s="20" t="n">
+      <c r="G51" s="21" t="n">
         <v>6.414000000000001</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -16693,7 +16696,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G52" s="21" t="n">
+      <c r="G52" s="22" t="n">
         <v>10.064</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -16731,7 +16734,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G53" s="20" t="n">
+      <c r="G53" s="21" t="n">
         <v>7.435</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -16769,7 +16772,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G54" s="21" t="n">
+      <c r="G54" s="22" t="n">
         <v>21.757999</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -16807,7 +16810,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G55" s="20" t="n">
+      <c r="G55" s="21" t="n">
         <v>10.922</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -16845,7 +16848,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G56" s="21" t="n">
+      <c r="G56" s="22" t="n">
         <v>21.345</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -16879,7 +16882,7 @@
       <c r="F57" s="16" t="n">
         <v>12.022634</v>
       </c>
-      <c r="G57" s="20" t="n">
+      <c r="G57" s="21" t="n">
         <v>10.697</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -16913,7 +16916,7 @@
       <c r="F58" s="17" t="n">
         <v>29.628126</v>
       </c>
-      <c r="G58" s="21" t="n">
+      <c r="G58" s="22" t="n">
         <v>5.842</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -16947,7 +16950,7 @@
       <c r="F59" s="16" t="n">
         <v>20.560537</v>
       </c>
-      <c r="G59" s="20" t="n">
+      <c r="G59" s="21" t="n">
         <v>30.955</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -16981,7 +16984,7 @@
       <c r="F60" s="17" t="n">
         <v>15.749999</v>
       </c>
-      <c r="G60" s="21" t="n">
+      <c r="G60" s="22" t="n">
         <v>11.611</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -17015,7 +17018,7 @@
       <c r="F61" s="16" t="n">
         <v>27.900793</v>
       </c>
-      <c r="G61" s="20" t="n">
+      <c r="G61" s="21" t="n">
         <v>23.482999</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -17049,7 +17052,7 @@
       <c r="F62" s="17" t="n">
         <v>13.897888</v>
       </c>
-      <c r="G62" s="21" t="n">
+      <c r="G62" s="22" t="n">
         <v>40.905997</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -17083,7 +17086,7 @@
       <c r="F63" s="16" t="n">
         <v>13.429799</v>
       </c>
-      <c r="G63" s="20" t="n">
+      <c r="G63" s="21" t="n">
         <v>15.824</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -17117,7 +17120,7 @@
       <c r="F64" s="17" t="n">
         <v>12.046511</v>
       </c>
-      <c r="G64" s="21" t="n">
+      <c r="G64" s="22" t="n">
         <v>9.552</v>
       </c>
       <c r="H64" s="10" t="inlineStr">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Contents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cover" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Most Asymmetric" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="By Archetype" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Reserve Baskets" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Caution List" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Without Valuation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Recent 30d" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Foreign Markets" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Turnaround Signal" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Single-Measure Best" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Layer Correlation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Methodology" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Most Asymmetric" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Archetype" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reserve Baskets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Caution List" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Without Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recent 30d" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foreign Markets" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turnaround Signal" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single-Measure Best" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer Correlation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Tiers" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -186,9 +186,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -942,7 +939,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="19" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -984,7 +981,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="19" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1026,7 +1023,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1068,7 +1065,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="19" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1110,7 +1107,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="19" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1152,7 +1149,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="19" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1194,7 +1191,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="19" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2665,14 +2662,14 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Highest PSU forensic core</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>What it measures: depth + rigor of the PSU plan</t>
         </is>
@@ -2935,14 +2932,14 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Highest governance score</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
         </is>
@@ -3205,14 +3202,14 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>Deepest P/B floor (&lt;0.5x book)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>What it measures: hard balance-sheet value floor</t>
         </is>
@@ -3475,14 +3472,14 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="22" t="inlineStr">
         <is>
           <t>Cheapest EV/EBITDA (&lt;6x)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>What it measures: enterprise-value to earnings power</t>
         </is>
@@ -3745,14 +3742,14 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>Lowest trailing P/E (&lt;8x, positive)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>What it measures: earnings yield</t>
         </is>
@@ -4015,14 +4012,14 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="22" t="inlineStr">
         <is>
           <t>Largest verified buyback shrinkage</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>What it measures: actual supply curve compression</t>
         </is>
@@ -4285,14 +4282,14 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="23" t="inlineStr">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>Highest 10b5-1 termination signed score</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24" t="inlineStr">
+      <c r="A77" s="23" t="inlineStr">
         <is>
           <t>What it measures: insider walked back scheduled selling</t>
         </is>
@@ -4555,14 +4552,14 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="23" t="inlineStr">
+      <c r="A88" s="22" t="inlineStr">
         <is>
           <t>Largest insider Form 4 dollar cluster</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="23" t="inlineStr">
         <is>
           <t>What it measures: insider conviction in dollars</t>
         </is>
@@ -4825,14 +4822,14 @@
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="23" t="inlineStr">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>Live tender / 13E-3 events</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="inlineStr">
+      <c r="A101" s="23" t="inlineStr">
         <is>
           <t>What it measures: mechanical bid as floor</t>
         </is>
@@ -5223,7 +5220,7 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Raw layers: 30    Effective-independent (rho&gt;0.6): 25</t>
+          <t>Raw layers: 30    Effective-independent (rho&gt;0.6): 26</t>
         </is>
       </c>
     </row>
@@ -5272,16 +5269,16 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>f4_buys</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>0.696</v>
+        <v>0.667</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -5292,16 +5289,16 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>f4_buys</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>0.667</v>
+        <v>-0.652</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -5312,16 +5309,16 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>bumpitrage</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>-0.652</v>
+        <v>-0.623</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -5332,16 +5329,16 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>bumpitrage</t>
+          <t>quarterly_10q</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-0.623</v>
+        <v>0.601</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -5352,36 +5349,36 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0.601</v>
+        <v>0.581</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.581</v>
+        <v>0.515</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -5457,11 +5454,11 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.45</v>
+        <v>0.428</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -5472,7 +5469,7 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5481,7 +5478,7 @@
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>0.428</v>
+        <v>0.411</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -5492,56 +5489,56 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
           <t>voss_cic</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>coval_stafford</t>
-        </is>
-      </c>
       <c r="C19" s="16" t="n">
-        <v>0.417</v>
+        <v>0.365</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>coval_stafford</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.411</v>
+        <v>0.342</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>moderate</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -5552,16 +5549,16 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>special_sits</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0.342</v>
+        <v>0.301</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -5577,11 +5574,11 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -5592,16 +5589,16 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>special_sits</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>0.301</v>
+        <v>0.297</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -5612,16 +5609,16 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>odd_lot</t>
+          <t>financial_primary</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.281</v>
+        <v>0.275</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -5632,16 +5629,16 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>f4_buys</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>financial_primary</t>
+          <t>bb_insider_overlay</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
@@ -5652,16 +5649,16 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>f4_buys</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>bb_insider_overlay</t>
+          <t>quarterly_10q</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>0.274</v>
+        <v>0.265</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -5672,16 +5669,16 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>buyback</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>0.265</v>
+        <v>0.255</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -5692,16 +5689,16 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>buyback</t>
+          <t>odd_lot</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>0.255</v>
+        <v>0.251</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -5807,7 +5804,7 @@
       <c r="B5" s="16" t="n">
         <v>4410</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="20" t="n">
         <v>71.54445165476963</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -5835,7 +5832,7 @@
       <c r="B6" s="17" t="n">
         <v>4410</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="21" t="n">
         <v>71.54445165476963</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -5863,7 +5860,7 @@
       <c r="B7" s="16" t="n">
         <v>6164</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="20" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -5891,7 +5888,7 @@
       <c r="B8" s="17" t="n">
         <v>6164</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <v>100</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -5919,7 +5916,7 @@
       <c r="B9" s="16" t="n">
         <v>2935</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="20" t="n">
         <v>47.61518494484101</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -5947,7 +5944,7 @@
       <c r="B10" s="17" t="n">
         <v>2807</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="21" t="n">
         <v>45.53861129136924</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -5975,7 +5972,7 @@
       <c r="B11" s="16" t="n">
         <v>1221</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="20" t="n">
         <v>19.80856586632057</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -6003,7 +6000,7 @@
       <c r="B12" s="17" t="n">
         <v>346</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="21" t="n">
         <v>5.613238157040882</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -6031,7 +6028,7 @@
       <c r="B13" s="16" t="n">
         <v>346</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="20" t="n">
         <v>5.613238157040882</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -6059,7 +6056,7 @@
       <c r="B14" s="17" t="n">
         <v>164</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="21" t="n">
         <v>2.660609993510707</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -6087,7 +6084,7 @@
       <c r="B15" s="16" t="n">
         <v>260</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="20" t="n">
         <v>4.218040233614536</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -6115,7 +6112,7 @@
       <c r="B16" s="17" t="n">
         <v>1982</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="21" t="n">
         <v>32.15444516547696</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -6143,7 +6140,7 @@
       <c r="B17" s="16" t="n">
         <v>1180</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="20" t="n">
         <v>19.14341336794289</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -6169,10 +6166,10 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>1167</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>18.93251135626216</v>
+        <v>1142</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>18.52693056456846</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -6197,10 +6194,10 @@
         </is>
       </c>
       <c r="B19" s="16" t="n">
-        <v>46</v>
-      </c>
-      <c r="C19" s="21" t="n">
-        <v>0.7462686567164178</v>
+        <v>45</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>0.7300454250486696</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -6227,7 +6224,7 @@
       <c r="B20" s="17" t="n">
         <v>209</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="21" t="n">
         <v>3.390655418559377</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6255,7 +6252,7 @@
       <c r="B21" s="16" t="n">
         <v>71</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="20" t="n">
         <v>1.151849448410123</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -6281,10 +6278,10 @@
         </is>
       </c>
       <c r="B22" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.4055807916937054</v>
+        <v>19</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0.3082414016872161</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -6311,7 +6308,7 @@
       <c r="B23" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="20" t="n">
         <v>1.443867618429591</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -6384,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -6397,7 +6394,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6410,7 +6407,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6423,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6436,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6449,7 +6446,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6462,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1111</v>
+        <v>1092</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6556,7 +6553,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set. Foreign names (JP/KR/UK) live in a separate tab and universe.</t>
         </is>
@@ -6571,7 +6568,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>30 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, and financial-sector primary.</t>
         </is>
@@ -6586,7 +6583,7 @@
           <t>Additive discipline</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Every layer ADDS to the composite; none modifies another's score. New legs append fields; existing weights never change. This is enforced and audited (verify_universe_methodology.py).</t>
         </is>
@@ -6601,7 +6598,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Sparse-coverage names are not penalised for missing layers; the norm score rescales by sqrt(n_total/n_present) so a name strong on few layers competes with a name mediocre on many.</t>
         </is>
@@ -6616,7 +6613,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Top names in each catalyst pattern (forward $ hurdle, M&amp;A close, spin trigger, FDA/PDUFA, post-Ch11, asset sale, etc.) — surfaces single-mandate leaders (see Single-Measure tab).</t>
         </is>
@@ -6631,7 +6628,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe (PSU_ARCHETYPES.md 38 + ASYMMETRIC_BY_ARCHETYPE.md 19).</t>
         </is>
@@ -6646,7 +6643,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>n_layers_firing = how many of the 30 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
         </is>
@@ -6661,7 +6658,7 @@
           <t>Layer independence</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 30 raw layers to ~21 effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
         </is>
@@ -6676,7 +6673,7 @@
           <t>Freshness weighting</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>layer_freshness.json records each layer's data age. Most layers are &lt;14 days old. An optional age-decay multiplier (opt-in) can down-weight stale layers; current build reports age without auto-decaying.</t>
         </is>
@@ -6691,7 +6688,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Eight red-flag classes from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -6706,7 +6703,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean high-layer-count names. Material (2-5%): strong but 1-2 flags. Participation (0.5-2%): single-leg or multi-flag. Basket (&lt;1% each): sub-archetype groups, Cohen-Malloy stack, R2000-boundary, NOL shells, foreign.</t>
         </is>
@@ -6721,7 +6718,7 @@
           <t>Honest limitations</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>No realized-return backtest yet (AUDIT.md S1.1) — the composite is a structurally-sound pattern-recognition system, not yet validated alpha. Cohen-Malloy needs deeper Form 4 history. Coval-Stafford proxy supplements but does not replace the N-PORT real signal. See AUDIT.md for the full ledger.</t>
         </is>
@@ -6941,7 +6938,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.154</t>
+          <t>9 layers firing | cons 6.238</t>
         </is>
       </c>
     </row>
@@ -6951,22 +6948,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.876</t>
+          <t>8 layers firing | cons 6.756</t>
         </is>
       </c>
     </row>
@@ -6976,22 +6973,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.574</t>
+          <t>8 layers firing | cons 6.59</t>
         </is>
       </c>
     </row>
@@ -7001,22 +6998,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7026,22 +7023,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>8 layers firing | cons 5.512</t>
         </is>
       </c>
     </row>
@@ -7051,22 +7048,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ADT Inc</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.704</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7088,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.802</t>
+          <t>7 layers firing | cons 6.084</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7138,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.522</t>
+          <t>7 layers firing | cons 5.594</t>
         </is>
       </c>
     </row>
@@ -7176,22 +7173,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GIII</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.332</t>
+          <t>7 layers firing | cons 5.252</t>
         </is>
       </c>
     </row>
@@ -7201,22 +7198,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.26</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7226,22 +7223,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.174</t>
         </is>
       </c>
     </row>
@@ -7251,22 +7248,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.002</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7276,22 +7273,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>MGPI</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.94</t>
+          <t>7 layers firing | cons 4.868</t>
         </is>
       </c>
     </row>
@@ -7301,22 +7298,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.844</t>
         </is>
       </c>
     </row>
@@ -7326,12 +7323,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -7341,7 +7338,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7348,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -7366,7 +7363,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.666</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7373,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -7391,7 +7388,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.658</t>
+          <t>7 layers firing | cons 4.618</t>
         </is>
       </c>
     </row>
@@ -7401,12 +7398,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -7416,7 +7413,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.656</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7591,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.154</t>
+          <t>9 layers firing | cons 6.238</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7611,34 +7608,36 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>4004</v>
+        <v>4180</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>76.64</v>
+        <v>14.42</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.876</t>
+          <t>8 layers firing | cons 6.756</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7646,45 +7645,43 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4180</v>
+        <v>4004</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>14.42</v>
+        <v>76.64</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+        <v>1.18</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>spin_separation</t>
-        </is>
-      </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.574</t>
+          <t>8 layers firing | cons 6.59</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7692,34 +7689,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5004</v>
+        <v>124308</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>6.58</v>
+        <v>151.78</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.38</v>
+        <v>3.63</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -7728,42 +7725,42 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>Mega-cap recurring revenue base</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>124308</v>
+        <v>631</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>151.78</v>
+        <v>15.29</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>3.63</v>
+        <v>0.76</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -7772,42 +7769,42 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>8 layers firing | cons 5.512</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>631</v>
+        <v>5004</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>15.29</v>
+        <v>6.58</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.76</v>
+        <v>1.38</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -7816,17 +7813,17 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.704</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7857,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.802</t>
+          <t>7 layers firing | cons 6.084</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -7948,7 +7945,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.522</t>
+          <t>7 layers firing | cons 5.594</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -8009,25 +8006,25 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1418</v>
+        <v>1467</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>10.25</v>
+        <v>34.77</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -8036,7 +8033,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.332</t>
+          <t>7 layers firing | cons 5.252</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -8044,122 +8041,124 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>7252</v>
+        <v>1394</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>198.99</v>
+        <v>8.6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>6.4</v>
+        <v>0.48</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.26</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1394</v>
+        <v>7252</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>8.6</v>
+        <v>198.99</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.48</v>
+        <v>6.4</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.174</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>862</v>
+        <v>222</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>5.54</v>
+        <v>5.27</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>29</v>
+        <v>0.93</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -8168,51 +8167,51 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.002</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>1.65</v>
+        <v>16.44</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-7.3</v>
+        <v>0.6</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.94</t>
+          <t>7 layers firing | cons 4.868</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8220,34 +8219,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1474</v>
+        <v>1418</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>25.03</v>
+        <v>10.25</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -8256,42 +8255,42 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.844</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>32997</v>
+        <v>1474</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>78.70999999999999</v>
+        <v>25.03</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>10.04</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -8300,12 +8299,12 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -8317,41 +8316,39 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>222</v>
+        <v>399</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>5.27</v>
+        <v>1.65</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+        <v>-7.3</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.666</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -8363,36 +8360,34 @@
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>13781</v>
+        <v>862</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>121.36</v>
+        <v>5.54</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
+        <v>0.84</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.658</t>
+          <t>7 layers firing | cons 4.618</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8409,25 +8404,25 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1467</v>
+        <v>32997</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>34.77</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.8</v>
+        <v>10.04</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -8436,12 +8431,12 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.656</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J24" s="10" t="inlineStr">
@@ -12153,10 +12148,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.638</v>
+        <v>6.582</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -12175,22 +12170,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.198</v>
+        <v>6.116</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -12199,7 +12194,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -12209,22 +12204,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.748</v>
+        <v>6.006</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -12233,7 +12228,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 BB:5 F4:10 RI:51</t>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -12243,22 +12238,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>6.116</v>
+        <v>5.822</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12267,7 +12262,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:10 C10:-29 F4:18 RI:53</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12277,22 +12272,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.918</v>
+        <v>5.796</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12301,7 +12296,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:10 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -12311,22 +12306,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.578</v>
+        <v>5.792</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -12335,7 +12330,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12345,31 +12340,31 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.176</v>
+        <v>5.276</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>-1</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12379,31 +12374,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.88</v>
+        <v>5.066</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -12413,31 +12408,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.876</v>
+        <v>4.534</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-5</v>
+        <v>16</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -12447,31 +12442,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.348</v>
+        <v>4.494</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12481,31 +12476,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.234</v>
+        <v>4.478</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -12527,10 +12522,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.314</v>
+        <v>5.248</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -12549,31 +12544,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>5.086</v>
+        <v>4.912</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12583,31 +12578,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.894</v>
+        <v>4.802</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:12 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -12617,31 +12612,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.876</v>
+        <v>4.782</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -12651,31 +12646,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.732</v>
+        <v>4.75</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12685,31 +12680,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>IQVIA Holdings, Inc.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.726</v>
+        <v>4.732</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:43 RI:51 SS:21</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -12719,22 +12714,22 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.688</v>
+        <v>4.486</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-9</v>
+        <v>23</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -12743,7 +12738,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -12753,31 +12748,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.61</v>
+        <v>4.486</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:12 C10:-6 F4:16 RI:54</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -12787,31 +12782,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.478</v>
+        <v>4.462</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>18</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -12821,31 +12816,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>CarMax Inc</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.458</v>
+        <v>4.386</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 BB:8 RI:33</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -12855,31 +12850,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.448</v>
+        <v>4.366</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>26</v>
+        <v>-5</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -12889,31 +12884,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.43</v>
+        <v>4.326</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>11</v>
+        <v>-7</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -12923,31 +12918,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>G-III Apparel Group, LTD.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.314</v>
+        <v>4.228</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>16</v>
+        <v>-13</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:37 BB:5 RI:34</t>
         </is>
       </c>
     </row>
@@ -12957,31 +12952,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>American Assets Trust, Inc.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.296</v>
+        <v>4.196</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-15</v>
+        <v>35</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
         </is>
       </c>
     </row>
@@ -12991,31 +12986,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.224</v>
+        <v>4.168</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-15</v>
+        <v>18</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -13025,31 +13020,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.144</v>
+        <v>4.134</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -13059,22 +13054,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.126</v>
+        <v>4.074</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
@@ -13083,7 +13078,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:29</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -13093,31 +13088,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>MGP Ingredients, Inc.</t>
+          <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.012</v>
+        <v>4.022</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 RI:46</t>
+          <t>PSU:22 F4:5 RI:50</t>
         </is>
       </c>
     </row>
@@ -13127,31 +13122,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>TSEOF</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Trinseo PLC</t>
+          <t>TKO Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <v>66</v>
+        <v>4.012</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>33</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:17 C10:-10 RI:40 SS:55</t>
+          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13280,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="19" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -13299,7 +13294,7 @@
       <c r="G5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="H5" s="20" t="n">
         <v>44</v>
       </c>
       <c r="I5" s="16" t="n">
@@ -13325,7 +13320,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="19" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -13339,7 +13334,7 @@
       <c r="G6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="21" t="n">
         <v>96</v>
       </c>
       <c r="I6" s="17" t="n">
@@ -13365,7 +13360,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="19" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -13379,7 +13374,7 @@
       <c r="G7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="20" t="n">
         <v>78</v>
       </c>
       <c r="I7" s="16" t="n">
@@ -13405,7 +13400,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -13419,7 +13414,7 @@
       <c r="G8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="21" t="n">
         <v>70</v>
       </c>
       <c r="I8" s="17" t="n">
@@ -13445,7 +13440,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="19" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -13459,7 +13454,7 @@
       <c r="G9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="20" t="n">
         <v>60</v>
       </c>
       <c r="I9" s="16" t="n">
@@ -13485,7 +13480,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="19" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -13499,7 +13494,7 @@
       <c r="G10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="21" t="n">
         <v>61</v>
       </c>
       <c r="I10" s="17" t="n">
@@ -13525,7 +13520,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="19" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -13539,7 +13534,7 @@
       <c r="G11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="20" t="n">
         <v>96</v>
       </c>
       <c r="I11" s="16" t="n">
@@ -13565,7 +13560,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="19" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -13579,7 +13574,7 @@
       <c r="G12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="21" t="n">
         <v>49</v>
       </c>
       <c r="I12" s="17" t="n">
@@ -13605,7 +13600,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="19" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -13619,7 +13614,7 @@
       <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H13" s="20" t="n">
         <v>48</v>
       </c>
       <c r="I13" s="16" t="n">
@@ -13645,7 +13640,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="19" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -13659,7 +13654,7 @@
       <c r="G14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="21" t="n">
         <v>86</v>
       </c>
       <c r="I14" s="17" t="n">
@@ -13685,7 +13680,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="19" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -13699,7 +13694,7 @@
       <c r="G15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="20" t="n">
         <v>36</v>
       </c>
       <c r="I15" s="16" t="n">
@@ -13725,7 +13720,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -13739,7 +13734,7 @@
       <c r="G16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="21" t="n">
         <v>63</v>
       </c>
       <c r="I16" s="17" t="n">
@@ -13765,7 +13760,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="19" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -13779,7 +13774,7 @@
       <c r="G17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="H17" s="20" t="n">
         <v>39</v>
       </c>
       <c r="I17" s="16" t="n">
@@ -13805,7 +13800,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="19" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -13819,7 +13814,7 @@
       <c r="G18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="21" t="n">
         <v>82</v>
       </c>
       <c r="I18" s="17" t="n">
@@ -13845,7 +13840,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="19" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -13859,7 +13854,7 @@
       <c r="G19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="21" t="n">
+      <c r="H19" s="20" t="n">
         <v>52</v>
       </c>
       <c r="I19" s="16" t="n">
@@ -13885,7 +13880,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="19" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -13899,7 +13894,7 @@
       <c r="G20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="21" t="n">
         <v>76</v>
       </c>
       <c r="I20" s="17" t="n">
@@ -13925,7 +13920,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="19" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -13939,7 +13934,7 @@
       <c r="G21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="H21" s="20" t="n">
         <v>58</v>
       </c>
       <c r="I21" s="16" t="n">
@@ -13965,7 +13960,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="19" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -13979,7 +13974,7 @@
       <c r="G22" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="21" t="n">
         <v>45</v>
       </c>
       <c r="I22" s="17" t="n">
@@ -14005,7 +14000,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="19" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -14019,7 +14014,7 @@
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="21" t="n">
+      <c r="H23" s="20" t="n">
         <v>92</v>
       </c>
       <c r="I23" s="16" t="n">
@@ -14045,7 +14040,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="19" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -14059,7 +14054,7 @@
       <c r="G24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="H24" s="21" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="17" t="n">
@@ -14085,7 +14080,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="19" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -14099,7 +14094,7 @@
       <c r="G25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="21" t="n">
+      <c r="H25" s="20" t="n">
         <v>31</v>
       </c>
       <c r="I25" s="16" t="n">
@@ -14125,7 +14120,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="20" t="n">
+      <c r="D26" s="19" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -14139,7 +14134,7 @@
       <c r="G26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="21" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="17" t="n">
@@ -14165,7 +14160,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="19" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="5" t="n">
@@ -14179,7 +14174,7 @@
       <c r="G27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="21" t="n">
+      <c r="H27" s="20" t="n">
         <v>72</v>
       </c>
       <c r="I27" s="16" t="n">
@@ -14205,7 +14200,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="19" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -14219,7 +14214,7 @@
       <c r="G28" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="H28" s="21" t="n">
         <v>66</v>
       </c>
       <c r="I28" s="17" t="n">
@@ -14245,7 +14240,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="19" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -14259,7 +14254,7 @@
       <c r="G29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="21" t="n">
+      <c r="H29" s="20" t="n">
         <v>84</v>
       </c>
       <c r="I29" s="16" t="n">
@@ -14285,7 +14280,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="19" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="8" t="n">
@@ -14299,7 +14294,7 @@
       <c r="G30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="21" t="n">
         <v>67</v>
       </c>
       <c r="I30" s="17" t="n">
@@ -14325,7 +14320,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="19" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -14339,7 +14334,7 @@
       <c r="G31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="21" t="n">
+      <c r="H31" s="20" t="n">
         <v>80</v>
       </c>
       <c r="I31" s="16" t="n">
@@ -14365,7 +14360,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="19" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="8" t="n">
@@ -14379,7 +14374,7 @@
       <c r="G32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="H32" s="21" t="n">
         <v>45</v>
       </c>
       <c r="I32" s="17" t="n">
@@ -14405,7 +14400,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="19" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="5" t="n">
@@ -14419,7 +14414,7 @@
       <c r="G33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="21" t="n">
+      <c r="H33" s="20" t="n">
         <v>41</v>
       </c>
       <c r="I33" s="16" t="n">
@@ -14445,7 +14440,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="20" t="n">
+      <c r="D34" s="19" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="8" t="n">
@@ -14459,7 +14454,7 @@
       <c r="G34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="H34" s="21" t="n">
         <v>37</v>
       </c>
       <c r="I34" s="17" t="n">
@@ -14485,7 +14480,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="20" t="n">
+      <c r="D35" s="19" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="5" t="n">
@@ -14499,7 +14494,7 @@
       <c r="G35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="21" t="n">
+      <c r="H35" s="20" t="n">
         <v>51</v>
       </c>
       <c r="I35" s="16" t="n">
@@ -14525,7 +14520,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="20" t="n">
+      <c r="D36" s="19" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="8" t="n">
@@ -14539,7 +14534,7 @@
       <c r="G36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="22" t="n">
+      <c r="H36" s="21" t="n">
         <v>49</v>
       </c>
       <c r="I36" s="17" t="n">
@@ -14565,7 +14560,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="20" t="n">
+      <c r="D37" s="19" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="5" t="n">
@@ -14579,7 +14574,7 @@
       <c r="G37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="21" t="n">
+      <c r="H37" s="20" t="n">
         <v>25</v>
       </c>
       <c r="I37" s="16" t="n">
@@ -14605,7 +14600,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="19" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -14619,7 +14614,7 @@
       <c r="G38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="22" t="n">
+      <c r="H38" s="21" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="17" t="n">
@@ -14645,7 +14640,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="20" t="n">
+      <c r="D39" s="19" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="5" t="n">
@@ -14659,7 +14654,7 @@
       <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="21" t="n">
+      <c r="H39" s="20" t="n">
         <v>29</v>
       </c>
       <c r="I39" s="16" t="n">
@@ -14685,7 +14680,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="20" t="n">
+      <c r="D40" s="19" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -14699,7 +14694,7 @@
       <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="22" t="n">
+      <c r="H40" s="21" t="n">
         <v>40</v>
       </c>
       <c r="I40" s="17" t="n">
@@ -14725,7 +14720,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="19" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="5" t="n">
@@ -14739,7 +14734,7 @@
       <c r="G41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="21" t="n">
+      <c r="H41" s="20" t="n">
         <v>57</v>
       </c>
       <c r="I41" s="16" t="n">
@@ -14765,7 +14760,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="20" t="n">
+      <c r="D42" s="19" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -14779,7 +14774,7 @@
       <c r="G42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="22" t="n">
+      <c r="H42" s="21" t="n">
         <v>55</v>
       </c>
       <c r="I42" s="17" t="n">
@@ -14819,7 +14814,7 @@
       <c r="G43" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="21" t="n">
+      <c r="H43" s="20" t="n">
         <v>87</v>
       </c>
       <c r="I43" s="16" t="n">
@@ -14859,7 +14854,7 @@
       <c r="G44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="22" t="n">
+      <c r="H44" s="21" t="n">
         <v>63</v>
       </c>
       <c r="I44" s="17" t="n">
@@ -14998,7 +14993,7 @@
       <c r="F5" s="16" t="n">
         <v>5.854111</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="20" t="n">
         <v>11.4700004</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -15034,7 +15029,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="21" t="n">
         <v>-12.622</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -15068,7 +15063,7 @@
       <c r="F7" s="16" t="n">
         <v>6.5333333</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="20" t="n">
         <v>4.2069998</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -15102,7 +15097,7 @@
       <c r="F8" s="17" t="n">
         <v>4.679035</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="21" t="n">
         <v>19.077998</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -15138,7 +15133,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="20" t="n">
         <v>0.10899999</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -15172,7 +15167,7 @@
       <c r="F10" s="17" t="n">
         <v>17.51089</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="21" t="n">
         <v>6.4109996</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -15206,7 +15201,7 @@
       <c r="F11" s="16" t="n">
         <v>9.148345000000001</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="20" t="n">
         <v>10.233</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -15242,7 +15237,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="21" t="n">
         <v>-2.8499998</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -15276,7 +15271,7 @@
       <c r="F13" s="16" t="n">
         <v>19.150717</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="20" t="n">
         <v>3.3069998</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -15312,7 +15307,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="21" t="n">
         <v>-9.856</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
@@ -15346,7 +15341,7 @@
       <c r="F15" s="16" t="n">
         <v>9.943130500000001</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="20" t="n">
         <v>8.282</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -15380,7 +15375,7 @@
       <c r="F16" s="17" t="n">
         <v>12.411422</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="21" t="n">
         <v>8.5</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -15414,7 +15409,7 @@
       <c r="F17" s="16" t="n">
         <v>166.7683</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="20" t="n">
         <v>0.75</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -15448,7 +15443,7 @@
       <c r="F18" s="17" t="n">
         <v>14.648475</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="21" t="n">
         <v>2.8110001</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -15482,7 +15477,7 @@
       <c r="F19" s="16" t="n">
         <v>10.444035</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="20" t="n">
         <v>7.056</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
@@ -15516,7 +15511,7 @@
       <c r="F20" s="17" t="n">
         <v>8.47991</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="21" t="n">
         <v>7.566000000000001</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -15550,7 +15545,7 @@
       <c r="F21" s="16" t="n">
         <v>7.682529</v>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="20" t="n">
         <v>12.528</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -15584,7 +15579,7 @@
       <c r="F22" s="17" t="n">
         <v>8.268003999999999</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="21" t="n">
         <v>12.644</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -15618,7 +15613,7 @@
       <c r="F23" s="16" t="n">
         <v>9.176824</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="20" t="n">
         <v>12.286</v>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -15652,7 +15647,7 @@
       <c r="F24" s="17" t="n">
         <v>9.315649000000001</v>
       </c>
-      <c r="G24" s="22" t="n">
+      <c r="G24" s="21" t="n">
         <v>12.94</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -15686,7 +15681,7 @@
       <c r="F25" s="16" t="n">
         <v>6.766146</v>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="20" t="n">
         <v>11.607</v>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -15724,7 +15719,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="21" t="n">
         <v>61.172</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -15762,7 +15757,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="20" t="n">
         <v>7.478999999999999</v>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -15800,7 +15795,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="G28" s="21" t="n">
         <v>4.777</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -15838,7 +15833,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="20" t="n">
         <v>-5.933999999999999</v>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -15876,7 +15871,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="21" t="n">
         <v>-2.5710002</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -15914,7 +15909,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="20" t="n">
         <v>5.252</v>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -15952,7 +15947,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="21" t="n">
         <v>7.2129995</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -15990,7 +15985,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="20" t="n">
         <v>2.609</v>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -16028,7 +16023,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G34" s="22" t="n">
+      <c r="G34" s="21" t="n">
         <v>13.207</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -16066,7 +16061,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="G35" s="20" t="n">
         <v>16.758</v>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -16100,7 +16095,7 @@
       <c r="F36" s="17" t="n">
         <v>7.927419</v>
       </c>
-      <c r="G36" s="22" t="n">
+      <c r="G36" s="21" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -16134,7 +16129,7 @@
       <c r="F37" s="16" t="n">
         <v>11.657143</v>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="20" t="n">
         <v>7.823</v>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -16168,7 +16163,7 @@
       <c r="F38" s="17" t="n">
         <v>20.921429</v>
       </c>
-      <c r="G38" s="22" t="n">
+      <c r="G38" s="21" t="n">
         <v>3.918999799999999</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -16202,7 +16197,7 @@
       <c r="F39" s="16" t="n">
         <v>11.634099</v>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="G39" s="20" t="n">
         <v>7.754</v>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -16240,7 +16235,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G40" s="22" t="n">
+      <c r="G40" s="21" t="n">
         <v>18.855</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -16278,7 +16273,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G41" s="21" t="n">
+      <c r="G41" s="20" t="n">
         <v>7.539999999999999</v>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -16316,7 +16311,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G42" s="22" t="n">
+      <c r="G42" s="21" t="n">
         <v>1.125</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -16354,7 +16349,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G43" s="21" t="n">
+      <c r="G43" s="20" t="n">
         <v>9.097</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -16392,7 +16387,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G44" s="22" t="n">
+      <c r="G44" s="21" t="n">
         <v>8.518000000000001</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -16430,7 +16425,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G45" s="21" t="n">
+      <c r="G45" s="20" t="n">
         <v>9.991</v>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -16468,7 +16463,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G46" s="22" t="n">
+      <c r="G46" s="21" t="n">
         <v>18.855</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -16506,7 +16501,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G47" s="21" t="n">
+      <c r="G47" s="20" t="n">
         <v>3.85</v>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -16544,7 +16539,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G48" s="22" t="n">
+      <c r="G48" s="21" t="n">
         <v>7.2270006</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -16582,7 +16577,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G49" s="21" t="n">
+      <c r="G49" s="20" t="n">
         <v>18.671</v>
       </c>
       <c r="H49" s="7" t="inlineStr">
@@ -16620,7 +16615,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G50" s="22" t="n">
+      <c r="G50" s="21" t="n">
         <v>14.094</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -16658,7 +16653,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G51" s="21" t="n">
+      <c r="G51" s="20" t="n">
         <v>6.414000000000001</v>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -16696,7 +16691,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G52" s="22" t="n">
+      <c r="G52" s="21" t="n">
         <v>10.064</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -16734,7 +16729,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G53" s="21" t="n">
+      <c r="G53" s="20" t="n">
         <v>7.435</v>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -16772,7 +16767,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G54" s="22" t="n">
+      <c r="G54" s="21" t="n">
         <v>21.757999</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -16810,7 +16805,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G55" s="21" t="n">
+      <c r="G55" s="20" t="n">
         <v>10.922</v>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -16848,7 +16843,7 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G56" s="22" t="n">
+      <c r="G56" s="21" t="n">
         <v>21.345</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -16882,7 +16877,7 @@
       <c r="F57" s="16" t="n">
         <v>12.022634</v>
       </c>
-      <c r="G57" s="21" t="n">
+      <c r="G57" s="20" t="n">
         <v>10.697</v>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -16916,7 +16911,7 @@
       <c r="F58" s="17" t="n">
         <v>29.628126</v>
       </c>
-      <c r="G58" s="22" t="n">
+      <c r="G58" s="21" t="n">
         <v>5.842</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -16950,7 +16945,7 @@
       <c r="F59" s="16" t="n">
         <v>20.560537</v>
       </c>
-      <c r="G59" s="21" t="n">
+      <c r="G59" s="20" t="n">
         <v>30.955</v>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -16984,7 +16979,7 @@
       <c r="F60" s="17" t="n">
         <v>15.749999</v>
       </c>
-      <c r="G60" s="22" t="n">
+      <c r="G60" s="21" t="n">
         <v>11.611</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -17018,7 +17013,7 @@
       <c r="F61" s="16" t="n">
         <v>27.900793</v>
       </c>
-      <c r="G61" s="21" t="n">
+      <c r="G61" s="20" t="n">
         <v>23.482999</v>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -17052,7 +17047,7 @@
       <c r="F62" s="17" t="n">
         <v>13.897888</v>
       </c>
-      <c r="G62" s="22" t="n">
+      <c r="G62" s="21" t="n">
         <v>40.905997</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -17086,7 +17081,7 @@
       <c r="F63" s="16" t="n">
         <v>13.429799</v>
       </c>
-      <c r="G63" s="21" t="n">
+      <c r="G63" s="20" t="n">
         <v>15.824</v>
       </c>
       <c r="H63" s="7" t="inlineStr">
@@ -17120,7 +17115,7 @@
       <c r="F64" s="17" t="n">
         <v>12.046511</v>
       </c>
-      <c r="G64" s="22" t="n">
+      <c r="G64" s="21" t="n">
         <v>9.552</v>
       </c>
       <c r="H64" s="10" t="inlineStr">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -5809,7 +5809,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>19d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>20d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>11d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>13d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>30d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>10d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>9d</t>
+          <t>1d</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>8d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -6381,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.238</t>
+          <t>9 layers firing | cons 6.604</t>
         </is>
       </c>
     </row>
@@ -6948,22 +6948,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.756</t>
+          <t>8 layers firing | cons 6.726</t>
         </is>
       </c>
     </row>
@@ -6973,22 +6973,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.59</t>
+          <t>8 layers firing | cons 6.698</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.512</t>
+          <t>8 layers firing | cons 5.848</t>
         </is>
       </c>
     </row>
@@ -7073,22 +7073,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.084</t>
+          <t>7 layers firing | cons 5.678</t>
         </is>
       </c>
     </row>
@@ -7098,22 +7098,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.402</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.594</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7173,22 +7173,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>GIII</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.252</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7198,22 +7198,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.058</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.174</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7248,22 +7248,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.934</t>
         </is>
       </c>
     </row>
@@ -7273,22 +7273,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.868</t>
+          <t>7 layers firing | cons 4.828</t>
         </is>
       </c>
     </row>
@@ -7298,22 +7298,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.844</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7323,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.696</t>
         </is>
       </c>
     </row>
@@ -7348,12 +7348,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.666</t>
+          <t>7 layers firing | cons 4.628</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.618</t>
+          <t>7 layers firing | cons 4.548</t>
         </is>
       </c>
     </row>
@@ -7398,22 +7398,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.238</t>
+          <t>9 layers firing | cons 6.604</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7608,36 +7608,34 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>4180</v>
+        <v>4004</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>14.42</v>
+        <v>76.64</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+        <v>1.18</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>spin_separation</t>
-        </is>
-      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.756</t>
+          <t>8 layers firing | cons 6.726</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7645,43 +7643,45 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4004</v>
+        <v>4180</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>76.64</v>
+        <v>14.42</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.59</t>
+          <t>8 layers firing | cons 6.698</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7689,9 +7689,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.512</t>
+          <t>8 layers firing | cons 5.848</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -7830,25 +7830,25 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9011</v>
+        <v>1043</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>176.03</v>
+        <v>5.29</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>4.58</v>
+        <v>0.43</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.084</t>
+          <t>7 layers firing | cons 5.678</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -7867,90 +7867,90 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4158</v>
+        <v>9011</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>88.94</v>
+        <v>176.03</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2.44</v>
+        <v>4.58</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.402</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1043</v>
+        <v>4158</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>5.29</v>
+        <v>88.94</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.43</v>
+        <v>2.44</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.594</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -8006,25 +8006,25 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1467</v>
+        <v>1394</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>34.77</v>
+        <v>8.6</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.8</v>
+        <v>0.48</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -8033,100 +8033,100 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.252</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1394</v>
+        <v>7252</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>8.6</v>
+        <v>198.99</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.48</v>
+        <v>6.4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 5.058</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>7252</v>
+        <v>32997</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>198.99</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>6.4</v>
+        <v>10.04</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.174</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -8138,80 +8138,78 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>222</v>
+        <v>862</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>5.27</v>
+        <v>5.54</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+        <v>0.84</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.934</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>351</v>
+        <v>1418</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>16.44</v>
+        <v>10.25</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.868</t>
+          <t>7 layers firing | cons 4.828</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8219,34 +8217,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1418</v>
+        <v>1474</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>10.25</v>
+        <v>25.03</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -8255,56 +8253,56 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.844</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1474</v>
+        <v>351</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>25.03</v>
+        <v>16.44</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.696</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -8316,25 +8314,25 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>ANGI</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>399</v>
+        <v>203</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>1.65</v>
+        <v>5.02</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>-7.3</v>
+        <v>0.22</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -8343,7 +8341,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.666</t>
+          <t>7 layers firing | cons 4.628</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -8360,25 +8358,25 @@
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>862</v>
+        <v>981</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>5.54</v>
+        <v>32.58</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -8387,7 +8385,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.618</t>
+          <t>7 layers firing | cons 4.548</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8404,25 +8402,27 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>32997</v>
+        <v>222</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>78.70999999999999</v>
+        <v>5.27</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>10</v>
+        <v>0.93</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -8431,17 +8431,17 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>FUBO</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FUBO</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>BCO</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>TROX</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>GRND</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>GRND</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -11421,12 +11421,12 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, repricing language</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
@@ -11444,12 +11444,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>LCII</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>INFU</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>LCII</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>INFU</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
@@ -11582,12 +11582,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>DCH</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
@@ -11674,7 +11674,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>OI</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>repricing language, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>front-loaded grant, retirement carveout</t>
+          <t>retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>BLMN</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
@@ -11881,12 +11881,12 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -11904,12 +11904,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>front-loaded grant, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>NVCR</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C55" s="16" t="n">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
@@ -12019,17 +12019,63 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
+          <t>discretionary hurdle, front-loaded grant</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>NVCR</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
           <t>discretionary hurdle, single-trigger CIC</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Eight flag classes: single-trigger CIC, repricing language, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural variants. Counter-intuitive: a 'repricing language' flag can become a re-rate catalyst when a stock has fallen sharply, since management becomes incentivised to reset hurdles. Read the flag in context, not as automatic veto.</t>
         </is>
@@ -12038,8 +12084,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A60:E60"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -12148,10 +12194,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.582</v>
+        <v>6.662</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -12182,7 +12228,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.116</v>
+        <v>6.418</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>-1</v>
@@ -12216,7 +12262,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6.006</v>
+        <v>6.044</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1</v>
@@ -12238,19 +12284,19 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.822</v>
+        <v>6.03</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>4</v>
@@ -12262,7 +12308,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12284,10 +12330,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.796</v>
+        <v>5.982</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12306,31 +12352,33 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.792</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>5.48</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12340,31 +12388,31 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.276</v>
+        <v>5.396</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12434,7 @@
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.066</v>
+        <v>4.938</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>-3</v>
@@ -12408,31 +12456,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.534</v>
+        <v>4.842</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12442,31 +12490,31 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.494</v>
+        <v>4.686</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -12476,31 +12524,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.478</v>
+        <v>3.882</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -12522,10 +12570,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.248</v>
+        <v>5.184</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -12544,31 +12592,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.912</v>
+        <v>4.75</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>22</v>
+        <v>-6</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12578,31 +12626,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.802</v>
+        <v>4.73</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:12 C10:-6 F4:16 RI:54</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12612,31 +12660,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.782</v>
+        <v>4.664</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-5</v>
+        <v>27</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -12646,31 +12694,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.75</v>
+        <v>4.636</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-7</v>
+        <v>24</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>PSU:12 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -12680,31 +12728,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.732</v>
+        <v>4.608</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>26</v>
+        <v>-7</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -12714,31 +12762,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.486</v>
+        <v>4.598</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>23</v>
+        <v>-5</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -12748,31 +12796,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>CarMax Inc</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.486</v>
+        <v>4.586</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-5</v>
+        <v>38</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:30 BB:8 RI:33</t>
         </is>
       </c>
     </row>
@@ -12782,31 +12830,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.462</v>
+        <v>4.55</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-8</v>
+        <v>31</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -12816,31 +12864,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.386</v>
+        <v>4.442</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>17</v>
+        <v>-1</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -12850,31 +12898,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>American Assets Trust, Inc.</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.366</v>
+        <v>4.398</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-5</v>
+        <v>24</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
         </is>
       </c>
     </row>
@@ -12884,31 +12932,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.326</v>
+        <v>4.304</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>-7</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -12918,31 +12966,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, LTD.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.228</v>
+        <v>4.246</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-13</v>
+        <v>28</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:37 BB:5 RI:34</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -12952,31 +13000,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>American Assets Trust, Inc.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.196</v>
+        <v>4.22</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -12986,31 +13034,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.168</v>
+        <v>4.152</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>18</v>
+        <v>-15</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -13020,22 +13068,22 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.134</v>
+        <v>4.004</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
@@ -13044,7 +13092,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:29</t>
         </is>
       </c>
     </row>
@@ -13054,22 +13102,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.074</v>
+        <v>3.994</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-8</v>
+        <v>19</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
@@ -13078,7 +13126,7 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -13088,31 +13136,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Vitesse Energy, Inc.</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.022</v>
+        <v>3.978</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:22 F4:5 RI:50</t>
+          <t>PSU:28 BB:5 C10:28 RI:23</t>
         </is>
       </c>
     </row>
@@ -13122,31 +13170,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>TKO Group Holdings, Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.012</v>
+        <v>3.978</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>33</v>
+        <v>-15</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6381,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1098</v>
+        <v>1108</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.604</t>
+          <t>9 layers firing | cons 6.564</t>
         </is>
       </c>
     </row>
@@ -6948,22 +6948,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.726</t>
+          <t>8 layers firing | cons 6.644</t>
         </is>
       </c>
     </row>
@@ -6973,22 +6973,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.698</t>
+          <t>8 layers firing | cons 6.616</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.848</t>
+          <t>8 layers firing | cons 5.93</t>
         </is>
       </c>
     </row>
@@ -7073,12 +7073,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.678</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.402</t>
+          <t>7 layers firing | cons 5.868</t>
         </is>
       </c>
     </row>
@@ -7148,22 +7148,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>7 layers firing | cons 5.608</t>
         </is>
       </c>
     </row>
@@ -7173,22 +7173,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7198,22 +7198,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.058</t>
+          <t>7 layers firing | cons 5.454</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7223,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.284</t>
         </is>
       </c>
     </row>
@@ -7248,22 +7248,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.934</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.828</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7298,22 +7298,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 5.014</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.696</t>
+          <t>7 layers firing | cons 4.882</t>
         </is>
       </c>
     </row>
@@ -7348,22 +7348,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.628</t>
+          <t>7 layers firing | cons 4.818</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7373,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>CNMD</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.548</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7398,22 +7398,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>OPCH</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.558</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.604</t>
+          <t>9 layers firing | cons 6.564</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7608,34 +7608,36 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>4004</v>
+        <v>4180</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>76.64</v>
+        <v>14.42</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.726</t>
+          <t>8 layers firing | cons 6.644</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7643,45 +7645,43 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4180</v>
+        <v>4004</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>14.42</v>
+        <v>76.64</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+        <v>1.18</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>spin_separation</t>
-        </is>
-      </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.698</t>
+          <t>8 layers firing | cons 6.616</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7689,9 +7689,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.848</t>
+          <t>8 layers firing | cons 5.93</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -7830,39 +7830,39 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1043</v>
+        <v>244</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5.29</v>
+        <v>5.02</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.678</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.402</t>
+          <t>7 layers firing | cons 5.868</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -7962,122 +7962,122 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>244</v>
+        <v>7252</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>5.02</v>
+        <v>198.99</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.31</v>
+        <v>6.4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>7 layers firing | cons 5.608</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1394</v>
+        <v>101</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>8.6</v>
+        <v>1.89</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>7252</v>
+        <v>1043</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>198.99</v>
+        <v>5.29</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>6.4</v>
+        <v>0.43</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.058</t>
+          <t>7 layers firing | cons 5.454</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -8085,34 +8085,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>32997</v>
+        <v>1418</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>78.70999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>10.04</v>
+        <v>0.57</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -8121,42 +8121,44 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.284</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>862</v>
+        <v>222</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>5.54</v>
+        <v>5.27</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>29</v>
+        <v>0.93</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -8165,42 +8167,42 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.934</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1418</v>
+        <v>1394</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>10.25</v>
+        <v>8.6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -8209,12 +8211,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.828</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -8226,25 +8228,25 @@
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1474</v>
+        <v>399</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>25.03</v>
+        <v>1.65</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>-7.3</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -8253,17 +8255,17 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 5.014</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8299,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.696</t>
+          <t>7 layers firing | cons 4.882</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -8314,25 +8316,25 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>ANGI</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>203</v>
+        <v>20670</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>5.02</v>
+        <v>43.7</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.22</v>
+        <v>1.37</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -8341,7 +8343,7 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.628</t>
+          <t>7 layers firing | cons 4.818</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -8351,32 +8353,32 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>981</v>
+        <v>1474</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>32.58</v>
+        <v>25.03</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.97</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -8385,63 +8387,61 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.548</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>222</v>
+        <v>3453</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>5.27</v>
+        <v>21.99</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
+        <v>2.56</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.558</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -8618,14 +8618,14 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>117806</v>
+        <v>4080</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>15.69</v>
+        <v>1.94</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -9021,14 +9021,14 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="E20" s="8" t="n">
-        <v>5004</v>
+        <v>1180</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>1.38</v>
+        <v>0.92</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -9083,14 +9083,14 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>RNR</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="E22" s="8" t="n">
-        <v>12755</v>
+        <v>1180</v>
       </c>
       <c r="F22" s="17" t="n">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -9114,14 +9114,14 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>40924</v>
+        <v>25522</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>12.82</v>
+        <v>0.97</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBI</t>
+          <t>HPP</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>204</v>
+        <v>6422</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
@@ -9424,14 +9424,14 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>14011</v>
+        <v>2519</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>10.15</v>
+        <v>0.67</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
@@ -9486,14 +9486,14 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HPP</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1394</v>
+        <v>6422</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
@@ -9548,14 +9548,14 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1474</v>
+        <v>25522</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BCO</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>OSUR</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>repricing language, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>GRNT</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>GRNT</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11183,20 +11183,20 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11206,20 +11206,20 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>TROX</t>
+          <t>GRND</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>GRND</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>discretionary hurdle, repricing language</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>single-trigger CIC</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>LCII</t>
+          <t>DCH</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>HAIN</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>LCII</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>FCN</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>ECPG</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
+          <t>retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
+          <t>repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
@@ -11858,12 +11858,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>BLMN</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
@@ -11881,12 +11881,12 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>front-loaded grant, retirement carveout</t>
+          <t>discretionary hurdle, front-loaded grant</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>OI</t>
         </is>
       </c>
       <c r="C55" s="16" t="n">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>repricing language, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>NVCR</t>
+          <t>HOG</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -12194,10 +12194,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.662</v>
+        <v>6.65</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.418</v>
+        <v>6.452</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>-1</v>
@@ -12262,7 +12262,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6.044</v>
+        <v>6.192</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>1</v>
@@ -12284,22 +12284,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>6.03</v>
+        <v>5.694</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:10 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -12318,22 +12318,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.982</v>
+        <v>5.492</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:10 C10:-29 F4:18 RI:53</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.48</v>
+        <v>5.4</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -12388,22 +12388,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.396</v>
+        <v>5.398</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12422,31 +12422,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.938</v>
+        <v>5.286</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12456,31 +12456,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.842</v>
+        <v>4.97</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -12502,10 +12502,10 @@
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.686</v>
+        <v>4.81</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -12524,31 +12524,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3.882</v>
+        <v>4.646</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -12558,31 +12558,31 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Grocery Outlet Holding Corp.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.184</v>
+        <v>4.058</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>PSU:38 F4:28 RI:38</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -12592,31 +12592,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Grocery Outlet Holding Corp.</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.75</v>
+        <v>5.148</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-6</v>
+        <v>19</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>PSU:38 F4:28 RI:38</t>
         </is>
       </c>
     </row>
@@ -12626,31 +12626,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.73</v>
+        <v>4.85</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>21</v>
+        <v>-7</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -12660,22 +12660,22 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.664</v>
+        <v>4.844</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>27</v>
+        <v>-3</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12706,10 +12706,10 @@
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.636</v>
+        <v>4.724</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -12728,31 +12728,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.608</v>
+        <v>4.71</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -12762,31 +12762,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.598</v>
+        <v>4.71</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-5</v>
+        <v>21</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12796,31 +12796,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>CarMax Inc</t>
+          <t>HF Foods Group Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.586</v>
+        <v>4.696</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>38</v>
+        <v>-8</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 BB:8 RI:33</t>
+          <t>PSU:48 F4:18 RI:59 SS:20</t>
         </is>
       </c>
     </row>
@@ -12830,31 +12830,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.55</v>
+        <v>4.626</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>31</v>
+        <v>-6</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -12864,31 +12864,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.442</v>
+        <v>4.562</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -12898,31 +12898,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>AAT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>American Assets Trust, Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.398</v>
+        <v>4.426</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>24</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -12932,31 +12932,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.304</v>
+        <v>4.364</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-7</v>
+        <v>13</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -12966,31 +12966,31 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.246</v>
+        <v>4.34</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>28</v>
+        <v>-3</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:21 BB:5 C10:-12 RI:43</t>
         </is>
       </c>
     </row>
@@ -13000,22 +13000,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>KMX</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>CarMax Inc</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:30 BB:8 RI:33</t>
         </is>
       </c>
     </row>
@@ -13034,31 +13034,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.152</v>
+        <v>4.128</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-15</v>
+        <v>23</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -13068,31 +13068,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Cognizant Technology Solutions</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.004</v>
+        <v>4.122</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:29</t>
+          <t>PSU:33 BB:5 RI:32</t>
         </is>
       </c>
     </row>
@@ -13102,31 +13102,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>BrightView Holdings, Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>3.994</v>
+        <v>4.076</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>19</v>
+        <v>-2</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:3 BB:5 RI:44 SS:29</t>
         </is>
       </c>
     </row>
@@ -13136,31 +13136,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>3.978</v>
+        <v>4.076</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>-10</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:28 BB:5 C10:28 RI:23</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -13170,31 +13170,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3.978</v>
+        <v>4.06</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-15</v>
+        <v>14</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -5809,7 +5809,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -6381,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1108</v>
+        <v>1100</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.564</t>
+          <t>9 layers firing | cons 6.162</t>
         </is>
       </c>
     </row>
@@ -6948,22 +6948,22 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>EPAM</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.644</t>
+          <t>8 layers firing | cons 7.054</t>
         </is>
       </c>
     </row>
@@ -6973,22 +6973,22 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GPGI</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.616</t>
+          <t>8 layers firing | cons 6.554</t>
         </is>
       </c>
     </row>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.93</t>
+          <t>8 layers firing | cons 5.958</t>
         </is>
       </c>
     </row>
@@ -7048,22 +7048,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7073,22 +7073,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>7 layers firing | cons 6.012</t>
         </is>
       </c>
     </row>
@@ -7098,12 +7098,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.868</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7148,22 +7148,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.608</t>
+          <t>7 layers firing | cons 5.432</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.454</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.284</t>
+          <t>7 layers firing | cons 5.226</t>
         </is>
       </c>
     </row>
@@ -7248,22 +7248,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 5.172</t>
         </is>
       </c>
     </row>
@@ -7273,22 +7273,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7298,22 +7298,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>MGPI</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.014</t>
+          <t>7 layers firing | cons 4.68</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7323,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.882</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7348,22 +7348,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>CTSH</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.818</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7373,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>CNMD</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.474</t>
         </is>
       </c>
     </row>
@@ -7398,22 +7398,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>OPCH</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.558</t>
+          <t>7 layers firing | cons 4.464</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.564</t>
+          <t>9 layers firing | cons 6.162</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7608,36 +7608,34 @@
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>4180</v>
+        <v>4004</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>14.42</v>
+        <v>76.64</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
+        <v>1.18</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>spin_separation</t>
-        </is>
-      </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.644</t>
+          <t>8 layers firing | cons 7.054</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7645,43 +7643,45 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>GPGI</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4004</v>
+        <v>4180</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>76.64</v>
+        <v>14.42</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>14</v>
+        <v>1.34</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.616</t>
+          <t>8 layers firing | cons 6.554</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7689,34 +7689,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>124308</v>
+        <v>5004</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>151.78</v>
+        <v>6.58</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>3.63</v>
+        <v>1.38</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -7725,17 +7725,17 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.93</t>
+          <t>8 layers firing | cons 5.958</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -7786,25 +7786,25 @@
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5004</v>
+        <v>124308</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>6.58</v>
+        <v>151.78</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1.38</v>
+        <v>3.63</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -7813,86 +7813,86 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>Mega-cap recurring revenue base</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>244</v>
+        <v>9011</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5.02</v>
+        <v>176.03</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.31</v>
+        <v>4.58</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>7 layers firing | cons 6.012</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>9011</v>
+        <v>1394</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>176.03</v>
+        <v>8.6</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.58</v>
+        <v>0.48</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.868</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -7918,25 +7918,25 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>4158</v>
+        <v>101</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>88.94</v>
+        <v>1.89</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>2.44</v>
+        <v>0.49</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -7945,12 +7945,12 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -7962,34 +7962,34 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>7252</v>
+        <v>1043</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>198.99</v>
+        <v>5.29</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>6.4</v>
+        <v>0.43</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.608</t>
+          <t>7 layers firing | cons 5.432</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -7997,34 +7997,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>101</v>
+        <v>4158</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1.89</v>
+        <v>88.94</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.49</v>
+        <v>2.44</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -8050,39 +8050,39 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1043</v>
+        <v>244</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>5.29</v>
+        <v>5.02</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.454</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.284</t>
+          <t>7 layers firing | cons 5.226</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -8138,71 +8138,71 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>222</v>
+        <v>7252</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>5.27</v>
+        <v>198.99</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.4</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 5.172</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1394</v>
+        <v>222</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>8.6</v>
+        <v>5.27</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>43</v>
+        <v>0.93</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -8211,51 +8211,51 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>399</v>
+        <v>351</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>1.65</v>
+        <v>16.44</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>-7.3</v>
+        <v>0.6</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.014</t>
+          <t>7 layers firing | cons 4.68</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -8263,48 +8263,48 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>351</v>
+        <v>32997</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>16.44</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.6</v>
+        <v>10.04</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.882</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -8316,25 +8316,25 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>20670</v>
+        <v>1474</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>43.7</v>
+        <v>25.03</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>1.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -8343,42 +8343,42 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.818</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1474</v>
+        <v>981</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>25.03</v>
+        <v>32.58</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -8387,42 +8387,42 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.474</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>3453</v>
+        <v>399</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>21.99</v>
+        <v>1.65</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>2.56</v>
+        <v>-7.3</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.558</t>
+          <t>7 layers firing | cons 4.464</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -8439,9 +8439,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -10776,7 +10776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -10884,20 +10884,20 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>GETY</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
@@ -10938,12 +10938,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>FUBO</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
@@ -10984,12 +10984,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>OSUR</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>repricing language, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>BCO</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>GRNT</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C17" s="16" t="n">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, repricing language</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>discretionary hurdle, front-loaded grant</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -11183,20 +11183,20 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>GRNT</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11206,20 +11206,20 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11229,20 +11229,20 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>TROX</t>
+          <t>AIN</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>GRND</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
@@ -11306,12 +11306,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
+          <t>repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>GPRO</t>
+          <t>GETY</t>
         </is>
       </c>
       <c r="C28" s="17" t="n">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -11421,12 +11421,12 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>FUBO</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
@@ -11467,12 +11467,12 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>discretionary hurdle, repricing language</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
@@ -11559,12 +11559,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11574,7 +11574,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>INFU</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>DCH</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>HAIN</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>LCII</t>
+          <t>TBI</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CNH</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
@@ -11697,12 +11697,12 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GRND</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>FCN</t>
+          <t>JTAI</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>ECPG</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>PTLO</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -11812,12 +11812,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
@@ -11835,7 +11835,7 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>UNFI</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>GPGI</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>front-loaded grant, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="C55" s="16" t="n">
@@ -11996,12 +11996,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>HOG</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>SKIN</t>
         </is>
       </c>
       <c r="C58" s="17" t="n">
@@ -12065,17 +12065,178 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Watch only — multi-flag stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>HOG</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>TCBK</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
           <t>discretionary hurdle, single-trigger CIC</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>MERC</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
         <is>
           <t>Eight flag classes: single-trigger CIC, repricing language, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural variants. Counter-intuitive: a 'repricing language' flag can become a re-rate catalyst when a stock has fallen sharply, since management becomes incentivised to reset hurdles. Read the flag in context, not as automatic veto.</t>
         </is>
@@ -12085,7 +12246,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A67:E67"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -12194,10 +12355,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.65</v>
+        <v>6.702</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
@@ -12216,22 +12377,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.452</v>
+        <v>5.974</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -12240,7 +12401,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>PSU:30 BB:5 F4:10 RI:51</t>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -12250,22 +12411,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>6.192</v>
+        <v>5.866</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -12274,7 +12435,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -12296,10 +12457,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.694</v>
+        <v>6.218</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12330,10 +12491,10 @@
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.492</v>
+        <v>5.888</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12352,33 +12513,31 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>5.64</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12388,22 +12547,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.398</v>
+        <v>5.438</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -12412,7 +12571,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -12422,22 +12581,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.286</v>
+        <v>5.32</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -12446,7 +12605,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12456,31 +12615,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.97</v>
+        <v>4.972</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12502,10 +12661,10 @@
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.81</v>
+        <v>4.868</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -12524,31 +12683,31 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>lululemon athletica inc.</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.646</v>
+        <v>4.52</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
         </is>
       </c>
     </row>
@@ -12558,31 +12717,31 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>lululemon athletica inc.</t>
+          <t>Grocery Outlet Holding Corp.</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>4.058</v>
+        <v>5.136</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>PSU:1 BB:8 C10:-40 F4:11 RI:41 SS:10</t>
+          <t>PSU:38 F4:28 RI:38</t>
         </is>
       </c>
     </row>
@@ -12592,31 +12751,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Grocery Outlet Holding Corp.</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>5.148</v>
+        <v>4.866</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>19</v>
+        <v>-3</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU:38 F4:28 RI:38</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12626,31 +12785,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.85</v>
+        <v>4.66</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -12660,31 +12819,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.844</v>
+        <v>4.622</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-3</v>
+        <v>21</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>PSU:12 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -12694,31 +12853,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.724</v>
+        <v>4.61</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:12 C10:-6 F4:16 RI:54</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12728,31 +12887,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.71</v>
+        <v>4.588</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -12762,31 +12921,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.71</v>
+        <v>4.488</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -12796,31 +12955,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>HF Foods Group Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.696</v>
+        <v>4.48</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-8</v>
+        <v>29</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 F4:18 RI:59 SS:20</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -12830,31 +12989,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>G-III Apparel Group, LTD.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.626</v>
+        <v>4.404</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:37 BB:5 RI:34</t>
         </is>
       </c>
     </row>
@@ -12864,31 +13023,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.562</v>
+        <v>4.374</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -12910,10 +13069,10 @@
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.426</v>
+        <v>4.374</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -12932,31 +13091,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.364</v>
+        <v>4.258</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>13</v>
+        <v>-11</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -12966,22 +13125,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.34</v>
+        <v>4.184</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -12990,7 +13149,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:21 BB:5 C10:-12 RI:43</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -13000,31 +13159,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>KMX</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>CarMax Inc</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.3</v>
+        <v>4.182</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 BB:8 RI:33</t>
+          <t>PSU:29</t>
         </is>
       </c>
     </row>
@@ -13034,31 +13193,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.128</v>
+        <v>4.106</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:21 BB:5 C10:-12 RI:43</t>
         </is>
       </c>
     </row>
@@ -13080,10 +13239,10 @@
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.122</v>
+        <v>4.102</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-9</v>
+        <v>10</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
@@ -13102,31 +13261,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>BrightView Holdings, Inc.</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.076</v>
+        <v>4.04</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 RI:44 SS:29</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -13136,31 +13295,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.076</v>
+        <v>3.92</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>-10</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:28 BB:5 C10:28 RI:23</t>
         </is>
       </c>
     </row>
@@ -13182,10 +13341,10 @@
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.06</v>
+        <v>3.92</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -5190,7 +5190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.853</v>
+        <v>0.783</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -5289,16 +5289,16 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>bumpitrage</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>-0.652</v>
+        <v>-0.623</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -5309,16 +5309,16 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>bumpitrage</t>
+          <t>quarterly_10q</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>-0.623</v>
+        <v>0.601</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -5329,20 +5329,20 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.601</v>
+        <v>-0.598</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -5686,28 +5686,8 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>tender</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>odd_lot</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Spearman rank correlation across the full universe. Pairs above rho 0.6 are folded into a single effective layer for the independence count: PSU + Voss CIC (Voss derives from the PSU plan), the tender family (tender + mechanism + bumpitrage share one source), and Form 4 + opportunistic insiders (one refines the other). A high raw layer-firing count should be read against this: nine layers firing is closer to seven or eight genuinely independent confirmations.</t>
         </is>
@@ -5717,7 +5697,7 @@
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -5809,7 +5789,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5837,7 +5817,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -5865,7 +5845,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -5893,7 +5873,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -5921,7 +5901,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -5949,7 +5929,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -5977,7 +5957,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6005,7 +5985,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -6033,7 +6013,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -6089,7 +6069,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -6117,7 +6097,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -6145,7 +6125,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>1d</t>
+          <t>3d</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -6285,7 +6265,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>0d</t>
+          <t>2d</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -6368,7 +6348,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -6381,7 +6361,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -6394,7 +6374,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6407,7 +6387,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6420,7 +6400,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6433,7 +6413,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6446,7 +6426,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6459,7 +6439,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1100</v>
+        <v>1110</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6938,7 +6918,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.162</t>
+          <t>9 layers firing | cons 6.498</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6943,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 7.054</t>
+          <t>8 layers firing | cons 6.848</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6968,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.554</t>
+          <t>8 layers firing | cons 6.628</t>
         </is>
       </c>
     </row>
@@ -6998,22 +6978,22 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7023,22 +7003,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.958</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7048,22 +7028,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -7073,22 +7053,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.012</t>
+          <t>8 layers firing | cons 5.698</t>
         </is>
       </c>
     </row>
@@ -7098,12 +7078,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -7113,7 +7093,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 6.038</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7103,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -7138,7 +7118,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7128,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -7163,7 +7143,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.432</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7153,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -7188,7 +7168,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.52</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7178,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -7213,7 +7193,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7223,22 +7203,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.226</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7248,12 +7228,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -7263,7 +7243,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.172</t>
+          <t>7 layers firing | cons 4.866</t>
         </is>
       </c>
     </row>
@@ -7273,22 +7253,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.844</t>
         </is>
       </c>
     </row>
@@ -7298,12 +7278,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -7313,7 +7293,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.68</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7323,22 +7303,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.68</t>
         </is>
       </c>
     </row>
@@ -7348,22 +7328,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.67</t>
         </is>
       </c>
     </row>
@@ -7373,22 +7353,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>CNMD</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>GIII</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.474</t>
+          <t>7 layers firing | cons 4.648</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7393,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.464</t>
+          <t>7 layers firing | cons 4.636</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7571,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.162</t>
+          <t>9 layers firing | cons 6.498</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7635,7 +7615,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 7.054</t>
+          <t>8 layers firing | cons 6.848</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7681,7 +7661,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.554</t>
+          <t>8 layers firing | cons 6.628</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7698,22 +7678,22 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5004</v>
+        <v>1394</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>6.58</v>
+        <v>8.6</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.38</v>
+        <v>0.48</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>43</v>
@@ -7725,42 +7705,42 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>631</v>
+        <v>124308</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>15.29</v>
+        <v>151.78</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.76</v>
+        <v>3.63</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -7769,42 +7749,42 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.958</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Mega-cap recurring revenue base</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>124308</v>
+        <v>5004</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>151.78</v>
+        <v>6.58</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>3.63</v>
+        <v>1.38</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -7813,42 +7793,42 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9011</v>
+        <v>631</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>176.03</v>
+        <v>15.29</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>4.58</v>
+        <v>0.76</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -7857,7 +7837,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.012</t>
+          <t>8 layers firing | cons 5.698</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -7865,34 +7845,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1394</v>
+        <v>9011</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>8.6</v>
+        <v>176.03</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>0.48</v>
+        <v>4.58</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -7901,12 +7881,12 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>7 layers firing | cons 6.038</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -7918,25 +7898,25 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>101</v>
+        <v>4158</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>1.89</v>
+        <v>88.94</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.49</v>
+        <v>2.44</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -7945,12 +7925,12 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -7962,39 +7942,39 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1043</v>
+        <v>244</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>5.29</v>
+        <v>5.02</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.432</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -8006,39 +7986,39 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4158</v>
+        <v>1043</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>88.94</v>
+        <v>5.29</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>2.44</v>
+        <v>0.43</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.52</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -8050,39 +8030,41 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>5.02</v>
+        <v>5.27</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>40</v>
+        <v>0.93</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -8094,25 +8076,25 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1418</v>
+        <v>1474</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>10.25</v>
+        <v>25.03</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -8121,51 +8103,51 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.226</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>7252</v>
+        <v>351</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>198.99</v>
+        <v>16.44</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>22</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.172</t>
+          <t>7 layers firing | cons 4.866</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -8182,85 +8164,83 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>222</v>
+        <v>7252</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>5.27</v>
+        <v>198.99</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>6.4</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 4.844</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>351</v>
+        <v>32997</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>16.44</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.6</v>
+        <v>10.04</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.68</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
@@ -8272,25 +8252,25 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>32997</v>
+        <v>1418</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>78.70999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>10.04</v>
+        <v>0.57</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -8299,42 +8279,44 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.68</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1474</v>
+        <v>13781</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>25.03</v>
+        <v>121.36</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>27</v>
+        <v>2.85</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -8343,42 +8325,42 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>7 layers firing | cons 4.67</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>981</v>
+        <v>1467</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>32.58</v>
+        <v>34.77</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -8387,7 +8369,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.474</t>
+          <t>7 layers firing | cons 4.648</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8395,9 +8377,9 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8413,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.464</t>
+          <t>7 layers firing | cons 4.636</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -10776,7 +10758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10884,7 +10866,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
@@ -10892,7 +10874,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>discretionary hurdle, single-trigger CIC</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -10907,20 +10889,20 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>MAT</t>
+          <t>BCO</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -10930,20 +10912,20 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -10953,20 +10935,20 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>DXLG</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -10976,20 +10958,20 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -10999,20 +10981,20 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>GRNT</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11004,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>MAT</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
@@ -11045,7 +11027,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>BCO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
@@ -11053,12 +11035,12 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11050,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>DXLG</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -11091,7 +11073,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>OSUR</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
@@ -11099,7 +11081,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+          <t>repricing language, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -11137,7 +11119,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
@@ -11145,12 +11127,12 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11142,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
@@ -11168,7 +11150,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -11183,7 +11165,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>GRNT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
@@ -11191,12 +11173,12 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11188,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SOLS</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
@@ -11214,12 +11196,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, front-loaded grant</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11229,20 +11211,20 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11234,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TROX</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
@@ -11260,12 +11242,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11275,7 +11257,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>TROX</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
@@ -11283,12 +11265,12 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11303,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
@@ -11329,12 +11311,12 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11326,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>BEEP</t>
+          <t>GPRO</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
@@ -11390,7 +11372,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BEEP</t>
         </is>
       </c>
       <c r="C29" s="16" t="n">
@@ -11398,12 +11380,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11395,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -11421,12 +11403,12 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11418,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
@@ -11444,12 +11426,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11441,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>FUBO</t>
+          <t>WHR</t>
         </is>
       </c>
       <c r="C32" s="17" t="n">
@@ -11467,12 +11449,12 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11464,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>WHR</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
@@ -11490,12 +11472,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11505,7 +11487,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -11513,12 +11495,12 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11510,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
@@ -11536,7 +11518,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>discretionary hurdle, repricing language</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -11551,7 +11533,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
@@ -11574,7 +11556,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="C37" s="16" t="n">
@@ -11582,12 +11564,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11579,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>DCH</t>
+          <t>GRND</t>
         </is>
       </c>
       <c r="C38" s="17" t="n">
@@ -11605,12 +11587,12 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11602,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
@@ -11628,7 +11610,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
+          <t>retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -11643,7 +11625,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TBI</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
@@ -11651,12 +11633,12 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11648,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>TBI</t>
+          <t>BHF</t>
         </is>
       </c>
       <c r="C41" s="16" t="n">
@@ -11689,7 +11671,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>CNH</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C42" s="17" t="n">
@@ -11712,7 +11694,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>GRND</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C43" s="16" t="n">
@@ -11720,7 +11702,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>discretionary hurdle, repricing language</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -11735,7 +11717,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -11758,7 +11740,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>LCID</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -11766,12 +11748,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, front-loaded grant, repricing language, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11763,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -11804,7 +11786,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>PTLO</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -11812,12 +11794,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11809,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DCH</t>
         </is>
       </c>
       <c r="C48" s="17" t="n">
@@ -11835,12 +11817,12 @@
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11832,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>AUPH</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C49" s="16" t="n">
@@ -11858,12 +11840,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11873,7 +11855,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>JTAI</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
@@ -11881,12 +11863,12 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11878,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>UNFI</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -11904,12 +11886,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11901,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>BUSE</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C52" s="17" t="n">
@@ -11942,7 +11924,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>AUPH</t>
         </is>
       </c>
       <c r="C53" s="16" t="n">
@@ -11950,12 +11932,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>front-loaded grant, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11947,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>TCBK</t>
         </is>
       </c>
       <c r="C54" s="17" t="n">
@@ -11973,12 +11955,12 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11970,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="C55" s="16" t="n">
@@ -11996,7 +11978,7 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -12011,7 +11993,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
@@ -12034,7 +12016,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
@@ -12042,12 +12024,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12039,7 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>SKIN</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C58" s="17" t="n">
@@ -12065,7 +12047,7 @@
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -12080,7 +12062,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>SOLS</t>
         </is>
       </c>
       <c r="C59" s="16" t="n">
@@ -12088,12 +12070,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12085,7 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>ACH</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="C60" s="17" t="n">
@@ -12111,12 +12093,12 @@
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12108,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>HOG</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="C61" s="16" t="n">
@@ -12134,12 +12116,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12131,7 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>TCBK</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="C62" s="17" t="n">
@@ -12157,12 +12139,12 @@
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12154,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>BUSE</t>
         </is>
       </c>
       <c r="C63" s="16" t="n">
@@ -12180,12 +12162,12 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12177,7 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>RPAY</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="C64" s="17" t="n">
@@ -12203,12 +12185,12 @@
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12200,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>MERC</t>
+          <t>AIN</t>
         </is>
       </c>
       <c r="C65" s="16" t="n">
@@ -12226,17 +12208,155 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>IDCC</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>CINF</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Watch only — multi-flag stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>discretionary hurdle, front-loaded grant, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>MERC</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
           <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>Participation — limited size</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>NXT</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>Eight flag classes: single-trigger CIC, repricing language, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural variants. Counter-intuitive: a 'repricing language' flag can become a re-rate catalyst when a stock has fallen sharply, since management becomes incentivised to reset hurdles. Read the flag in context, not as automatic veto.</t>
         </is>
@@ -12246,7 +12366,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A73:E73"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -12355,7 +12475,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.702</v>
+        <v>6.778</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -12377,22 +12497,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>5.974</v>
+        <v>6.37</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -12401,7 +12521,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -12411,22 +12531,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.866</v>
+        <v>5.924</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -12435,7 +12555,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU:30 BB:5 F4:10 RI:51</t>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -12445,22 +12565,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>6.218</v>
+        <v>5.84</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12469,7 +12589,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:10 C10:-29 F4:18 RI:53</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12479,22 +12599,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.888</v>
+        <v>5.788</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12503,7 +12623,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:10 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -12513,22 +12633,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.64</v>
+        <v>5.578</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -12537,7 +12657,7 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12547,31 +12667,31 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.438</v>
+        <v>5.398</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12581,22 +12701,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.32</v>
+        <v>5.244</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -12605,7 +12725,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12615,31 +12735,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.972</v>
+        <v>5.228</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -12661,7 +12781,7 @@
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.868</v>
+        <v>4.902</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>10</v>
@@ -12695,10 +12815,10 @@
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.52</v>
+        <v>3.946</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -12729,10 +12849,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.136</v>
+        <v>5.252</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -12751,31 +12871,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.866</v>
+        <v>4.868</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -12785,31 +12905,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.66</v>
+        <v>4.786</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12819,31 +12939,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.622</v>
+        <v>4.778</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>PSU:12 C10:-6 F4:16 RI:54</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -12853,31 +12973,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.61</v>
+        <v>4.778</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:12 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -12887,31 +13007,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.588</v>
+        <v>4.772</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12921,31 +13041,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.488</v>
+        <v>4.618</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -12955,31 +13075,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.48</v>
+        <v>4.572</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>29</v>
+        <v>-9</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -12989,31 +13109,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, LTD.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.404</v>
+        <v>4.568</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:37 BB:5 RI:34</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -13023,31 +13143,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.374</v>
+        <v>4.556</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>32</v>
+        <v>-17</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -13057,31 +13177,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.374</v>
+        <v>4.42</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>-14</v>
+        <v>34</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -13091,31 +13211,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.258</v>
+        <v>4.362</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-11</v>
+        <v>3</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:29</t>
         </is>
       </c>
     </row>
@@ -13125,22 +13245,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.184</v>
+        <v>4.332</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -13149,7 +13269,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -13159,22 +13279,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.182</v>
+        <v>4.264</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
@@ -13183,7 +13303,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:29</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -13193,22 +13313,22 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.106</v>
+        <v>4.232</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -13217,7 +13337,7 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:21 BB:5 C10:-12 RI:43</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -13227,31 +13347,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Cognizant Technology Solutions</t>
+          <t>TKO Group Holdings, Inc.</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.102</v>
+        <v>4.156</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:33 BB:5 RI:32</t>
+          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
         </is>
       </c>
     </row>
@@ -13261,31 +13381,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>BrightView Holdings, Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:3 BB:5 RI:44 SS:29</t>
         </is>
       </c>
     </row>
@@ -13295,31 +13415,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:28 BB:5 C10:28 RI:23</t>
+          <t>PSU:22 F4:5 RI:50</t>
         </is>
       </c>
     </row>
@@ -13329,22 +13449,22 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3.92</v>
+        <v>4.036</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>15</v>
+        <v>-17</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
@@ -13353,7 +13473,7 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1180</v>
+        <v>1187</v>
       </c>
       <c r="C17" s="20" t="n">
-        <v>19.14341336794289</v>
+        <v>19.25697598961713</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>6</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>657</v>
+        <v>672</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.498</t>
+          <t>9 layers firing | cons 5.824</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.848</t>
+          <t>8 layers firing | cons 6.764</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.628</t>
+          <t>8 layers firing | cons 6.606</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7003,22 +7003,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>8 layers firing | cons 5.7</t>
         </is>
       </c>
     </row>
@@ -7053,22 +7053,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>DXC Technology</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.698</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -7078,22 +7078,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.038</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -7103,22 +7103,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.562</t>
         </is>
       </c>
     </row>
@@ -7128,12 +7128,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -7153,12 +7153,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.52</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 5.432</t>
         </is>
       </c>
     </row>
@@ -7203,22 +7203,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Kemper</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Hudson Technologies</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -7228,22 +7228,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>MGPI</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.866</t>
+          <t>7 layers firing | cons 5.232</t>
         </is>
       </c>
     </row>
@@ -7253,22 +7253,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>PRGO</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.844</t>
+          <t>7 layers firing | cons 5.202</t>
         </is>
       </c>
     </row>
@@ -7278,12 +7278,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.866</t>
         </is>
       </c>
     </row>
@@ -7303,22 +7303,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>MGPI</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.68</t>
+          <t>7 layers firing | cons 4.628</t>
         </is>
       </c>
     </row>
@@ -7328,22 +7328,22 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Kemper</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.67</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>GIII</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>AZTA</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.648</t>
+          <t>7 layers firing | cons 4.492</t>
         </is>
       </c>
     </row>
@@ -7378,22 +7378,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.636</t>
+          <t>7 layers firing | cons 4.476</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 6.498</t>
+          <t>9 layers firing | cons 5.824</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.848</t>
+          <t>8 layers firing | cons 6.764</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.628</t>
+          <t>8 layers firing | cons 6.606</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -7678,25 +7678,25 @@
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1394</v>
+        <v>124308</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>8.6</v>
+        <v>151.78</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.48</v>
+        <v>3.63</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>Mega-cap recurring revenue base</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -7722,25 +7722,25 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>124308</v>
+        <v>631</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>151.78</v>
+        <v>15.29</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>3.63</v>
+        <v>0.76</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU + buyback + recent 10b5-1 termination + F4 cluster</t>
+          <t>8 layers firing | cons 5.7</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Mega-cap recurring revenue base</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
@@ -7810,25 +7810,25 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>631</v>
+        <v>1394</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>15.29</v>
+        <v>8.6</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -7837,144 +7837,144 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.698</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>IT services franchise; transformation signal in PSU</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>9011</v>
+        <v>4158</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>176.03</v>
+        <v>88.94</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>4.58</v>
+        <v>2.44</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.038</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>4158</v>
+        <v>7252</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>88.94</v>
+        <v>198.99</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 5.562</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>244</v>
+        <v>101</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>5.02</v>
+        <v>1.89</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.31</v>
+        <v>0.49</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -7986,39 +7986,39 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1043</v>
+        <v>244</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>5.29</v>
+        <v>5.02</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.52</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -8030,41 +8030,39 @@
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>222</v>
+        <v>1043</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+        <v>0.43</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>7 layers firing | cons 5.432</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -8076,25 +8074,27 @@
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1474</v>
+        <v>222</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>25.03</v>
+        <v>5.27</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>27</v>
+        <v>0.93</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -8103,51 +8103,51 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Refrigerant reclaim regulatory moat</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>351</v>
+        <v>9011</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>16.44</v>
+        <v>176.03</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>0.6</v>
+        <v>4.58</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.866</t>
+          <t>7 layers firing | cons 5.232</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -8155,43 +8155,43 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>7252</v>
+        <v>1418</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>198.99</v>
+        <v>10.25</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>6.4</v>
+        <v>0.57</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.844</t>
+          <t>7 layers firing | cons 5.202</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8199,34 +8199,34 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>32997</v>
+        <v>1467</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>78.70999999999999</v>
+        <v>34.77</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>10.04</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -8235,12 +8235,12 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>7 layers firing | cons 4.866</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J20" s="10" t="inlineStr">
@@ -8252,34 +8252,34 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>MGPI</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1418</v>
+        <v>351</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>10.25</v>
+        <v>16.44</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>ebitda_dollar_target</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.68</t>
+          <t>7 layers firing | cons 4.628</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -8287,80 +8287,78 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>13781</v>
+        <v>1474</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>121.36</v>
+        <v>25.03</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.67</t>
+          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1467</v>
+        <v>1074</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>34.77</v>
+        <v>23.31</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -8369,7 +8367,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.648</t>
+          <t>7 layers firing | cons 4.492</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -8377,34 +8375,36 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>399</v>
+        <v>13781</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>1.65</v>
+        <v>121.36</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>17</v>
+        <v>2.85</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.636</t>
+          <t>7 layers firing | cons 4.476</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12475,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.778</v>
+        <v>6.79</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -12497,22 +12497,22 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Shift4 Payments, Inc.</t>
+          <t>Salesforce, Inc.</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.37</v>
+        <v>6.258</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>PSU:30 BB:5 F4:10 RI:51</t>
+          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
         </is>
       </c>
     </row>
@@ -12531,22 +12531,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Salesforce, Inc.</t>
+          <t>Shift4 Payments, Inc.</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.924</v>
+        <v>5.788</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>PSU:36 BB:8 C10:-5 F4:11 RI:61</t>
+          <t>PSU:30 BB:5 F4:10 RI:51</t>
         </is>
       </c>
     </row>
@@ -12565,22 +12565,22 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>EPAM</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>EPAM Systems, Inc.</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.84</v>
+        <v>5.782</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:10 C10:-29 F4:18 RI:53</t>
         </is>
       </c>
     </row>
@@ -12599,22 +12599,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>EPAM</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>EPAM Systems, Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.788</v>
+        <v>5.724</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:10 C10:-29 F4:18 RI:53</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -12633,31 +12633,33 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.578</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>3</v>
+        <v>5.43</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -12667,22 +12669,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.398</v>
+        <v>5.342</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -12691,7 +12693,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:26 BB:5 F4:28 RI:60</t>
         </is>
       </c>
     </row>
@@ -12701,31 +12703,31 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.244</v>
+        <v>5.262</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:26 BB:5 F4:28 RI:60</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -12747,10 +12749,10 @@
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5.228</v>
+        <v>5.23</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -12781,10 +12783,10 @@
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.902</v>
+        <v>4.542</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -12815,10 +12817,10 @@
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3.946</v>
+        <v>4.102</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -12849,10 +12851,10 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.252</v>
+        <v>5.292</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -12871,31 +12873,31 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.868</v>
+        <v>4.88</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -12905,31 +12907,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>SharpLink, Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.786</v>
+        <v>4.878</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>PSU:22 C10:15 RI:71</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -12939,31 +12941,31 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>SharpLink, Inc.</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.778</v>
+        <v>4.816</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>24</v>
+        <v>-3</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:22 C10:15 RI:71</t>
         </is>
       </c>
     </row>
@@ -12973,22 +12975,22 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.778</v>
+        <v>4.79</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>22</v>
+        <v>-9</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -12997,7 +12999,7 @@
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:12 C10:-6 F4:16 RI:54</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -13007,31 +13009,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.772</v>
+        <v>4.77</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>18</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:12 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -13041,31 +13043,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.618</v>
+        <v>4.688</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -13075,31 +13077,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin Enterprises, Inc.</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.572</v>
+        <v>4.688</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-9</v>
+        <v>13</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:48 BB:5 C10:-32 RI:53</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -13121,10 +13123,10 @@
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.568</v>
+        <v>4.63</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -13143,31 +13145,31 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.556</v>
+        <v>4.486</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-17</v>
+        <v>-6</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -13177,31 +13179,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.42</v>
+        <v>4.478</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -13211,31 +13213,31 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Azenta, Inc.</t>
+          <t>Nu Skin Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.362</v>
+        <v>4.472</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>PSU:29</t>
+          <t>PSU:48 BB:5 C10:-32 RI:53</t>
         </is>
       </c>
     </row>
@@ -13245,22 +13247,22 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>CERT</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>Certara, Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.332</v>
+        <v>4.428</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -13269,7 +13271,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:21 BB:5 C10:-12 RI:43</t>
         </is>
       </c>
     </row>
@@ -13279,31 +13281,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Option Care Health, Inc.</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.264</v>
+        <v>4.356</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -13313,31 +13315,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>G-III Apparel Group, LTD.</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.232</v>
+        <v>4.316</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:37 BB:5 RI:34</t>
         </is>
       </c>
     </row>
@@ -13347,31 +13349,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>TKO Group Holdings, Inc.</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.156</v>
+        <v>4.09</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 C10:2 F4:17 RI:42</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -13381,31 +13383,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>CNMD</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>BrightView Holdings, Inc.</t>
+          <t>CONMED Corporation</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>4.07</v>
+        <v>3.988</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:3 BB:5 RI:44 SS:29</t>
+          <t>PSU:28 BB:5 C10:28 RI:23</t>
         </is>
       </c>
     </row>
@@ -13415,31 +13417,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>STIM</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Vitesse Energy, Inc.</t>
+          <t>Neuronetics, Inc.</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>4.05</v>
+        <v>3.986</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-4</v>
+        <v>26</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:22 F4:5 RI:50</t>
+          <t>PSU:29 RI:52 SS:10</t>
         </is>
       </c>
     </row>
@@ -13449,31 +13451,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>OSUR</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>OraSure Technologies, Inc.</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>4.036</v>
+        <v>3.966</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>-17</v>
+        <v>23</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:28 BB:8 RI:42</t>
         </is>
       </c>
     </row>

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -13,14 +13,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Archetype" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reserve Baskets" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Caution List" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Without Valuation" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recent 30d" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foreign Markets" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turnaround Signal" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single-Measure Best" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer Correlation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Tiers" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incentive Improvers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Without Valuation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recent 30d" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foreign Markets" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turnaround Signal" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single-Measure Best" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer Correlation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Tiers" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -29,14 +30,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'By Archetype'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Reserve Baskets'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Caution List'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Incentive Improvers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -186,13 +188,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -695,12 +697,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>Incentive Improvers</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>Latest proxy tightened the incentive architecture (rarity-weighted).</t>
         </is>
       </c>
     </row>
@@ -710,12 +712,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -725,12 +727,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -740,12 +742,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -755,12 +757,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -770,12 +772,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -785,12 +787,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -800,17 +802,32 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -819,7 +836,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -829,6 +846,2264 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Foreign Markets — JP / KR / UK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Japan TSE PBR&lt;1 reform targets, Korea Value-Up chaebol, UK FTSE 100 scheme/take-private candidates. Foreign tickers kept separate from US universe consensus.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Mkt</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ROE %</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>9022.T</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>CENTRAL JAPAN RAILWAY CO</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.6296625</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>5.854111</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>11.4700004</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.63 (TSE reform target); quality+value ROE 11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>9501.T</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>TOKYO ELEC POWER CO HLDGS INC</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0.22752257</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>-12.622</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.23 (TSE reform target); DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>VTY.L</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>VISTRY GROUP PLC ORD 50P</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.26397306</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>6.5333333</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>4.2069998</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>P/B 0.26 (scheme candidate); P/E 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>III.L</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>3I GROUP PLC ORD 73 19/22P</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0.83113635</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>4.679035</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>19.077998</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.83; P/E 4.7; div yield 372.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>VOD.L</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>VODAFONE GROUP PLC ORD USD0.20</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.5547121</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.10899999</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>P/B 0.55 (scheme candidate); div yield 378.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>SBRY.L</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>SAINSBURY (J) PLC ORD 28 4/7P</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.688652</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>17.51089</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>6.4109996</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.69 (scheme candidate); div yield 439.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7203.T</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>TOYOTA MOTOR CORP</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.881705</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>9.148345000000001</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>10.233</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.88; quality+value ROE 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>7267.T</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>HONDA MOTOR CO</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.46575868</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-2.8499998</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.47 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7270.T</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>SUBARU CORPORATION</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.6179315</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>19.150717</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>3.3069998</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.62 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>7201.T</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>NISSAN MOTOR CO</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0.22002745</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>-9.856</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.22 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>1605.T</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>INPEX CORPORATION</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>0.7812199</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>9.943130500000001</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>8.282</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.78; quality+value ROE 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>5020.T</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ENEOS HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.9507054</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>12.411422</v>
+      </c>
+      <c r="G16" s="20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.95; quality+value ROE 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>5401.T</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>NIPPON STEEL CORPORATION</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0.516917</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>166.7683</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.52 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>5411.T</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>JFE HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0.37543565</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>14.648475</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>2.8110001</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.38 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>9101.T</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>NIPPON YUSEN KABUSHIKI KAISHA</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.6957521</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>10.444035</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>7.056</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.70 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>9104.T</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>MITSUI O.S.K. LINES LTD</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0.62819624</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>8.47991</v>
+      </c>
+      <c r="G20" s="20" t="n">
+        <v>7.566000000000001</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.63 (TSE reform target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>1925.T</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>DAIWA HOUSE INDUSTRY CO</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.93027914</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>7.682529</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>12.528</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.93; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>1928.T</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>SEKISUI HOUSE</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.9845158000000001</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>8.268003999999999</v>
+      </c>
+      <c r="G22" s="20" t="n">
+        <v>12.644</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.98; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>9201.T</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>JAPAN AIRLINES CO LTD</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.9385531</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>9.176824</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.94; quality+value ROE 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>9202.T</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ANA HOLDINGS INC</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.90998346</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>9.315649000000001</v>
+      </c>
+      <c r="G24" s="20" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>PBR 0.91; quality+value ROE 13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>9503.T</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>KANSAI ELECTRIC POWER CO INC</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.74417263</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <v>6.766146</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>11.607</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.74; quality+value ROE 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>000660.KS</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>SK hynix</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="n">
+        <v>61.172</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>028260.KS</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>SAMSUNG C&amp;T</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>7.478999999999999</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>066570.KS</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>LGELECTRONICS</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>051910.KS</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>LGCHEM</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>-5.933999999999999</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>006400.KS</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>SAMSUNG SDI CO.,LTD.</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>-2.5710002</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>032830.KS</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>SAMSUNG LIFE</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>5.252</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~48%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>029780.KS</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>SAMSUNG CARD</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="n">
+        <v>7.2129995</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~78%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>017670.KS</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>SKTelecom</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>010140.KS</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>SamsungHvyInd</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="n">
+        <v>13.207</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~28%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>267250.KS</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>HD HYUNDAI</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>16.758</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate; treasury ~37%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>IAG.L</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>INTERNATIONAL CONSOLIDATED AIRL</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>3.4071958</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>7.927419</v>
+      </c>
+      <c r="G36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>P/E 7.9; div yield 178.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ABDN.L</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.88921183</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>11.657143</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>7.823</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>P/B 0.89; div yield 629.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>KGF.L</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>KINGFISHER PLC ORD 15 5/7P</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0.80710936</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>20.921429</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>3.918999799999999</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>P/B 0.81; div yield 430.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>9107.T</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>KAWASAKI KISEN KAISHA</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.85800916</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>11.634099</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>7.754</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>PBR 0.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>005930.KS</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>SamsungElec</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>18.855</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>005380.KS</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>HyundaiMtr</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>7.539999999999999</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>005490.KS</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>POSCO Holdings</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>086790.KS</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>HANAFINANCIALGR</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>9.097</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>316140.KS</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>WooriFinancialGroup</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G44" s="20" t="n">
+        <v>8.518000000000001</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>105560.KS</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>KBFinancialGroup</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>005935.KS</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>SamsungElec(1P)</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G46" s="20" t="n">
+        <v>18.855</v>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>chaebol Value-Up candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>035720.KS</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Kakao</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>012330.KS</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Mobis</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G48" s="20" t="n">
+        <v>7.2270006</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~36%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>015760.KS</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>KEPCO</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>18.671</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>036570.KS</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="20" t="n">
+        <v>14.094</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>251270.KS</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Netmarble</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>6.414000000000001</v>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>010130.KS</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>KOREA ZINC</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G52" s="20" t="n">
+        <v>10.064</v>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>024110.KS</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>7.435</v>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>009540.KS</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>HDKSOE</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G54" s="20" t="n">
+        <v>21.757999</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>047810.KS</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>KOREA AEROSPACE</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="n">
+        <v>10.922</v>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>treasury ~32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>138040.KS</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Meritz Financial</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="n">
+        <v>21.345</v>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>treasury ~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>SHEL.L</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>SHELL PLC ORD EUR0.07</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>1.2567812</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>12.022634</v>
+      </c>
+      <c r="G57" s="19" t="n">
+        <v>10.697</v>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>div yield 396.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>BP.L</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>BP PLC $0.25</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>1.7580478</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>29.628126</v>
+      </c>
+      <c r="G58" s="20" t="n">
+        <v>5.842</v>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>div yield 518.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>ULVR.L</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>UNILEVER PLC ORD 3.5P</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>7.4571557</v>
+      </c>
+      <c r="F59" s="16" t="n">
+        <v>20.560537</v>
+      </c>
+      <c r="G59" s="19" t="n">
+        <v>30.955</v>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>div yield 372.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>HSBA.L</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>HSBC HOLDINGS PLC ORD $0.50 (UK</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>1.8993394</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>15.749999</v>
+      </c>
+      <c r="G60" s="20" t="n">
+        <v>11.611</v>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>div yield 389.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>AZN.L</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>ASTRAZENECA PLC ORD SHS $0.25</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>6.094377</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>27.900793</v>
+      </c>
+      <c r="G61" s="19" t="n">
+        <v>23.482999</v>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>div yield 170.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>GSK.L</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>GSK PLC ORD 31 1/4P</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>4.443819</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>13.897888</v>
+      </c>
+      <c r="G62" s="20" t="n">
+        <v>40.905997</v>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>div yield 349.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>BATS.L</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>BRITISH AMERICAN TOBACCO PLC OR</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>2.2128325</v>
+      </c>
+      <c r="F63" s="16" t="n">
+        <v>13.429799</v>
+      </c>
+      <c r="G63" s="19" t="n">
+        <v>15.824</v>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>div yield 524.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>BARC.L</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>BARCLAYS PLC ORD 25P</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>1.1118265</v>
+      </c>
+      <c r="F64" s="17" t="n">
+        <v>12.046511</v>
+      </c>
+      <c r="G64" s="20" t="n">
+        <v>9.552</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>div yield 170.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Japan signal: TSE explicit policy targets PBR&lt;1 companies for capital return reform; scored highest at PBR&lt;0.7. Korea: Value-Up / treasury cancellation program (chaebol families named candidates: Samsung, Hyundai, LG, SK, POSCO). UK: scheme of arrangement is the dominant take-private mechanism in London; deep-discount FTSE names are the target pool. Source: foreign_markets.json (yfinance with .T/.KS/.L suffixes; seed list ~130 tickers, expandable).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -939,7 +3214,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -981,7 +3256,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -1023,7 +3298,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1065,7 +3340,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -1107,7 +3382,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1149,7 +3424,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1191,7 +3466,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2624,7 +4899,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5184,7 +7459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5706,7 +7981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5784,7 +8059,7 @@
       <c r="B5" s="16" t="n">
         <v>4410</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="19" t="n">
         <v>71.54445165476963</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -5812,7 +8087,7 @@
       <c r="B6" s="17" t="n">
         <v>4410</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="20" t="n">
         <v>71.54445165476963</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -5840,7 +8115,7 @@
       <c r="B7" s="16" t="n">
         <v>6164</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="19" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -5868,7 +8143,7 @@
       <c r="B8" s="17" t="n">
         <v>6164</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="20" t="n">
         <v>100</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -5896,7 +8171,7 @@
       <c r="B9" s="16" t="n">
         <v>2935</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>47.61518494484101</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -5924,7 +8199,7 @@
       <c r="B10" s="17" t="n">
         <v>2807</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="20" t="n">
         <v>45.53861129136924</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -5952,7 +8227,7 @@
       <c r="B11" s="16" t="n">
         <v>1221</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="19" t="n">
         <v>19.80856586632057</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -5980,7 +8255,7 @@
       <c r="B12" s="17" t="n">
         <v>346</v>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="20" t="n">
         <v>5.613238157040882</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -6008,7 +8283,7 @@
       <c r="B13" s="16" t="n">
         <v>346</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="19" t="n">
         <v>5.613238157040882</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -6036,7 +8311,7 @@
       <c r="B14" s="17" t="n">
         <v>164</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="20" t="n">
         <v>2.660609993510707</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -6064,7 +8339,7 @@
       <c r="B15" s="16" t="n">
         <v>260</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="19" t="n">
         <v>4.218040233614536</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -6092,7 +8367,7 @@
       <c r="B16" s="17" t="n">
         <v>1982</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="20" t="n">
         <v>32.15444516547696</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -6120,7 +8395,7 @@
       <c r="B17" s="16" t="n">
         <v>1187</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="19" t="n">
         <v>19.25697598961713</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -6148,7 +8423,7 @@
       <c r="B18" s="17" t="n">
         <v>1142</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="20" t="n">
         <v>18.52693056456846</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -6176,7 +8451,7 @@
       <c r="B19" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="19" t="n">
         <v>0.7300454250486696</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -6204,7 +8479,7 @@
       <c r="B20" s="17" t="n">
         <v>209</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="20" t="n">
         <v>3.390655418559377</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6232,7 +8507,7 @@
       <c r="B21" s="16" t="n">
         <v>71</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="19" t="n">
         <v>1.151849448410123</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -6260,7 +8535,7 @@
       <c r="B22" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="20" t="n">
         <v>0.3082414016872161</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -6288,7 +8563,7 @@
       <c r="B23" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="19" t="n">
         <v>1.443867618429591</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -6476,7 +8751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12380,6 +14655,1800 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Governance / PSU / Incentive-Structure Improvers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Names whose latest proxy tightened the incentive architecture vs the prior plan · rarity-weighted (rare deltas score high, post-2023-rule boilerplate scores low)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Improve</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PSU core</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Gov</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>PSU %</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>What improved</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Caveats / date</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>DOCU</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>DocuSign, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>4.6117125</v>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>PSU weight increased; shareholder-responsive redesign; vesting period extended</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>front-loaded grant (worse) · 2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CMLSQ</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Cumulus Media Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>-0.0003314917</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>ownership requirement added; shareholder-responsive redesign; clawback strengthened; follo</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>GFF</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Griffon Corporation</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>44.497066</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>new performance metric; shareholder-responsive redesign; clawback strengthened; anti-hedge</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>COUR</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Coursera, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>1.4335476</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>PSU weight increased; anti-hedge/pledge added; follows SOP dissent (60%)</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DCH</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Dauch Corporation</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.9973131</v>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>PSU weight increased; shareholder-responsive redesign</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>SMHI</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>SEACOR Marine Holdings Inc</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>0.7303739</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>clawback strengthened; anti-hedge/pledge added; vesting period extended; follows SOP disse</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Intercontinental Exchange</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>69</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>2.5706112</v>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added; follows S</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>CGNX</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Cognex Corporation</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>7.442856</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added; follows S</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>SentinelOne, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>3.5299647</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>PSU weight increased; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>BURL</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Burlington Stores, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>11.411977</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>PSU weight increased; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>THRY</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Thryv Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.6885697</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>CORZ</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Core Scientific, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>-7.07767</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>PSU weight increased; follows SOP dissent (38%)</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ATEN</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>A10 Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>10.80923</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>clawback strengthened; anti-hedge/pledge added; vesting period extended</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>FROG</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>JFrog Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F18" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>10.847102</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>ownership requirement added; vesting period extended</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Agilent Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>82</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>5.0348706</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>CNC</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Centene Corporation</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1.4061527</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>ADC</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Agree Realty Corporation</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>1.4485731</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; shareholder-responsive redesign</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>IRTC</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>iRhythm Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>21.326675</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>ownership requirement added; shareholder-responsive redesign</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>LendingClub Corporation</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>1.4771241</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>NTGR</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>NETGEAR, Inc.</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>1.3377051</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Lithia Motors, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>1.0530019</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>clawback strengthened; vesting period extended; follows SOP dissent (45%)</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>IHRT</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>iHeartMedia, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>-0.32349604</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; follows SOP dissent (73%)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>CSGP</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>CoStar Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>1.5496218</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; follows SOP dissent (53%)</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>PTN</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Palatin Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>1.9654537</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; follows SOP dissent (58%)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>PCVX</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Vaxcyte, Inc.</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>2.4778419</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; follows SOP dissent (64%)</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>2.3349354</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; vesting period extended</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>SHLS</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Shoals Technologies Group,</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>87</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>2.9057446</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>shareholder-responsive redesign; clawback strengthened; follows SOP dissent (61%)</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>VITL</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Vital Farms, Inc.</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>1.3276367</v>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Lamb Weston Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>3.427398</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>new performance metric; anti-hedge/pledge added</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>CHD</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Church &amp; Dwight Company, I</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>5.4116917</v>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>PSU weight increased</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>PTC</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>PTC Inc.</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>3.4336755</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>PSU weight increased</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>HAYW</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Hayward Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>84</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>2.0256584</v>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>PSU weight increased</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>TENB</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Tenable Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>12.405356</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>PSU weight increased</t>
+        </is>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>KNSA</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Kiniksa Pharmaceuticals In</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F39" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>6.3134203</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>PSU weight increased</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>QuantumScape Corporation</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>4.456763</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>PSU weight increased</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>AMTM</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Amentum Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F41" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>1.1471243</v>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>NHI</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>National Health Investors,</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>2.2655873</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>PLMR</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Palomar Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>3.088109</v>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>The RealReal, Inc.</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>-4.1736507</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>WAT</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Waters Corporation</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>2.2817233</v>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>UVSP</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>UVSP</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>ownership requirement added; clawback strengthened</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>3.6310136</v>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>ownership requirement added; follows SOP dissent (77%)</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>WRB</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>W.R. Berkley Corporation</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>2.5707943</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>anti-hedge/pledge added; vesting period extended</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>ARVN</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Arvinas, Inc.</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>1.2789727</v>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>clawback strengthened; anti-hedge/pledge added; follows SOP dissent (75%)</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>983 names show at least one structural improvement in the latest proxy (top 45 shown). Weights reflect rarity across 4,410 scanned DEF 14As: PSU-weight increase (12 occurrences, +25) and ownership-requirement addition (23, +15) are deliberate alignment choices; clawback strengthening (607, +4) and anti-hedge language (331, +6) are largely post-2023 SEC-rule boilerplate. Multi-improvement redesigns earn a conjunction bonus; improvements that follow a sub-80% say-on-pay vote are tagged as forced-response. Regressions (front-loaded grants, metric elimination) subtract and are listed as caveats. Source: proxy_scan plan_deltas + pattern_reasons -- fully data-driven.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A51:I51"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13498,7 +17567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13609,7 +17678,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -13623,7 +17692,7 @@
       <c r="G5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>44</v>
       </c>
       <c r="I5" s="16" t="n">
@@ -13649,7 +17718,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -13663,7 +17732,7 @@
       <c r="G6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="20" t="n">
         <v>96</v>
       </c>
       <c r="I6" s="17" t="n">
@@ -13689,7 +17758,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -13703,7 +17772,7 @@
       <c r="G7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>78</v>
       </c>
       <c r="I7" s="16" t="n">
@@ -13729,7 +17798,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="21" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -13743,7 +17812,7 @@
       <c r="G8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="20" t="n">
         <v>70</v>
       </c>
       <c r="I8" s="17" t="n">
@@ -13769,7 +17838,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -13783,7 +17852,7 @@
       <c r="G9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="19" t="n">
         <v>60</v>
       </c>
       <c r="I9" s="16" t="n">
@@ -13809,7 +17878,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -13823,7 +17892,7 @@
       <c r="G10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="20" t="n">
         <v>61</v>
       </c>
       <c r="I10" s="17" t="n">
@@ -13849,7 +17918,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -13863,7 +17932,7 @@
       <c r="G11" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="19" t="n">
         <v>96</v>
       </c>
       <c r="I11" s="16" t="n">
@@ -13889,7 +17958,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -13903,7 +17972,7 @@
       <c r="G12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="20" t="n">
         <v>49</v>
       </c>
       <c r="I12" s="17" t="n">
@@ -13929,7 +17998,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="21" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -13943,7 +18012,7 @@
       <c r="G13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="19" t="n">
         <v>48</v>
       </c>
       <c r="I13" s="16" t="n">
@@ -13969,7 +18038,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -13983,7 +18052,7 @@
       <c r="G14" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="20" t="n">
         <v>86</v>
       </c>
       <c r="I14" s="17" t="n">
@@ -14009,7 +18078,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="21" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -14023,7 +18092,7 @@
       <c r="G15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="19" t="n">
         <v>36</v>
       </c>
       <c r="I15" s="16" t="n">
@@ -14049,7 +18118,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="21" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -14063,7 +18132,7 @@
       <c r="G16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H16" s="20" t="n">
         <v>63</v>
       </c>
       <c r="I16" s="17" t="n">
@@ -14089,7 +18158,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="21" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -14103,7 +18172,7 @@
       <c r="G17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="19" t="n">
         <v>39</v>
       </c>
       <c r="I17" s="16" t="n">
@@ -14129,7 +18198,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="21" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -14143,7 +18212,7 @@
       <c r="G18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="H18" s="20" t="n">
         <v>82</v>
       </c>
       <c r="I18" s="17" t="n">
@@ -14169,7 +18238,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="21" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -14183,7 +18252,7 @@
       <c r="G19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="19" t="n">
         <v>52</v>
       </c>
       <c r="I19" s="16" t="n">
@@ -14209,7 +18278,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="21" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -14223,7 +18292,7 @@
       <c r="G20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="21" t="n">
+      <c r="H20" s="20" t="n">
         <v>76</v>
       </c>
       <c r="I20" s="17" t="n">
@@ -14249,7 +18318,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="21" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -14263,7 +18332,7 @@
       <c r="G21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="19" t="n">
         <v>58</v>
       </c>
       <c r="I21" s="16" t="n">
@@ -14289,7 +18358,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="21" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -14303,7 +18372,7 @@
       <c r="G22" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="21" t="n">
+      <c r="H22" s="20" t="n">
         <v>45</v>
       </c>
       <c r="I22" s="17" t="n">
@@ -14329,7 +18398,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="21" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -14343,7 +18412,7 @@
       <c r="G23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="19" t="n">
         <v>92</v>
       </c>
       <c r="I23" s="16" t="n">
@@ -14369,7 +18438,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="21" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -14383,7 +18452,7 @@
       <c r="G24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="21" t="n">
+      <c r="H24" s="20" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="17" t="n">
@@ -14409,7 +18478,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="21" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -14423,7 +18492,7 @@
       <c r="G25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="19" t="n">
         <v>31</v>
       </c>
       <c r="I25" s="16" t="n">
@@ -14449,7 +18518,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="21" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -14463,7 +18532,7 @@
       <c r="G26" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="20" t="n">
         <v>53</v>
       </c>
       <c r="I26" s="17" t="n">
@@ -14489,7 +18558,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="21" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="5" t="n">
@@ -14503,7 +18572,7 @@
       <c r="G27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="20" t="n">
+      <c r="H27" s="19" t="n">
         <v>72</v>
       </c>
       <c r="I27" s="16" t="n">
@@ -14529,7 +18598,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="19" t="n">
+      <c r="D28" s="21" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -14543,7 +18612,7 @@
       <c r="G28" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="H28" s="20" t="n">
         <v>66</v>
       </c>
       <c r="I28" s="17" t="n">
@@ -14569,7 +18638,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="21" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -14583,7 +18652,7 @@
       <c r="G29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="20" t="n">
+      <c r="H29" s="19" t="n">
         <v>84</v>
       </c>
       <c r="I29" s="16" t="n">
@@ -14609,7 +18678,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="21" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="8" t="n">
@@ -14623,7 +18692,7 @@
       <c r="G30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="21" t="n">
+      <c r="H30" s="20" t="n">
         <v>67</v>
       </c>
       <c r="I30" s="17" t="n">
@@ -14649,7 +18718,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="21" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -14663,7 +18732,7 @@
       <c r="G31" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="20" t="n">
+      <c r="H31" s="19" t="n">
         <v>80</v>
       </c>
       <c r="I31" s="16" t="n">
@@ -14689,7 +18758,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="21" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="8" t="n">
@@ -14703,7 +18772,7 @@
       <c r="G32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="21" t="n">
+      <c r="H32" s="20" t="n">
         <v>45</v>
       </c>
       <c r="I32" s="17" t="n">
@@ -14729,7 +18798,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="21" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="5" t="n">
@@ -14743,7 +18812,7 @@
       <c r="G33" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="20" t="n">
+      <c r="H33" s="19" t="n">
         <v>41</v>
       </c>
       <c r="I33" s="16" t="n">
@@ -14769,7 +18838,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="D34" s="21" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="8" t="n">
@@ -14783,7 +18852,7 @@
       <c r="G34" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="H34" s="20" t="n">
         <v>37</v>
       </c>
       <c r="I34" s="17" t="n">
@@ -14809,7 +18878,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D35" s="21" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="5" t="n">
@@ -14823,7 +18892,7 @@
       <c r="G35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="20" t="n">
+      <c r="H35" s="19" t="n">
         <v>51</v>
       </c>
       <c r="I35" s="16" t="n">
@@ -14849,7 +18918,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="21" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="8" t="n">
@@ -14863,7 +18932,7 @@
       <c r="G36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="H36" s="20" t="n">
         <v>49</v>
       </c>
       <c r="I36" s="17" t="n">
@@ -14889,7 +18958,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="19" t="n">
+      <c r="D37" s="21" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="5" t="n">
@@ -14903,7 +18972,7 @@
       <c r="G37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="20" t="n">
+      <c r="H37" s="19" t="n">
         <v>25</v>
       </c>
       <c r="I37" s="16" t="n">
@@ -14929,7 +18998,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="19" t="n">
+      <c r="D38" s="21" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -14943,7 +19012,7 @@
       <c r="G38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="H38" s="20" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="17" t="n">
@@ -14969,7 +19038,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="21" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="5" t="n">
@@ -14983,7 +19052,7 @@
       <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="19" t="n">
         <v>29</v>
       </c>
       <c r="I39" s="16" t="n">
@@ -15009,7 +19078,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="19" t="n">
+      <c r="D40" s="21" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -15023,7 +19092,7 @@
       <c r="G40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="21" t="n">
+      <c r="H40" s="20" t="n">
         <v>40</v>
       </c>
       <c r="I40" s="17" t="n">
@@ -15049,7 +19118,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="19" t="n">
+      <c r="D41" s="21" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="5" t="n">
@@ -15063,7 +19132,7 @@
       <c r="G41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="20" t="n">
+      <c r="H41" s="19" t="n">
         <v>57</v>
       </c>
       <c r="I41" s="16" t="n">
@@ -15089,7 +19158,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="19" t="n">
+      <c r="D42" s="21" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="8" t="n">
@@ -15103,7 +19172,7 @@
       <c r="G42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H42" s="21" t="n">
+      <c r="H42" s="20" t="n">
         <v>55</v>
       </c>
       <c r="I42" s="17" t="n">
@@ -15143,7 +19212,7 @@
       <c r="G43" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="20" t="n">
+      <c r="H43" s="19" t="n">
         <v>87</v>
       </c>
       <c r="I43" s="16" t="n">
@@ -15183,7 +19252,7 @@
       <c r="G44" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H44" s="21" t="n">
+      <c r="H44" s="20" t="n">
         <v>63</v>
       </c>
       <c r="I44" s="17" t="n">
@@ -15212,2262 +19281,4 @@
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Foreign Markets — JP / KR / UK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Japan TSE PBR&lt;1 reform targets, Korea Value-Up chaebol, UK FTSE 100 scheme/take-private candidates. Foreign tickers kept separate from US universe consensus.</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Mkt</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>ROE %</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>Reasons</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>9022.T</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>CENTRAL JAPAN RAILWAY CO</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.6296625</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>5.854111</v>
-      </c>
-      <c r="G5" s="20" t="n">
-        <v>11.4700004</v>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.63 (TSE reform target); quality+value ROE 11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>9501.T</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>TOKYO ELEC POWER CO HLDGS INC</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0.22752257</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>-12.622</v>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.23 (TSE reform target); DD 49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>VTY.L</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>VISTRY GROUP PLC ORD 50P</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.26397306</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>6.5333333</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>4.2069998</v>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>P/B 0.26 (scheme candidate); P/E 6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>III.L</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>3I GROUP PLC ORD 73 19/22P</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.83113635</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>4.679035</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>19.077998</v>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.83; P/E 4.7; div yield 372.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>VOD.L</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>VODAFONE GROUP PLC ORD USD0.20</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.5547121</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.10899999</v>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>P/B 0.55 (scheme candidate); div yield 378.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>SBRY.L</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>SAINSBURY (J) PLC ORD 28 4/7P</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>28</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.688652</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>17.51089</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>6.4109996</v>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.69 (scheme candidate); div yield 439.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>7203.T</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>TOYOTA MOTOR CORP</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.881705</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>9.148345000000001</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>10.233</v>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.88; quality+value ROE 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>7267.T</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>HONDA MOTOR CO</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0.46575868</v>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-2.8499998</v>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.47 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>7270.T</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>SUBARU CORPORATION</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.6179315</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>19.150717</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>3.3069998</v>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.62 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>7201.T</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>NISSAN MOTOR CO</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0.22002745</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>-9.856</v>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.22 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>1605.T</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>INPEX CORPORATION</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.7812199</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>9.943130500000001</v>
-      </c>
-      <c r="G15" s="20" t="n">
-        <v>8.282</v>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.78; quality+value ROE 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>5020.T</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>ENEOS HOLDINGS INC</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.9507054</v>
-      </c>
-      <c r="F16" s="17" t="n">
-        <v>12.411422</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.95; quality+value ROE 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>5401.T</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>NIPPON STEEL CORPORATION</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.516917</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>166.7683</v>
-      </c>
-      <c r="G17" s="20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.52 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>5411.T</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>JFE HOLDINGS INC</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0.37543565</v>
-      </c>
-      <c r="F18" s="17" t="n">
-        <v>14.648475</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>2.8110001</v>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.38 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>9101.T</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>NIPPON YUSEN KABUSHIKI KAISHA</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>0.6957521</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>10.444035</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <v>7.056</v>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.70 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>9104.T</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>MITSUI O.S.K. LINES LTD</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0.62819624</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>8.47991</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>7.566000000000001</v>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.63 (TSE reform target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>1925.T</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>DAIWA HOUSE INDUSTRY CO</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0.93027914</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>7.682529</v>
-      </c>
-      <c r="G21" s="20" t="n">
-        <v>12.528</v>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.93; quality+value ROE 13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>1928.T</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>SEKISUI HOUSE</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0.9845158000000001</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>8.268003999999999</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>12.644</v>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.98; quality+value ROE 13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>9201.T</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>JAPAN AIRLINES CO LTD</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.9385531</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>9.176824</v>
-      </c>
-      <c r="G23" s="20" t="n">
-        <v>12.286</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.94; quality+value ROE 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>9202.T</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>ANA HOLDINGS INC</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.90998346</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>9.315649000000001</v>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>PBR 0.91; quality+value ROE 13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>9503.T</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>KANSAI ELECTRIC POWER CO INC</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.74417263</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>6.766146</v>
-      </c>
-      <c r="G25" s="20" t="n">
-        <v>11.607</v>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.74; quality+value ROE 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>000660.KS</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>SK hynix</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>61.172</v>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>028260.KS</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>SAMSUNG C&amp;T</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>7.478999999999999</v>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>066570.KS</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>LGELECTRONICS</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>4.777</v>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>051910.KS</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>LGCHEM</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="n">
-        <v>-5.933999999999999</v>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>006400.KS</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>SAMSUNG SDI CO.,LTD.</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>-2.5710002</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>032830.KS</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>SAMSUNG LIFE</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="n">
-        <v>5.252</v>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~48%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>029780.KS</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>SAMSUNG CARD</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>7.2129995</v>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>017670.KS</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>SKTelecom</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v>2.609</v>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>010140.KS</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>SamsungHvyInd</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="n">
-        <v>13.207</v>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>267250.KS</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>HD HYUNDAI</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="n">
-        <v>16.758</v>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate; treasury ~37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>IAG.L</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>INTERNATIONAL CONSOLIDATED AIRL</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>3.4071958</v>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>7.927419</v>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>P/E 7.9; div yield 178.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>ABDN.L</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>ABERDEEN GROUP PLC ORD 13 61/63</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0.88921183</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>11.657143</v>
-      </c>
-      <c r="G37" s="20" t="n">
-        <v>7.823</v>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>P/B 0.89; div yield 629.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>KGF.L</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>KINGFISHER PLC ORD 15 5/7P</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0.80710936</v>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>20.921429</v>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>3.918999799999999</v>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>P/B 0.81; div yield 430.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>9107.T</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>KAWASAKI KISEN KAISHA</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>0.85800916</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>11.634099</v>
-      </c>
-      <c r="G39" s="20" t="n">
-        <v>7.754</v>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>PBR 0.86</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>005930.KS</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>SamsungElec</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>18.855</v>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>005380.KS</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>HyundaiMtr</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G41" s="20" t="n">
-        <v>7.539999999999999</v>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>005490.KS</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>POSCO Holdings</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G42" s="21" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>086790.KS</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>HANAFINANCIALGR</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>9.097</v>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>316140.KS</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>WooriFinancialGroup</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G44" s="21" t="n">
-        <v>8.518000000000001</v>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>105560.KS</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>KBFinancialGroup</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G45" s="20" t="n">
-        <v>9.991</v>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>005935.KS</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>SamsungElec(1P)</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G46" s="21" t="n">
-        <v>18.855</v>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>chaebol Value-Up candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>035720.KS</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Kakao</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>012330.KS</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Mobis</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="n">
-        <v>7.2270006</v>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>015760.KS</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>KEPCO</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>18.671</v>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>036570.KS</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="n">
-        <v>14.094</v>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~45%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>251270.KS</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Netmarble</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="n">
-        <v>6.414000000000001</v>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>010130.KS</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>KOREA ZINC</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="n">
-        <v>10.064</v>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>024110.KS</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>IBK</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G53" s="20" t="n">
-        <v>7.435</v>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>009540.KS</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>HDKSOE</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G54" s="21" t="n">
-        <v>21.757999</v>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>047810.KS</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>KOREA AEROSPACE</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G55" s="20" t="n">
-        <v>10.922</v>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>treasury ~32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>138040.KS</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Meritz Financial</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G56" s="21" t="n">
-        <v>21.345</v>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>treasury ~60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>SHEL.L</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>SHELL PLC ORD EUR0.07</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>1.2567812</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>12.022634</v>
-      </c>
-      <c r="G57" s="20" t="n">
-        <v>10.697</v>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>div yield 396.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>BP.L</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>BP PLC $0.25</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>1.7580478</v>
-      </c>
-      <c r="F58" s="17" t="n">
-        <v>29.628126</v>
-      </c>
-      <c r="G58" s="21" t="n">
-        <v>5.842</v>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>div yield 518.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>ULVR.L</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>UNILEVER PLC ORD 3.5P</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>7.4571557</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>20.560537</v>
-      </c>
-      <c r="G59" s="20" t="n">
-        <v>30.955</v>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>div yield 372.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>HSBA.L</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>HSBC HOLDINGS PLC ORD $0.50 (UK</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>1.8993394</v>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>15.749999</v>
-      </c>
-      <c r="G60" s="21" t="n">
-        <v>11.611</v>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>div yield 389.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>AZN.L</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>ASTRAZENECA PLC ORD SHS $0.25</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>6.094377</v>
-      </c>
-      <c r="F61" s="16" t="n">
-        <v>27.900793</v>
-      </c>
-      <c r="G61" s="20" t="n">
-        <v>23.482999</v>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>div yield 170.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>GSK.L</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>GSK PLC ORD 31 1/4P</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>4.443819</v>
-      </c>
-      <c r="F62" s="17" t="n">
-        <v>13.897888</v>
-      </c>
-      <c r="G62" s="21" t="n">
-        <v>40.905997</v>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>div yield 349.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>BATS.L</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>BRITISH AMERICAN TOBACCO PLC OR</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>2.2128325</v>
-      </c>
-      <c r="F63" s="16" t="n">
-        <v>13.429799</v>
-      </c>
-      <c r="G63" s="20" t="n">
-        <v>15.824</v>
-      </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>div yield 524.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>BARC.L</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>BARCLAYS PLC ORD 25P</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>1.1118265</v>
-      </c>
-      <c r="F64" s="17" t="n">
-        <v>12.046511</v>
-      </c>
-      <c r="G64" s="21" t="n">
-        <v>9.552</v>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>div yield 170.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>Japan signal: TSE explicit policy targets PBR&lt;1 companies for capital return reform; scored highest at PBR&lt;0.7. Korea: Value-Up / treasury cancellation program (chaebol families named candidates: Samsung, Hyundai, LG, SK, POSCO). UK: scheme of arrangement is the dominant take-private mechanism in London; deep-discount FTSE names are the target pool. Source: foreign_markets.json (yfinance with .T/.KS/.L suffixes; seed list ~130 tickers, expandable).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Most Asymmetric" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Archetype" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reserve Baskets" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Caution List" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incentive Improvers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Without Valuation" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recent 30d" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Foreign Markets" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turnaround Signal" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single-Measure Best" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer Correlation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Tiers" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cover" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Most Asymmetric" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="By Archetype" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Reserve Baskets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Caution List" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Incentive Improvers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Without Valuation" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Recent 30d" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Foreign Markets" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Turnaround Signal" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Single-Measure Best" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Layer Correlation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Methodology" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -192,6 +192,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3214,7 +3217,7 @@
           <t>Jet.AI Inc.</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -3256,7 +3259,7 @@
           <t>BEYOND MEAT, INC.</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -3298,7 +3301,7 @@
           <t>COMTECH TELECOMMUNICATIONS CORP</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -3340,7 +3343,7 @@
           <t>FISERV INC</t>
         </is>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -3382,7 +3385,7 @@
           <t>BTCS Inc.</t>
         </is>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -3424,7 +3427,7 @@
           <t>HERON THERAPEUTICS, INC. /DE/</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="22" t="n">
         <v>35</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -3466,7 +3469,7 @@
           <t>WW INTERNATIONAL, INC.</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -4937,14 +4940,14 @@
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Highest PSU forensic core</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>What it measures: depth + rigor of the PSU plan</t>
         </is>
@@ -5207,14 +5210,14 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Highest governance score</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>What it measures: clawback + anti-hedge + vesting + ownership multiple</t>
         </is>
@@ -5477,14 +5480,14 @@
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Deepest P/B floor (&lt;0.5x book)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>What it measures: hard balance-sheet value floor</t>
         </is>
@@ -5747,14 +5750,14 @@
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Cheapest EV/EBITDA (&lt;6x)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>What it measures: enterprise-value to earnings power</t>
         </is>
@@ -6017,14 +6020,14 @@
       </c>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>Lowest trailing P/E (&lt;8x, positive)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="23" t="inlineStr">
+      <c r="A53" s="24" t="inlineStr">
         <is>
           <t>What it measures: earnings yield</t>
         </is>
@@ -6287,14 +6290,14 @@
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>Largest verified buyback shrinkage</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="23" t="inlineStr">
+      <c r="A65" s="24" t="inlineStr">
         <is>
           <t>What it measures: actual supply curve compression</t>
         </is>
@@ -6557,14 +6560,14 @@
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="22" t="inlineStr">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>Highest 10b5-1 termination signed score</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="23" t="inlineStr">
+      <c r="A77" s="24" t="inlineStr">
         <is>
           <t>What it measures: insider walked back scheduled selling</t>
         </is>
@@ -6827,14 +6830,14 @@
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="22" t="inlineStr">
+      <c r="A88" s="23" t="inlineStr">
         <is>
           <t>Largest insider Form 4 dollar cluster</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="23" t="inlineStr">
+      <c r="A89" s="24" t="inlineStr">
         <is>
           <t>What it measures: insider conviction in dollars</t>
         </is>
@@ -7097,14 +7100,14 @@
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="22" t="inlineStr">
+      <c r="A100" s="23" t="inlineStr">
         <is>
           <t>Live tender / 13E-3 events</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="23" t="inlineStr">
+      <c r="A101" s="24" t="inlineStr">
         <is>
           <t>What it measures: mechanical bid as floor</t>
         </is>
@@ -7987,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8607,7 +8610,7 @@
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B27" s="17" t="n">
         <v>1</v>
@@ -8620,10 +8623,10 @@
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
@@ -8633,10 +8636,10 @@
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -8646,10 +8649,10 @@
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -8659,10 +8662,10 @@
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" s="17" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
@@ -8672,10 +8675,10 @@
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -8685,10 +8688,10 @@
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>364</v>
+        <v>205</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -8698,10 +8701,10 @@
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>672</v>
+        <v>355</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -8711,38 +8714,52 @@
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>679</v>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="17" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="B36" s="16" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>30 total scoring layers, all additive. Coverage and data age are read live from each layer's source file at build time; no figures are hardcoded. Layers with low coverage (Form 4, 13F-delta, tender) are signal-sparse by design — they fire only on names exhibiting the pattern. The layer-firing distribution is the count of names firing on N independent layers; per the correlation analysis (layer_correlation_pairs.csv) the effective-independent layer count is ~21 of 30 at rho&gt;0.6.</t>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>31 total scoring layers, all additive. Coverage and data age are read live from each layer's source file at build time; no figures are hardcoded. Layers with low coverage (Form 4, 13F-delta, tender) are signal-sparse by design — they fire only on names exhibiting the pattern. The layer-firing distribution is the count of names firing on N independent layers; per the correlation analysis (layer_correlation_pairs.csv) the effective-independent layer count is ~21 of 30 at rho&gt;0.6.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="C28:F28"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -8808,7 +8825,7 @@
           <t>Universe construction</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>6,164 US-listed common tickers from cancel_10b5_1.json — authoritative NYSE/Nasdaq/AMEX/CBOE set. Foreign names (JP/KR/UK) live in a separate tab and universe.</t>
         </is>
@@ -8823,7 +8840,7 @@
           <t>Layer ingestion</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>30 additive scoring layers ingested per ticker, spanning PSU forensics, governance, valuation, verified buybacks, tender mechanics, 10b5-1 direction, Form 4 (raw + Cohen-Malloy opportunistic), Form 144, quarterly 10-Q, NCAV, Voss CIC, post-Ch11, internalization, bumpitrage, spinoff timing, Arquitos, Coval-Stafford proxy + real N-PORT, backstopped rights, FDIC dark banks, activist letters, 13F-delta, biotech PDUFA, and financial-sector primary.</t>
         </is>
@@ -8838,7 +8855,7 @@
           <t>Additive discipline</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Every layer ADDS to the composite; none modifies another's score. New legs append fields; existing weights never change. This is enforced and audited (verify_universe_methodology.py).</t>
         </is>
@@ -8853,7 +8870,7 @@
           <t>Coverage-normalised composite</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Sparse-coverage names are not penalised for missing layers; the norm score rescales by sqrt(n_total/n_present) so a name strong on few layers competes with a name mediocre on many.</t>
         </is>
@@ -8868,7 +8885,7 @@
           <t>Per-pattern catalyst ranking</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Top names in each catalyst pattern (forward $ hurdle, M&amp;A close, spin trigger, FDA/PDUFA, post-Ch11, asset sale, etc.) — surfaces single-mandate leaders (see Single-Measure tab).</t>
         </is>
@@ -8883,7 +8900,7 @@
           <t>Archetype winners</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>57 PSU/governance/thesis buckets — single best representative of each archetype across the universe (PSU_ARCHETYPES.md 38 + ASYMMETRIC_BY_ARCHETYPE.md 19).</t>
         </is>
@@ -8898,7 +8915,7 @@
           <t>Consensus meta-ranking</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>n_layers_firing = how many of the 30 independent layers produce a non-zero score for the ticker. consensus_score = sum of per-layer rank-decay contributions across the universe.</t>
         </is>
@@ -8913,7 +8930,7 @@
           <t>Layer independence</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Pairwise Spearman correlation (layer_correlation_pairs.csv) collapses 30 raw layers to ~21 effective-independent at rho&gt;0.6. Three correlated clusters: PSU+Voss, tender family, F4+opportunistic. 'Fires 9 layers' ≈ 7-8 true confirmations.</t>
         </is>
@@ -8928,7 +8945,7 @@
           <t>Freshness weighting</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>layer_freshness.json records each layer's data age. Most layers are &lt;14 days old. An optional age-decay multiplier (opt-in) can down-weight stale layers; current build reports age without auto-decaying.</t>
         </is>
@@ -8943,7 +8960,7 @@
           <t>Caution layering</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Eight red-flag classes from plan text: single-trigger CIC, repricing, retirement carveout, front-loaded grant, discretionary hurdle, aggregate-only metrics, plus structural. Convergence without direction; flag count modulates sizing.</t>
         </is>
@@ -8958,7 +8975,7 @@
           <t>Deployment / sizing</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Concentrated (≥5%): clean high-layer-count names. Material (2-5%): strong but 1-2 flags. Participation (0.5-2%): single-leg or multi-flag. Basket (&lt;1% each): sub-archetype groups, Cohen-Malloy stack, R2000-boundary, NOL shells, foreign.</t>
         </is>
@@ -8973,7 +8990,7 @@
           <t>Honest limitations</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>No realized-return backtest yet (AUDIT.md S1.1) — the composite is a structurally-sound pattern-recognition system, not yet validated alpha. Cohen-Malloy needs deeper Form 4 history. Coval-Stafford proxy supplements but does not replace the N-PORT real signal. See AUDIT.md for the full ledger.</t>
         </is>
@@ -9193,7 +9210,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 5.824</t>
+          <t>10 layers firing | cons 6.906</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9235,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.764</t>
+          <t>9 layers firing | cons 7.734</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9260,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.606</t>
+          <t>9 layers firing | cons 7.512</t>
         </is>
       </c>
     </row>
@@ -9278,22 +9295,22 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>ADT Inc</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.7</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
     </row>
@@ -9303,12 +9320,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -9318,7 +9335,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -9328,22 +9345,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -9353,22 +9370,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>8 layers firing | cons 6.25</t>
         </is>
       </c>
     </row>
@@ -9378,22 +9395,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.562</t>
+          <t>8 layers firing | cons 6.176</t>
         </is>
       </c>
     </row>
@@ -9403,12 +9420,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -9418,7 +9435,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -9428,22 +9445,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -9453,22 +9470,22 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.432</t>
+          <t>8 layers firing | cons 5.798</t>
         </is>
       </c>
     </row>
@@ -9478,12 +9495,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -9493,7 +9510,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>8 layers firing | cons 5.72</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9520,12 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -9518,7 +9535,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.232</t>
+          <t>8 layers firing | cons 5.536</t>
         </is>
       </c>
     </row>
@@ -9528,22 +9545,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Zoetis</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.202</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9570,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -9568,7 +9585,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.866</t>
+          <t>8 layers firing | cons 4.95</t>
         </is>
       </c>
     </row>
@@ -9578,12 +9595,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -9593,7 +9610,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.628</t>
+          <t>7 layers firing | cons 6.298</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9620,12 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -9618,7 +9635,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
     </row>
@@ -9628,12 +9645,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -9643,7 +9660,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.492</t>
+          <t>7 layers firing | cons 5.806</t>
         </is>
       </c>
     </row>
@@ -9653,22 +9670,22 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.476</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9863,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 5.824</t>
+          <t>10 layers firing | cons 6.906</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -9890,7 +9907,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.764</t>
+          <t>9 layers firing | cons 7.734</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -9936,7 +9953,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.606</t>
+          <t>9 layers firing | cons 7.512</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -9997,25 +10014,25 @@
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT Inc</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>631</v>
+        <v>5004</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>15.29</v>
+        <v>6.58</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.76</v>
+        <v>1.38</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -10024,56 +10041,56 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.7</t>
+          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5004</v>
+        <v>101</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>6.58</v>
+        <v>1.89</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1.38</v>
+        <v>0.49</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Heaviest PSU%LTI in universe (90%) + verified -7.3% shrinkage</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>Recurring monitoring revenue + verified supply-curve compression</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -10085,122 +10102,122 @@
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1394</v>
+        <v>4158</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>8.6</v>
+        <v>88.94</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.48</v>
+        <v>2.44</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>OLED IP moat</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4158</v>
+        <v>7252</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>88.94</v>
+        <v>198.99</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>8 layers firing | cons 6.25</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>7252</v>
+        <v>9011</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>198.99</v>
+        <v>176.03</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>6.4</v>
+        <v>4.58</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.562</t>
+          <t>8 layers firing | cons 6.176</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -10208,48 +10225,50 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>101</v>
+        <v>222</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>1.89</v>
+        <v>5.27</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>52</v>
+        <v>0.93</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
@@ -10261,69 +10280,69 @@
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>NUS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Nu Skin</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>244</v>
+        <v>1394</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>5.02</v>
+        <v>8.6</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.31</v>
+        <v>0.48</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>asset_sale_named</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>P/B 0.33 + buyback shrinking organically</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>SBET</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>1043</v>
+        <v>631</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>5.29</v>
+        <v>15.29</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -10332,7 +10351,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.432</t>
+          <t>8 layers firing | cons 5.798</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -10340,50 +10359,48 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>222</v>
+        <v>399</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>5.27</v>
+        <v>1.65</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+        <v>-7.3</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>8 layers firing | cons 5.72</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -10395,25 +10412,27 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>9011</v>
+        <v>13781</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>176.03</v>
+        <v>121.36</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>7</v>
+        <v>2.85</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -10422,7 +10441,7 @@
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.232</t>
+          <t>8 layers firing | cons 5.536</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -10439,25 +10458,25 @@
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1418</v>
+        <v>32997</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>10.25</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0.57</v>
+        <v>10.04</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -10466,51 +10485,51 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.202</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>Animal health franchise</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1467</v>
+        <v>668</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>34.77</v>
+        <v>16.01</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.8</v>
+        <v>1.14</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.866</t>
+          <t>8 layers firing | cons 4.95</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -10527,34 +10546,34 @@
     <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>MGPI</t>
+          <t>GPK</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>351</v>
+        <v>3169</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>16.44</v>
+        <v>10.71</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.6</v>
+        <v>0.98</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>ebitda_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.628</t>
+          <t>7 layers firing | cons 6.298</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -10571,25 +10590,25 @@
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Grocery Outlet</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1474</v>
+        <v>916</v>
       </c>
       <c r="D22" s="17" t="n">
-        <v>25.03</v>
+        <v>9.26</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -10598,12 +10617,12 @@
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>Anti-hedge/pledge + verified buyback EXECUTING (largest verified shrinkage)</t>
+          <t>Forward $ targets + Cohen-Malloy 6-buyer cluster</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
-          <t>Insurer at 0.54x book; $ repurchased = 1.85x NAV-accretive</t>
+          <t>Discount-grocery defensive base</t>
         </is>
       </c>
       <c r="J22" s="10" t="inlineStr">
@@ -10615,25 +10634,25 @@
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1074</v>
+        <v>13476</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>23.31</v>
+        <v>63.68</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -10642,7 +10661,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.492</t>
+          <t>7 layers firing | cons 5.806</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -10659,46 +10678,44 @@
     <row r="24" ht="56" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>NUS</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>Nu Skin</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>13781</v>
+        <v>244</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>121.36</v>
+        <v>5.02</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.31</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>asset_sale_named</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 4.476</t>
+          <t>Named asset-sale trigger + 5-metric clean per-share stack</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>P/B 0.33 + buyback shrinking organically</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -16683,7 +16700,7 @@
         <v>5.724</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -16716,10 +16733,8 @@
       <c r="E10" s="17" t="n">
         <v>5.43</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="F10" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -16753,7 +16768,7 @@
         <v>5.342</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -16787,7 +16802,7 @@
         <v>5.262</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -16821,7 +16836,7 @@
         <v>5.23</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -16855,7 +16870,7 @@
         <v>4.542</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -16889,7 +16904,7 @@
         <v>4.102</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -16923,7 +16938,7 @@
         <v>5.292</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -16956,8 +16971,8 @@
       <c r="E17" s="16" t="n">
         <v>4.88</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>24</v>
+      <c r="F17" s="21" t="n">
+        <v>53</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -16991,7 +17006,7 @@
         <v>4.878</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
@@ -17025,7 +17040,7 @@
         <v>4.816</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -17059,7 +17074,7 @@
         <v>4.79</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
@@ -17093,7 +17108,7 @@
         <v>4.77</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
@@ -17127,7 +17142,7 @@
         <v>4.688</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
@@ -17160,8 +17175,10 @@
       <c r="E23" s="16" t="n">
         <v>4.688</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>13</v>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -17195,7 +17212,7 @@
         <v>4.63</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
@@ -17229,7 +17246,7 @@
         <v>4.486</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
@@ -17263,7 +17280,7 @@
         <v>4.478</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>14</v>
+        <v>-1</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
@@ -17297,7 +17314,7 @@
         <v>4.472</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
@@ -17331,7 +17348,7 @@
         <v>4.428</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -17365,7 +17382,7 @@
         <v>4.356</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
@@ -17399,7 +17416,7 @@
         <v>4.316</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>-10</v>
+        <v>12</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
@@ -17433,7 +17450,7 @@
         <v>4.09</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
@@ -17467,7 +17484,7 @@
         <v>3.988</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>-7</v>
+        <v>15</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
@@ -17501,7 +17518,7 @@
         <v>3.986</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
@@ -17535,7 +17552,7 @@
         <v>3.966</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
@@ -17678,7 +17695,7 @@
           <t>Repay Holdings Corporation</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <v>68</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -17718,7 +17735,7 @@
           <t>Gossamer Bio, Inc.</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="22" t="n">
         <v>61</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -17758,7 +17775,7 @@
           <t>ZoomInfo Technologies Inc.</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <v>60</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -17798,7 +17815,7 @@
           <t>Goosehead Insurance, Inc.</t>
         </is>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="22" t="n">
         <v>53</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -17838,7 +17855,7 @@
           <t>Guidewire Software, Inc.</t>
         </is>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="22" t="n">
         <v>53</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -17878,7 +17895,7 @@
           <t>Comtech Telecommunications Corp</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -17918,7 +17935,7 @@
           <t>BiomX Inc.</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -17958,7 +17975,7 @@
           <t>ChargePoint Holdings, Inc.</t>
         </is>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -17998,7 +18015,7 @@
           <t>DXC Technology Company</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>52</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -18038,7 +18055,7 @@
           <t>Processa Pharmaceuticals, Inc.</t>
         </is>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>51</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -18078,7 +18095,7 @@
           <t>Peabody Energy Corporation</t>
         </is>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="22" t="n">
         <v>51</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -18118,7 +18135,7 @@
           <t>Ready Capital Corporation</t>
         </is>
       </c>
-      <c r="D16" s="21" t="n">
+      <c r="D16" s="22" t="n">
         <v>49</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -18158,7 +18175,7 @@
           <t>Kingsway Corporation</t>
         </is>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="22" t="n">
         <v>49</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -18198,7 +18215,7 @@
           <t>Heron Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="22" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -18238,7 +18255,7 @@
           <t>Standard BioTools Inc.</t>
         </is>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="22" t="n">
         <v>48</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -18278,7 +18295,7 @@
           <t>InspireMD Inc.</t>
         </is>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="22" t="n">
         <v>47</v>
       </c>
       <c r="E20" s="8" t="n">
@@ -18318,7 +18335,7 @@
           <t>Rein Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D21" s="21" t="n">
+      <c r="D21" s="22" t="n">
         <v>46</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -18358,7 +18375,7 @@
           <t>Booz Allen Hamilton Holding Cor</t>
         </is>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="22" t="n">
         <v>46</v>
       </c>
       <c r="E22" s="8" t="n">
@@ -18398,7 +18415,7 @@
           <t>VolitionRX Limited</t>
         </is>
       </c>
-      <c r="D23" s="21" t="n">
+      <c r="D23" s="22" t="n">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -18438,7 +18455,7 @@
           <t>Total Return Securities Fund</t>
         </is>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="22" t="n">
         <v>44</v>
       </c>
       <c r="E24" s="8" t="n">
@@ -18478,7 +18495,7 @@
           <t>Fox Corporation</t>
         </is>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="22" t="n">
         <v>44</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -18518,7 +18535,7 @@
           <t>Outlook Therapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="22" t="n">
         <v>44</v>
       </c>
       <c r="E26" s="8" t="n">
@@ -18558,7 +18575,7 @@
           <t>My Size, Inc.</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E27" s="5" t="n">
@@ -18598,7 +18615,7 @@
           <t>Purple Innovation, Inc.</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E28" s="8" t="n">
@@ -18638,7 +18655,7 @@
           <t>Cosmos Health Inc.</t>
         </is>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -18678,7 +18695,7 @@
           <t>Power Solutions International,</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E30" s="8" t="n">
@@ -18718,7 +18735,7 @@
           <t>NexGel, Inc</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="22" t="n">
         <v>43</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -18758,7 +18775,7 @@
           <t>Salesforce, Inc.</t>
         </is>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="22" t="n">
         <v>42</v>
       </c>
       <c r="E32" s="8" t="n">
@@ -18798,7 +18815,7 @@
           <t>Vitesse Energy, Inc.</t>
         </is>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="22" t="n">
         <v>42</v>
       </c>
       <c r="E33" s="5" t="n">
@@ -18838,7 +18855,7 @@
           <t>Krispy Kreme, Inc.</t>
         </is>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="22" t="n">
         <v>42</v>
       </c>
       <c r="E34" s="8" t="n">
@@ -18878,7 +18895,7 @@
           <t>Nerdy Inc.</t>
         </is>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E35" s="5" t="n">
@@ -18918,7 +18935,7 @@
           <t>Artiva Biotherapeutics, Inc.</t>
         </is>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E36" s="8" t="n">
@@ -18958,7 +18975,7 @@
           <t>STERIS plc (Ireland)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="n">
+      <c r="D37" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E37" s="5" t="n">
@@ -18998,7 +19015,7 @@
           <t>Rubrik, Inc.</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="22" t="n">
         <v>41</v>
       </c>
       <c r="E38" s="8" t="n">
@@ -19038,7 +19055,7 @@
           <t>Medline Inc.</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E39" s="5" t="n">
@@ -19078,7 +19095,7 @@
           <t>Toro Corp.</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E40" s="8" t="n">
@@ -19118,7 +19135,7 @@
           <t>CuriosityStream Inc.</t>
         </is>
       </c>
-      <c r="D41" s="21" t="n">
+      <c r="D41" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E41" s="5" t="n">
@@ -19158,7 +19175,7 @@
           <t>Health Catalyst, Inc</t>
         </is>
       </c>
-      <c r="D42" s="21" t="n">
+      <c r="D42" s="22" t="n">
         <v>40</v>
       </c>
       <c r="E42" s="8" t="n">

--- a/MOST_ASYMMETRIC.xlsx
+++ b/MOST_ASYMMETRIC.xlsx
@@ -14,14 +14,15 @@
     <sheet name="Reserve Baskets" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Caution List" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Incentive Improvers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Without Valuation" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Recent 30d" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Foreign Markets" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Turnaround Signal" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Single-Measure Best" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Layer Correlation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Coverage &amp; Tiers" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Methodology" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Insider Conviction" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Without Valuation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Recent 30d" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Foreign Markets" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Turnaround Signal" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Single-Measure Best" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Layer Correlation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Coverage &amp; Tiers" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Methodology" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Contents'!$1:$4</definedName>
@@ -31,14 +32,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Reserve Baskets'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Caution List'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Incentive Improvers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Without Valuation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Recent 30d'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Foreign Markets'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Turnaround Signal'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Single-Measure Best'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Layer Correlation'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Coverage &amp; Tiers'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Methodology'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Insider Conviction'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Without Valuation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Recent 30d'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Foreign Markets'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Turnaround Signal'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Single-Measure Best'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Layer Correlation'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Coverage &amp; Tiers'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'Methodology'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -715,12 +717,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Without Valuation</t>
+          <t>Insider Conviction</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Parallel ranking excluding the valuation leg.</t>
+          <t>Discretionary open-market buying clusters (code P only, role-weighted).</t>
         </is>
       </c>
     </row>
@@ -730,12 +732,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Recent 30d</t>
+          <t>Without Valuation</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Material incentive events disclosed in the last 30 days.</t>
+          <t>Parallel ranking excluding the valuation leg.</t>
         </is>
       </c>
     </row>
@@ -745,12 +747,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Foreign Markets</t>
+          <t>Recent 30d</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
+          <t>Material incentive events disclosed in the last 30 days.</t>
         </is>
       </c>
     </row>
@@ -760,12 +762,12 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Turnaround Signal</t>
+          <t>Foreign Markets</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Bollenbach pattern: turnaround talent into distress.</t>
+          <t>Japan TSE PBR&lt;1, Korea Value-Up, UK schemes.</t>
         </is>
       </c>
     </row>
@@ -775,12 +777,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Single-Measure Best</t>
+          <t>Turnaround Signal</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Best in class on each individual signal.</t>
+          <t>Bollenbach pattern: turnaround talent into distress.</t>
         </is>
       </c>
     </row>
@@ -790,12 +792,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Layer Correlation</t>
+          <t>Single-Measure Best</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Pairwise layer correlation and effective independence.</t>
+          <t>Best in class on each individual signal.</t>
         </is>
       </c>
     </row>
@@ -805,12 +807,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Coverage &amp; Tiers</t>
+          <t>Layer Correlation</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Live per-layer coverage, data age, firing distribution.</t>
+          <t>Pairwise layer correlation and effective independence.</t>
         </is>
       </c>
     </row>
@@ -820,17 +822,32 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
+          <t>Coverage &amp; Tiers</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Live per-layer coverage, data age, firing distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>How the composite is built, step by step.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Generated by build_most_asymmetric_xlsx.py from the live consensus on disk. Every figure in this workbook is computed at build time; nothing is hardcoded. Single typeface (Times New Roman, 10pt); hierarchy by weight and rule only.</t>
         </is>
@@ -839,7 +856,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -849,6 +866,1722 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stale-Pricing Asymmetry -- Last 30 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Names where a material incentive event was disclosed in the last 30 days AND the price has not yet reflected it. Tightest possible information-lag window.</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Event kind</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Inner</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>DD%</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>RPAY</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Repay Holdings Corporation</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>0.49123317</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>event 6d ago; RESTRUCT_8K; 2 events in 30d; DD 44%; P/B 0.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>GOSS</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Gossamer Bio, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>96</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>-0.24418603</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>event 4d ago; RESTRUCT_8K; 2 events in 30d; DD 96% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>GTM</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0.56459713</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d; DD 78% (unpriced); only 8% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>GSHD</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Goosehead Insurance, Inc.</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>-6.708959</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 70% (unpriced); only 2% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>GWRE</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Guidewire Software, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>6.817952</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>event 16d ago; 10b5-1 termination; DD 60% (unpriced); only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>CMTL</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Comtech Telecommunications Corp</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0.67586595</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>event 4d ago; 2 events in 30d; DD 61% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>PHGE</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>BiomX Inc.</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>96</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>-0.041595332</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>event 5d ago; 3 events in 30d; DD 96% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>CHPT</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>ChargePoint Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>-23.675215</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>event 13d ago; 10b5-1 termination; 2 events in 30d; DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>DXC</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>DXC Technology Company</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>0.4839073</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>event 17d ago; PSU/gov in latest proxy; DD 48%; only 9% above 52w low; P/B 0.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>PCSA</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Processa Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>86</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>2.950474</v>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 5 events in 30d; DD 86% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>BTU</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Peabody Energy Corporation</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>0.91458744</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>event 6d ago; RESTRUCT_8K</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Ready Capital Corporation</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0.23546824</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; PSU/gov in latest proxy; DD 63% (unpriced); P/B 0.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>KWY</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Kingsway Corporation</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>22.396515</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 3 events in 30d; only 5% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>HRTX</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Heron Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>NOL_SHELL</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>9.709301999999999</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>event 5d ago; DD 82% (unpriced); only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Standard BioTools Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>0.5769819</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>event 12d ago; 2 events in 30d; DD 52%; only 5% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NSPR</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>InspireMD Inc.</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0.7626208</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>event 23d ago; insider P-buy; DD 76% (unpriced); only 3% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>RNTX</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Rein Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>-0.7682047</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>event 13d ago; PSU/gov in latest proxy; DD 58%; only 6% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>BAH</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton Holding Cor</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>7.2271833</v>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>event 10d ago; PSU/gov in latest proxy; DD 45%; only 0% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>VNRX</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>VolitionRX Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>92</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>-0.26262623</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 92% (unpriced); only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>SWZ</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Total Return Securities Fund</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0.8557581</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Fox Corporation</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="I25" s="16" t="n">
+        <v>1.8010588</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d; only 2% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>OTLK</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Outlook Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>-5.703971</v>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>event 20d ago; PSU/gov in latest proxy; 4 events in 30d; DD 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>MYSZ</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>My Size, Inc.</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <v>72</v>
+      </c>
+      <c r="I27" s="16" t="n">
+        <v>0.5609756</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 72% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>PRPL</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Purple Innovation, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>-0.7734178</v>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>event 13d ago; PSU/gov in latest proxy; DD 66% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>COSM</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Cosmos Health Inc.</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>84</v>
+      </c>
+      <c r="I29" s="16" t="n">
+        <v>0.5349246</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; PSU/gov in latest proxy; DD 84% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>PSIX</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Power Solutions International,</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>5.0018616</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>event 12d ago; PSU/gov in latest proxy; DD 67% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>NXGL</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>NexGel, Inc</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>1.2016985</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>event 12d ago; PSU/gov in latest proxy; DD 80% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Salesforce, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>3.6310136</v>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>event 24d ago; 10b5-1 termination; DD 45%; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Vitesse Energy, Inc.</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>1.1419401</v>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; DD 41%; only 1% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>DNUT</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Krispy Kreme, Inc.</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>0.98991</v>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>event 5d ago; 2 events in 30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>NRDY</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Nerdy Inc.</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>5.5558443</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>event 4d ago; 2 events in 30d; DD 51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>ARTV</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Artiva Biotherapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>2.0877886</v>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>event 6d ago; 2 events in 30d; DD 49%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>STE</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>STERIS plc (Ireland)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>DEF14A_PSU</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="16" t="n">
+        <v>2.7584</v>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>event 10d ago; PSU/gov in latest proxy; only 4% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Rubrik, Inc.</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>10b5-1_TERM</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>-30.021378</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>event 16d ago; 10b5-1 termination; 2 events in 30d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>MDLN</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Medline Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>RESTRUCT_8K</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="I39" s="16" t="n">
+        <v>2.697388</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>event 19d ago; RESTRUCT_8K; only 10% above 52w low</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>TORO</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Toro Corp.</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>0.6729493</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>event 12d ago; 2 events in 30d; DD 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>CURI</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>CuriosityStream Inc.</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>F4_PBUY</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="I41" s="16" t="n">
+        <v>4.113821</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>event 20d ago; insider P-buy; 2 events in 30d; DD 57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>HCAT</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Health Catalyst, Inc</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>0.98772025</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>event 13d ago; 2 events in 30d; DD 55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>DOMO</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Domo, Inc.</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="I43" s="16" t="n">
+        <v>-0.55213326</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>event 18d ago; 3 events in 30d; DD 87% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>BLND</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Blend Labs, Inc.</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVIST_13D</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>-7.300885</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>event 9d ago; 2 events in 30d; DD 63% (unpriced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>30-day window of `recent_incentive_asymmetry.py`. Event types: DEF14A_PSU (latest proxy), 10b5-1_TERM (insider walked back scheduled selling), F4_PBUY (insider open-market purchase), ACTIVIST_13D, RESTRUCT_8K (8-K restructuring keyword), FORM_10_SPINOFF, NOL_SHELL. Score boosts: drawdown &gt;60% unpriced (+15), multi-event cluster (+12), event in last 7 days (+25). Source: recent_incentive_asymmetry_30d.csv.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3106,7 +4839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4902,7 +6635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7462,13 +9195,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7498,7 +9231,7 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Raw layers: 30    Effective-independent (rho&gt;0.6): 26</t>
+          <t>Raw layers: 31    Effective-independent (rho&gt;0.6): 26</t>
         </is>
       </c>
     </row>
@@ -7527,16 +9260,16 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>f4_buys</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>bumpitrage</t>
+          <t>discretionary_conviction</t>
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>0.783</v>
+        <v>0.963</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -7547,16 +9280,16 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>f4_buys</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>bumpitrage</t>
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>0.667</v>
+        <v>0.783</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -7567,16 +9300,16 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>bumpitrage</t>
+          <t>discretionary_conviction</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>-0.623</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -7587,16 +9320,16 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>f4_buys</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.601</v>
+        <v>0.667</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -7607,56 +9340,56 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>tender</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>tender_mech</t>
+          <t>bumpitrage</t>
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>-0.598</v>
+        <v>-0.623</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very_high</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>quarterly_10q</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0.581</v>
+        <v>0.601</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very_high</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>tender</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>coval_stafford</t>
+          <t>tender_mech</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.515</v>
+        <v>-0.598</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
@@ -7672,11 +9405,11 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.48</v>
+        <v>0.581</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -7687,7 +9420,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -7696,7 +9429,7 @@
         </is>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.474</v>
+        <v>0.513</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -7707,16 +9440,16 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>psu</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
           <t>valuation</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>recent_incentive</t>
-        </is>
-      </c>
       <c r="C16" s="17" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
@@ -7727,7 +9460,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -7736,7 +9469,7 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.428</v>
+        <v>0.477</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -7747,16 +9480,16 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>coval_stafford</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="C18" s="17" t="n">
-        <v>0.411</v>
+        <v>0.46</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -7767,56 +9500,56 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>psu</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C19" s="16" t="n">
-        <v>0.365</v>
+        <v>0.43</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>net_net_ncav</t>
+          <t>coval_stafford</t>
         </is>
       </c>
       <c r="C20" s="17" t="n">
-        <v>0.342</v>
+        <v>0.413</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>psu</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>opportunistic</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>0.34</v>
+        <v>0.365</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -7827,16 +9560,16 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>recent_incentive</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>special_sits</t>
+          <t>net_net_ncav</t>
         </is>
       </c>
       <c r="C22" s="17" t="n">
-        <v>0.301</v>
+        <v>0.342</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -7852,11 +9585,11 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>opportunistic</t>
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -7867,16 +9600,16 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>voss_cic</t>
+          <t>special_sits</t>
         </is>
       </c>
       <c r="C24" s="17" t="n">
-        <v>0.297</v>
+        <v>0.301</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -7887,16 +9620,16 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>recent_incentive</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>financial_primary</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>0.275</v>
+        <v>0.3</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -7907,16 +9640,16 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>f4_buys</t>
+          <t>valuation</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>bb_insider_overlay</t>
+          <t>voss_cic</t>
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>0.274</v>
+        <v>0.297</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
@@ -7927,16 +9660,16 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>discretionary_conviction</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>quarterly_10q</t>
+          <t>bb_insider_overlay</t>
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>0.265</v>
+        <v>0.279</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -7947,25 +9680,85 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>financial_primary</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>f4_buys</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>bb_insider_overlay</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>valuation</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>quarterly_10q</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>psu</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>buyback</t>
         </is>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C31" s="16" t="n">
         <v>0.255</v>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Spearman rank correlation across the full universe. Pairs above rho 0.6 are folded into a single effective layer for the independence count: PSU + Voss CIC (Voss derives from the PSU plan), the tender family (tender + mechanism + bumpitrage share one source), and Form 4 + opportunistic insiders (one refines the other). A high raw layer-firing count should be read against this: nine layers firing is closer to seven or eight genuinely independent confirmations.</t>
         </is>
@@ -7974,8 +9767,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <printOptions horizontalCentered="0"/>
@@ -7984,7 +9777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8067,7 +9860,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -8095,7 +9888,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -8151,7 +9944,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -8179,7 +9972,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -8207,7 +10000,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -8235,7 +10028,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -8263,7 +10056,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -8291,7 +10084,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -8347,7 +10140,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -8375,7 +10168,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -8403,7 +10196,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>3d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -8543,7 +10336,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>2d</t>
+          <t>0d</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -8639,7 +10432,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
@@ -8652,7 +10445,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="16" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
@@ -8678,7 +10471,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="16" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -8691,7 +10484,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="17" t="n">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
@@ -8704,7 +10497,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -8717,7 +10510,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="17" t="n">
-        <v>679</v>
+        <v>642</v>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
@@ -8730,7 +10523,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="16" t="n">
-        <v>1023</v>
+        <v>1094</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -8768,7 +10561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9210,7 +11003,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.906</t>
+          <t>10 layers firing | cons 7.466</t>
         </is>
       </c>
     </row>
@@ -9235,7 +11028,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 7.734</t>
+          <t>9 layers firing | cons 7.668</t>
         </is>
       </c>
     </row>
@@ -9260,7 +11053,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 7.512</t>
+          <t>9 layers firing | cons 7.436</t>
         </is>
       </c>
     </row>
@@ -9320,22 +11113,22 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>8 layers firing | cons 6.662</t>
         </is>
       </c>
     </row>
@@ -9345,22 +11138,22 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>8 layers firing | cons 6.38</t>
         </is>
       </c>
     </row>
@@ -9370,22 +11163,22 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>Universal Display</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.25</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -9395,12 +11188,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -9410,7 +11203,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.176</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
     </row>
@@ -9420,22 +11213,22 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>8 layers firing | cons 5.99</t>
         </is>
       </c>
     </row>
@@ -9445,22 +11238,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
     </row>
@@ -9470,12 +11263,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -9485,7 +11278,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.798</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
     </row>
@@ -9510,7 +11303,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.72</t>
+          <t>8 layers firing | cons 5.128</t>
         </is>
       </c>
     </row>
@@ -9520,22 +11313,22 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.536</t>
+          <t>8 layers firing | cons 4.932</t>
         </is>
       </c>
     </row>
@@ -9545,22 +11338,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>8 layers firing | cons 4.764</t>
         </is>
       </c>
     </row>
@@ -9570,22 +11363,22 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>VTS</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>HF Foods Group</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 4.95</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
     </row>
@@ -9610,7 +11403,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.298</t>
+          <t>7 layers firing | cons 6.246</t>
         </is>
       </c>
     </row>
@@ -9645,12 +11438,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -9660,7 +11453,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.806</t>
+          <t>7 layers firing | cons 5.67</t>
         </is>
       </c>
     </row>
@@ -9863,7 +11656,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>10 layers firing | cons 6.906</t>
+          <t>10 layers firing | cons 7.466</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -9907,7 +11700,7 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 7.734</t>
+          <t>9 layers firing | cons 7.668</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr">
@@ -9953,7 +11746,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>9 layers firing | cons 7.512</t>
+          <t>9 layers firing | cons 7.436</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -10058,157 +11851,157 @@
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>HFFG</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>HF Foods Group</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>101</v>
+        <v>9011</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>1.89</v>
+        <v>176.03</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0.49</v>
+        <v>4.58</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
+          <t>8 layers firing | cons 6.662</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>P/B 0.48 + microcap distributor with hard assets</t>
+          <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Concentrated 5%+</t>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Universal Display</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>4158</v>
+        <v>7252</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>88.94</v>
+        <v>198.99</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>revenue_dollar_target</t>
+          <t>fda_phase_milestone</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
+          <t>8 layers firing | cons 6.38</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>OLED IP moat</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>Universal Display</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>7252</v>
+        <v>4158</v>
       </c>
       <c r="D12" s="17" t="n">
-        <v>198.99</v>
+        <v>88.94</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>6.4</v>
+        <v>2.44</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>fda_phase_milestone</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.25</t>
+          <t>PSU + F4 cluster + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>OLED IP moat</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>9011</v>
+        <v>1394</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>176.03</v>
+        <v>8.6</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>4.58</v>
+        <v>0.48</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
@@ -10217,12 +12010,12 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 6.176</t>
+          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>IT services franchise; transformation signal in PSU</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -10234,71 +12027,71 @@
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>222</v>
+        <v>631</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>5.27</v>
+        <v>15.29</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+        <v>0.76</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
+          <t>8 layers firing | cons 5.99</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>Refrigerant reclaim regulatory moat</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Concentrated 5%+</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Hudson Technologies</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1394</v>
+        <v>222</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>8.6</v>
+        <v>5.27</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>43</v>
+        <v>0.93</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -10307,42 +12100,42 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>PSU core 40 + buyback + recent-incentive 57% drawdown</t>
+          <t>Recent F4 cluster + buyback + special-sits + recent-incentive</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>IT services franchise; transformation signal in PSU</t>
+          <t>Refrigerant reclaim regulatory moat</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Participation 1-2%</t>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>631</v>
+        <v>32997</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>15.29</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>0.76</v>
+        <v>10.04</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
@@ -10351,12 +12144,12 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.798</t>
+          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
+          <t>Animal health franchise</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
@@ -10395,7 +12188,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.72</t>
+          <t>8 layers firing | cons 5.128</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -10412,36 +12205,34 @@
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>13781</v>
+        <v>668</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>121.36</v>
+        <v>16.01</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>1.14</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>spin_separation</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 5.536</t>
+          <t>8 layers firing | cons 4.932</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -10449,34 +12240,36 @@
           <t>see proxy_scan + buyback_verify</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Participation 1-2%</t>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Material 2-5%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>32997</v>
+        <v>13781</v>
       </c>
       <c r="D19" s="16" t="n">
-        <v>78.70999999999999</v>
+        <v>121.36</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>10</v>
+        <v>2.85</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -10485,61 +12278,61 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>F4 cluster + valuation + recent-incentive 60% drawdown</t>
+          <t>8 layers firing | cons 4.764</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Animal health franchise</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>see proxy_scan + buyback_verify</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Participation 1-2%</t>
         </is>
       </c>
     </row>
     <row r="20" ht="56" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>HFFG</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>HF Foods Group</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>668</v>
+        <v>101</v>
       </c>
       <c r="D20" s="17" t="n">
-        <v>16.01</v>
+        <v>1.89</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>1.14</v>
+        <v>0.49</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>spin_separation</t>
+          <t>revenue_dollar_target</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>8 layers firing | cons 4.95</t>
+          <t>Triple PSU $ hurdle (rev/EBITDA/FCF) + clawback strengthened + 4-buyer F4 cluster</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>see proxy_scan + buyback_verify</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Material 2-5%</t>
+          <t>P/B 0.48 + microcap distributor with hard assets</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Concentrated 5%+</t>
         </is>
       </c>
     </row>
@@ -10573,7 +12366,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 6.298</t>
+          <t>7 layers firing | cons 6.246</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -10634,25 +12427,25 @@
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>SBET</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>13476</v>
+        <v>1043</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>63.68</v>
+        <v>5.29</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>1.46</v>
+        <v>0.43</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
@@ -10661,7 +12454,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>7 layers firing | cons 5.806</t>
+          <t>7 layers firing | cons 5.67</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -13204,7 +14997,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="C9" s="16" t="n">
@@ -13212,12 +15005,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
+          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -13227,7 +15020,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C10" s="17" t="n">
@@ -13235,12 +15028,12 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout, single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -13687,7 +15480,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C30" s="17" t="n">
@@ -13695,12 +15488,12 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>retirement carveout</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -13710,7 +15503,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C31" s="16" t="n">
@@ -13718,12 +15511,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -13756,7 +15549,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>OPCH</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="C33" s="16" t="n">
@@ -13764,12 +15557,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -13779,7 +15572,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>LGL</t>
         </is>
       </c>
       <c r="C34" s="17" t="n">
@@ -13787,12 +15580,12 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, repricing language</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -13802,7 +15595,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>LGL</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C35" s="16" t="n">
@@ -13810,12 +15603,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -13825,7 +15618,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C36" s="17" t="n">
@@ -13833,12 +15626,12 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Participation — limited size</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -13894,7 +15687,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>TBI</t>
         </is>
       </c>
       <c r="C39" s="16" t="n">
@@ -13902,7 +15695,7 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>retirement carveout, single-trigger CIC</t>
+          <t>discretionary hurdle, retirement carveout</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -13917,7 +15710,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>TBI</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C40" s="17" t="n">
@@ -13925,7 +15718,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
+          <t>retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -14009,7 +15802,7 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>LCID</t>
         </is>
       </c>
       <c r="C44" s="17" t="n">
@@ -14017,12 +15810,12 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, front-loaded grant, repricing language, retirement carveout, single-trigger CIC</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -14032,7 +15825,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>LCID</t>
+          <t>CDE</t>
         </is>
       </c>
       <c r="C45" s="16" t="n">
@@ -14040,12 +15833,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, front-loaded grant, repricing language, retirement carveout, single-trigger CIC</t>
+          <t>single-trigger CIC</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -14055,7 +15848,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>CDE</t>
+          <t>PSN</t>
         </is>
       </c>
       <c r="C46" s="17" t="n">
@@ -14063,12 +15856,12 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
+          <t>discretionary hurdle, repricing language, retirement carveout, single-trigger CIC</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>Watch only — multi-flag stack</t>
         </is>
       </c>
     </row>
@@ -14078,7 +15871,7 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>PSN</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C47" s="16" t="n">
@@ -14086,12 +15879,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout, single-trigger CIC</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Watch only — multi-flag stack</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -14147,7 +15940,7 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>PII</t>
         </is>
       </c>
       <c r="C50" s="17" t="n">
@@ -14155,12 +15948,12 @@
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>discretionary hurdle, retirement carveout</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Material — basket diversify</t>
+          <t>discretionary hurdle, repricing language, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Participation — limited size</t>
         </is>
       </c>
     </row>
@@ -14170,7 +15963,7 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>PII</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="C51" s="16" t="n">
@@ -14178,12 +15971,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>discretionary hurdle, repricing language, retirement carveout</t>
+          <t>single-trigger CIC</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Participation — limited size</t>
+          <t>Concentrate (1 flag tolerable)</t>
         </is>
       </c>
     </row>
@@ -14285,7 +16078,7 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>IDA</t>
+          <t>JTAI</t>
         </is>
       </c>
       <c r="C56" s="17" t="n">
@@ -14293,12 +16086,12 @@
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>retirement carveout</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Concentrate (1 flag tolerable)</t>
+          <t>discretionary hurdle, retirement carveout</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Material — basket diversify</t>
         </is>
       </c>
     </row>
@@ -14308,7 +16101,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C57" s="16" t="n">
@@ -14316,7 +16109,7 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>single-trigger CIC</t>
+          <t>retirement carveout</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -16466,6 +18259,1832 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Discretionary Insider-Conviction Clusters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Open-market purchases only (Form 4 code P) · clustered, role-weighted, dollar-gated · grants and option exercises excluded by construction</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Conviction</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Insiders</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Same day</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>C-suite</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Total $M</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Top $M</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>BETR</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Better Home &amp; Finance Hold</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x5; 6 insiders in 28d; 3 C-suite buyers; $7.4M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>NSP</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Insperity, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 4 insiders in 8d; 2 C-suite buyers; $7.6M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>KKR &amp; Co. Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 5 insiders in 15d; 2 C-suite buyers; $17.2M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>On Holding AG</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers; $2.2M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>PATK</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Patrick Industries, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x5; 2 C-suite buyers; $2.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>POOL</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Pool Corporation</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 4 insiders in 4d; C-suite buyer; $5.8M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>TKO</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>TKO Group Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers; $2.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>ODTX</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Odyssey Therapeutics, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>75.31999999999999</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x5; 7 insiders in 2d; C-suite buyer; $25.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Grocery Outlet Holding Cor</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 6 insiders in 11d; C-suite buyer; $2.8M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>SRAD</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Sportradar Group AG</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x7; C-suite buyer; $10.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>FLUT</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Flutter Entertainment plc</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x5; 7 insiders in 1d; 4 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>IBP</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Installed Building Product</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x4; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>MOBI</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Mobia Medical, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x5; 6 insiders in 1d; $8.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>OPCH</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Option Care Health, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 3d; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>FCN</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>FTI Consulting, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers; $1.4M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>MRP</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Millrose Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; C-suite buyer; $6.4M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>HubSpot, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>39</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers; $1.8M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>XRN</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Chiron Real Estate Inc.</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 9 insiders in 4d; 3 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>GRNT</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Granite Ridge Resources, I</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>38</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 5 insiders in 1d; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>EVTC</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Evertec, Inc.</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 1d; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>VSNT</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Versant Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 7d; $5.3M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Lamb Weston Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>4 insiders in 21d; C-suite buyer; $16.1M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Nike, Inc.</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 6d; C-suite buyer; $2.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>GSHD</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Goosehead Insurance, Inc.</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 17d; 3 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>STRT</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>STRATTEC SECURITY CORPORAT</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>33</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>INSE</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Inspired Entertainment, In</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Taiwan Semiconductor Manuf</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x28; 6 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>PLSE</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Pulse Biosciences, Inc</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; C-suite buyer; $26.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>AGBK</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>AGI Inc</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 3d; 3 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>AVBC</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Avidia Bancorp, Inc.</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 3 insiders in 4d; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>PSN</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Parsons Corporation</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>4 insiders in 3d; C-suite buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>TXO</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>TXO Partners, L.P.</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; $13.4M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>AAT</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>American Assets Trust, Inc</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>C-suite buyer; $3.6M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>C-suite buyer; $13.4M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ALKT</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Alkami Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>65.86</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; $32.9M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>C-suite buyer; $7.8M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>OLED</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Universal Display Corporat</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 3 insiders in 2d; C-suite buyer; $1.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>WCN</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Waste Connections, Inc.</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>C-suite buyer; $7.6M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>PAM</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>PAM</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>C-suite buyer; $4.1M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>CHTR</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Charter Communications, In</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 3 insiders in 1d; C-suite buyer; $1.2M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QTTB</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Q32 Bio Inc.</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; $15.0M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>INFU</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>InfuSystems Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; 2 C-suite buyers</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>NSPR</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>InspireMD Inc.</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x2; 4 insiders in 5d; C-suite buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>MSCI</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>MSCI Inc.</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>C-suite buyer; $3.6M top buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>ADT Inc.</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>same-day cluster x3; C-suite buyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>139 names show scored discretionary buying (top 45 shown); 99 have a multi-insider cluster inside a 45-day window and 74 a same-day cluster. Population is Form 4 transaction code P only -- open-market cash purchases; grants (code A) and option exercises (code M) are excluded at the scanner, so every dollar here is discretionary. Cluster credit follows Lakonishok-Lee (temporal concentration, not raw count) and is scaled by aggregate dollars committed so filing artifacts cannot masquerade as conviction. Dollars are role-weighted (CEO/CFO 1.6x, Chair 1.5x, director 1.0x, 10% holder 0.6x); multiple C-suite buying together is the rarest and highest-signal configuration. This layer is additive and orthogonal to the raw Form 4 layer and the Cohen-Malloy opportunistic layer. Source: discretionary_insider_conviction.json.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16561,7 +20180,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>6.79</v>
+        <v>6.634</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -16595,7 +20214,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>6.258</v>
+        <v>6.002</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>2</v>
@@ -16629,7 +20248,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>5.788</v>
+        <v>5.706</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>-2</v>
@@ -16663,7 +20282,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5.782</v>
+        <v>5.878</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>-2</v>
@@ -16685,22 +20304,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Universal Display Corporation</t>
+          <t>HubSpot, Inc.</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>5.724</v>
+        <v>5.832</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
@@ -16709,7 +20328,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:17 RI:60</t>
+          <t>PSU:4 BB:5 F4:17 RI:57</t>
         </is>
       </c>
     </row>
@@ -16719,31 +20338,31 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>ADT Inc.</t>
+          <t>Universal Display Corporation</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>5.43</v>
+        <v>5.504</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
+          <t>PSU:39 BB:5 F4:17 RI:60</t>
         </is>
       </c>
     </row>
@@ -16765,10 +20384,12 @@
         <v>7</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>5.342</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>5.152</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
@@ -16787,22 +20408,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>BLND</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>HubSpot, Inc.</t>
+          <t>Blend Labs, Inc.</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5.262</v>
+        <v>5.058</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
@@ -16811,7 +20432,7 @@
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>PSU:4 BB:5 F4:17 RI:57</t>
+          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
         </is>
       </c>
     </row>
@@ -16821,31 +20442,31 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>PAR Technology Corporation</t>
+          <t>ADT Inc.</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5.23</v>
+        <v>4.962</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>PSU:16 C10:-50 RI:45 SS:35</t>
+          <t>PSU:39 BB:5 F4:12 RI:50 SS:10</t>
         </is>
       </c>
     </row>
@@ -16855,22 +20476,24 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>BLND</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Blend Labs, Inc.</t>
+          <t>PAR Technology Corporation</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>4.542</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>3</v>
+        <v>4.96</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
@@ -16879,7 +20502,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-35 F4:5 RI:52 SS:20</t>
+          <t>PSU:16 C10:-50 RI:45 SS:35</t>
         </is>
       </c>
     </row>
@@ -16901,10 +20524,10 @@
         <v>7</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>4.102</v>
+        <v>3.914</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
@@ -16935,7 +20558,7 @@
         <v>6</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>5.292</v>
+        <v>5.18</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>6</v>
@@ -16957,22 +20580,22 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>SNBR</t>
+          <t>APTV</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Sleep Number Corporation</t>
+          <t>Aptiv PLC</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>53</v>
+        <v>5.024</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>35</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -16981,7 +20604,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>PSU:49 RI:46 SS:20</t>
+          <t>PSU:40 BB:5 RI:35</t>
         </is>
       </c>
     </row>
@@ -16991,31 +20614,31 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>HDSN</t>
+          <t>SNBR</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Hudson Technologies, Inc.</t>
+          <t>Sleep Number Corporation</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E18" s="17" t="n">
-        <v>4.878</v>
+        <v>4.874</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>-4</v>
+        <v>41</v>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:18 RI:58</t>
+          <t>PSU:49 RI:46 SS:20</t>
         </is>
       </c>
     </row>
@@ -17037,10 +20660,10 @@
         <v>6</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>4.816</v>
+        <v>4.824</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
@@ -17059,31 +20682,31 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>DXC</t>
+          <t>PRGO</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>DXC Technology Company</t>
+          <t>Perrigo Company plc</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>4.79</v>
+        <v>4.676</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-5</v>
+        <v>13</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:57</t>
+          <t>PSU:20 RI:48 SS:29</t>
         </is>
       </c>
     </row>
@@ -17093,31 +20716,31 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ALKT</t>
+          <t>HDSN</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Alkami Technology, Inc.</t>
+          <t>Hudson Technologies, Inc.</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>4.77</v>
+        <v>4.646</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>7</v>
+        <v>-6</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>PSU:12 C10:-6 F4:16 RI:54</t>
+          <t>BB:5 F4:18 RI:58</t>
         </is>
       </c>
     </row>
@@ -17127,31 +20750,31 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Zoetis Inc.</t>
+          <t>MSCI Inc.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>4.688</v>
+        <v>4.604</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
+          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
         </is>
       </c>
     </row>
@@ -17161,33 +20784,31 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>APTV</t>
+          <t>ALKT</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Aptiv PLC</t>
+          <t>Alkami Technology, Inc.</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>4.688</v>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>4.564</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>PSU:40 BB:5 RI:35</t>
+          <t>PSU:12 C10:-6 F4:16 RI:54</t>
         </is>
       </c>
     </row>
@@ -17197,31 +20818,31 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>MSCI Inc.</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>4.63</v>
+        <v>4.52</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>PSU:35 BB:8 C10:-26 F4:16 RI:16</t>
+          <t>BB:5 F4:6 RI:54</t>
         </is>
       </c>
     </row>
@@ -17231,22 +20852,22 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>PRGO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Perrigo Company plc</t>
+          <t>Zoetis Inc.</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4.486</v>
+        <v>4.49</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>9</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
@@ -17255,7 +20876,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>PSU:20 RI:48 SS:29</t>
+          <t>PSU:8 BB:5 C10:-3 F4:12 RI:60</t>
         </is>
       </c>
     </row>
@@ -17265,31 +20886,31 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>AECOM</t>
+          <t>Mastercard Incorporated</t>
         </is>
       </c>
       <c r="D26" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>4.478</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>-1</v>
+        <v>4.43</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>51</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>BB:5 F4:6 RI:54</t>
+          <t>PSU:32 BB:5 C10:78 RI:50</t>
         </is>
       </c>
     </row>
@@ -17311,7 +20932,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4.472</v>
+        <v>4.374</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>-3</v>
@@ -17333,22 +20954,24 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>OPCH</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Certara, Inc.</t>
+          <t>Option Care Health, Inc.</t>
         </is>
       </c>
       <c r="D28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>4.428</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>5</v>
+        <v>4.358</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
@@ -17357,7 +20980,7 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>PSU:21 BB:5 C10:-12 RI:43</t>
+          <t>PSU:24 BB:5 C10:-1 F4:23 RI:52</t>
         </is>
       </c>
     </row>
@@ -17367,31 +20990,31 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>KMPR</t>
+          <t>AZTA</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Kemper Corporation</t>
+          <t>Azenta, Inc.</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>4.356</v>
+        <v>4.348</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>PSU:27 BB:8 C10:20 RI:65</t>
+          <t>PSU:29</t>
         </is>
       </c>
     </row>
@@ -17401,31 +21024,31 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>DXC</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, LTD.</t>
+          <t>DXC Technology Company</t>
         </is>
       </c>
       <c r="D30" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>4.316</v>
+        <v>4.184</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>12</v>
+        <v>-17</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>PSU:37 BB:5 RI:34</t>
+          <t>PSU:40 BB:5 RI:57</t>
         </is>
       </c>
     </row>
@@ -17435,31 +21058,31 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>G-III Apparel Group, LTD.</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>4.09</v>
+        <v>4.086</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>PSU:32 BB:5 C10:78 RI:50</t>
+          <t>PSU:37 BB:5 RI:34</t>
         </is>
       </c>
     </row>
@@ -17469,31 +21092,31 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>CNMD</t>
+          <t>AAT</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>CONMED Corporation</t>
+          <t>American Assets Trust, Inc.</t>
         </is>
       </c>
       <c r="D32" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E32" s="17" t="n">
-        <v>3.988</v>
+        <v>4.08</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 BB:5 C10:28 RI:23</t>
+          <t>PSU:4 BB:5 C10:-12 F4:5 RI:37 SS:10</t>
         </is>
       </c>
     </row>
@@ -17503,31 +21126,31 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>STIM</t>
+          <t>KMPR</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Neuronetics, Inc.</t>
+          <t>Kemper Corporation</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>3.986</v>
+        <v>4.048</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>PSU:29 RI:52 SS:10</t>
+          <t>PSU:27 BB:8 C10:20 RI:65</t>
         </is>
       </c>
     </row>
@@ -17537,31 +21160,31 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>OSUR</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>OraSure Technologies, Inc.</t>
+          <t>Maximus, Inc.</t>
         </is>
       </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>3.966</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>10</v>
+        <v>4.03</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>61</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>PSU:28 BB:8 RI:42</t>
+          <t>PSU:36 BB:5 RI:53 SS:26</t>
         </is>
       </c>
     </row>
@@ -17582,1720 +21205,4 @@
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stale-Pricing Asymmetry -- Last 30 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Names where a material incentive event was disclosed in the last 30 days AND the price has not yet reflected it. Tightest possible information-lag window.</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>